--- a/approved_jobs.xlsx
+++ b/approved_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H128"/>
+  <dimension ref="A1:H227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -471,55 +471,55 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-06T18:32:19.531425+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mercor</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fully Remote (Work From Home)</t>
+          <t>Tel Aviv, Israel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://bit.ly/4fQS7dt</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/job/Tel-Aviv-Israel/Intern_R1227757</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>R1227757</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-06T18:32:12.802999+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -530,102 +530,110 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bengaluru-VTP, India</t>
+          <t>Tel Aviv, Israel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/job/Tel-Aviv-Israel/Intern_R1275825</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>R1275825</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-06T18:32:12.088231+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ecologic Hackathon</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Wilayah Persekutuan Kuala Lumpur, Malaysia</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://bit.ly/EcoLogicHackathon</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/job/Wilayah-Persekutuan-Kuala-Lumpur-Malaysia/Intern_R1559598</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>R1559598</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-06T18:32:11.785346+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Generalist</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sofia, Bulgaria</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://bit.ly/4A1zUSE</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/job/Sofia-Bulgaria/Intern_R1563082</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>R1563082</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-06T18:32:09.855425+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>China Clinical Intern</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -634,32 +642,36 @@
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://hccz.fa.em3.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_2/job/25450</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/job/Shanghai-China/China-Clinical-Intern_R1509980</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>R1509980</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-06T18:32:09.765669+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>CRA Intern-KunTuo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -668,32 +680,36 @@
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2 Locations</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://careers.cargill.com/en/job/-/-/23251/100079360032</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/job/Beijing-China/CRA-Intern-_R1554563</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>R1554563</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-06T18:32:08.510234+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SDE Intern</t>
+          <t>DM Intern-KunTuo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spyne</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -702,222 +718,226 @@
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>3 Locations</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://spyneai.keka.com/careers/jobdetails/156605</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/job/Beijing-China/DM-Intern-KunTuo_R1554593</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>R1554593</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-06T18:32:08.206959+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>YouTube &amp; Content - Internship</t>
+          <t>HRBP Intern-KunTuo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bengaluru-VTP, India</t>
+          <t>2 Locations</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/job/Beijing-China/HRBP-Intern-KunTuo_R1554608</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>YouTube &amp; Content - Internship</t>
+          <t>R1554608</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:59.524083+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Frontend Engineer</t>
+          <t>RA Intern-KunTuo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Beijing, China</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://bit.ly/4i9Esjd</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/job/Beijing-China/RA-Intern-KunTuo_R1567157</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>R1567157</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:57.840717+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Visual Designer</t>
+          <t>BI Intern, EMEA Tech</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Athens, Greece</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://bit.ly/4ye7bbp</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/job/Athens-Greece/BI-Intern--EMEA-Tech_R1211502</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>R1211502</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:56.243151+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UX Designer</t>
+          <t>Intern Analyst - SEE Consulting</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Prague, Czech Republic</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://bit.ly/4wWLfQV</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/job/Prague-Czech-Republic/Intern-analyst_R1260082</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>R1260082</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:54.557526+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>CTA Intern （Admin function）</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Data / AI</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://bit.ly/3Usl5bu</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/job/Shanghai-China/CTA-Intern--Admin-function-_R1323639</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>R1323639</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:51.717612+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Quantitative Developer Intern</t>
+          <t>Intern - Country Site Activation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Towerresearchcapital</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -928,34 +948,34 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Lisbon, Portugal</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=7011493</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/job/Lisbon-Portugal/Intern---Country-Site-Activation_R1564897</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Quantitative Developer Intern</t>
+          <t>R1564897</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:49.789951+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>APAC Strategic Planning Intern</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Proctor &amp; Gamble</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -964,108 +984,112 @@
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.pgcareers.com/global/en/job/R000158265/Information-Technology-Intern</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/job/Shanghai-China/APAC-Strategic-Planning-Intern_R1566929</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>R1566929</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:47.137206+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Product Designer</t>
+          <t>Intern in the Accounting Department</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Bratislava, Slovakia</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://bit.ly/4xuqIEp</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/job/Bratislava-Slovakia/Intern-in-the-Accounting-Department_R1323476</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>R1323476</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:45.345284+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SDE1</t>
+          <t>Accounting Associate Intern, Student, hybrid</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hevo Data</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Sofia, Bulgaria</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://docs.google.com/forms/d/e/1FAIpQLSdUXEWZMGd9k4A_Thkhl_tya1Zcu5ROnWP9SjMKhHSQzKUGog/viewform</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/job/Sofia-Bulgaria/Accounting-Associate-Intern-Bulgarian-student-eligible_R1427959</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>R1427959</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:42.493975+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Quantitative Trader/Researcher Summer Internship 2027 (2028 Graduates)</t>
+          <t>Safety Operations Intern-DL 2027</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Towerresearchcapital</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1076,110 +1100,110 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Dalian, Liaoning, China</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=8037860</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/job/Dalian-Liaoning-China/Safety-Operations-Intern-DL-2027_R1538929</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Quantitative Trader/Researcher Summer Internship 2027 (2028 Graduates)</t>
+          <t>R1538929</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:39.619912+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Brand Manager – Netherlands &amp; International Markets</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Remote (Work From Home)</t>
+          <t>Amsterdam, Netherlands</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://bit.ly/4guHNbm</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/job/Amsterdam-Netherlands/Brand-Manager---Netherlands---International-Markets_R1559455</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>R1559455</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:37.644164+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AI Fullstack Engineer Intern</t>
+          <t>HRBP Intern (见习生）</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Gesture</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://jobs.gusto.com/postings/gesture-us-inc-ai-full-stack-engineer-intern-e6b31003-155a-48dd-a442-a664809ff969</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/job/Shanghai-China/HRBP-Intern---_R1565088</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>R1565088</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:34.590215+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Safety Operations Intern-DL 2027</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Joveo</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1188,32 +1212,36 @@
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dalian, Liaoning, China</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4458863278/</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/job/Dalian-Liaoning-China/Safety-Operations-Intern-DL-2027_R1565896</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>R1565896</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:32.212932+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Quantitative Researcher Intern, Bachelor or Master</t>
+          <t>Software Engineer Winter Intern</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Towerresearchcapital</t>
+          <t>Rubrik</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1224,29 +1252,29 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Singapore, Hong Kong, Shanghai, Sydney</t>
+          <t>Bangalore, India</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=8168750</t>
+          <t>https://bit.ly/RubrikIntern2027</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Quantitative Researcher Intern, Bachelor or Master</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:29.806106+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Quantitative Researcher Intern, PhD or Postdoc</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1262,68 +1290,72 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Singapore, Hong Kong, Shanghai, Sydney</t>
+          <t>Gift City</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=8168634</t>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=8184771</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Quantitative Researcher Intern, PhD or Postdoc</t>
+          <t>Intern</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:26.26421+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ecologic Hackathon</t>
+          <t>Intern - Advisory Services (m/w/d)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2 Locations</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://bit.ly/EcoLogicHackathon</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/job/Munich-Bavaria-Germany/Intern---Advisory-Services_R1539595</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>R1539595</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:23.45402+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tata Imagination Challenge</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tata</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1332,10 +1364,14 @@
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://bit.ly/TataChallenge2026</t>
+          <t>https://bit.ly/4r2sHxt</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1347,22 +1383,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:10.428183+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Github Contributor</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Weekday works</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1373,7 +1409,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/weekdayworks/a86efff4-1c2e-43fc-8ecb-dc8f873db2f1</t>
+          <t>https://bit.ly/3SwmNYL</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1385,17 +1421,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:07.464823+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ecologic Hackathon</t>
+          <t>Tata Imagination Challenge</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tata</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1407,7 +1443,7 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://bit.ly/EcoLogicHackathon</t>
+          <t>https://bit.ly/TataChallenge2026</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1419,29 +1455,33 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-06T18:29:59.581469+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fullstack Developer Intern</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Amber</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Bengaluru, India</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://amberstudent.keka.com/careers/jobdetails/140686</t>
+          <t>https://stripe.com/careers/listing/software-engineer-intern/8031833?gh_src=KrishanKumarLinkedin</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1453,17 +1493,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-06T18:29:55.077161+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Video Annotation Specialist</t>
+          <t>Tata Challenge 2026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Tata</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1472,14 +1512,10 @@
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://bit.ly/4ienwrP</t>
+          <t>https://bit.ly/TataChallenge2026</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1491,17 +1527,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-06T18:29:52.586654+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Video Annotation Specialist</t>
+          <t>Direct Interview opportunity &amp; PPI</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Tata</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1510,14 +1546,10 @@
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://bit.ly/4ienwrP</t>
+          <t>https://bit.ly/TataChallenge2026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1529,67 +1561,67 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-06T18:29:50.197001+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Generalist</t>
+          <t>CRC Intern-Avacare</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Beijing, China</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://bit.ly/4A1zUSE</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/job/Beijing-China/CRC-Intern-_R1554392</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>R1554392</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-06T18:29:46.570284+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>AI Engineering Intern</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Anakin</t>
+          <t>Stack Binary</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Data / AI</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://docs.google.com/forms/d/e/1FAIpQLSePeI5SrB8J3suBCknPymGNWFzvp-0xVoLR4eW4umoYj2y-CA/viewform</t>
+          <t>https://stackbinary.io/careers/ai-engineering-intern</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1601,17 +1633,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-29T13:47:20.141291+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Engineering Intern</t>
+          <t>2027 - Summer Software Engineer Intern, Gurugram</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CoinDCX</t>
+          <t>Mdbgeneralreferrals</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1620,32 +1652,36 @@
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://bit.ly/4gaN1ry</t>
+          <t>https://job-boards.greenhouse.io/mdbgeneralreferrals/jobs/8127576</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>2027 - Summer Software Engineer Intern, Gurugram</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-29T13:47:17.751204+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Product Manager  (Internal Platform)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1654,66 +1690,74 @@
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://bit.ly/3SdzZBE</t>
+          <t>https://jobs.lever.co/meesho/2f1dba8f-bc99-4490-8200-d2cd7f92f544</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>Location - Bangalore About the Team : The Platform Product team at Meesho is the backbone of our product ecosystem, empowering functions across product, business, analytics, tech, and data science. By building scalable platforms and tools, we enable teams to make data-driven decisions, accelerate development cycles, and enhance productivity. Our key focus areas include Data Acquisition, Analytics Tools, Experimentation, Segmentation, Payouts, Security, Reporting and so on, which support critical functions of Meesho About the Role : As a Platform Product Manager, you will own and drive one or more product charters within the Platform Product charter. Your role will be pivotal in enabling Meesho’s growth by ensuring seamless cross-functional collaboration and delivering impactful technical solutions. You will work closely with product managers, engineers, analysts, and data scientists across the organisation to turn complex ideas into actionable products.We’re looking for strategic thinkers passionate about building platforms that solve large-scale challenges. We want to hear from you if you are a self-starter, excel in driving initiatives independently, and thrive in dynamic environ</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-29T13:47:14.843938+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tata Challenge 2026</t>
+          <t>财务实习生 Finance Intern</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tata</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Shanghai, China</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://bit.ly/TataChallenge2026</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/job/Shanghai-China/-Finance-Intern_R1565129</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>R1565129</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-29T13:47:11.897733+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tata Imagination Challenge</t>
+          <t>Generalist</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tata</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1722,10 +1766,14 @@
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://bit.ly/TataChallenge2026</t>
+          <t>https://bit.ly/4A1zUSE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1737,29 +1785,33 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-29T13:47:10.137948+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (Summer Internship)</t>
+          <t>Video Annotation Specialist</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://bit.ly/3SdzZBE</t>
+          <t>https://bit.ly/4ienwrP</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1771,71 +1823,67 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-29T13:47:07.044183+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Product Marketing Manager, International Markets &amp; Family Offices</t>
+          <t>Data Analyst Intern</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Addepar1</t>
+          <t>SWIFT</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Data / AI</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Remote, USA</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/addepar1/jobs/8744007002</t>
+          <t>https://goswift.keka.com/careers/jobdetails/153432</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Product Marketing Manager, International Markets &amp; Family Offices</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-29T13:47:01.689263+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AI Engineering Intern</t>
+          <t>SDE Intern</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Unisys</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Data / AI</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bangalore, KA, India</t>
+          <t>Bengaluru/Hyderabad/Delhi/Pune/Chennai</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://unisys.wd5.myworkdayjobs.com/External/job/Bangalore-KA-India/AI-Engineering-Intern_REQ574280?source=KrishanKumarLinkedin</t>
+          <t>https://www.amazon.jobs/en/jobs/10498161/systems-development-engineer-intern-2027</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1847,67 +1895,67 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-25T14:24:51.17624+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Product Operations Intern</t>
+          <t>AI/ML Intern</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fampay</t>
+          <t>FDM Digital Solutions</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Data / AI</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/fampay/e21b862f-cde6-4fb7-a08b-02c72f26ae99</t>
+          <t>https://fairdealmarket.keka.com/careers/jobdetails/159586</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>About Fam (previously FamPay) Fam is India’s first payments app for everyone above 11. FamApp helps make online and offline payments through UPI and FamCard. We are on a mission to raise a new, financially aware generation, and drive 250 million+ young users in India to kickstart their financial journey super early in their life. We’re reimagining how the next generation experiences fintech—going beyond payments to build a lifestyle brand that blends money, identity, and everyday experiences into one seamless, intuitive journey. Founded in 2019 by IIT Roorkee alumni, Fam is backed by some of the most respected investors around the world like Elevation Capital, Y-Combinator, Peak XV (Sequoia Capital) India, Venture Highway, Global Founder’s Capital and the likes of Kunal Shah, Amrish Rao as angel investors. About this role This role is operations heavy role with analytics as an added responsibility. You need to be comfortable executing campaigns relentlessly and working with data. You’ll be majorly working on Category Growth projects and Product Operations along with delivering high-quality outcomes in a fast-paced, dynamic environment. Understand that outcomes &gt; outputs</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-25T14:24:11.044632+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>AI/ML Engineering Intern</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Enterpret</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Data / AI</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Bengaluru, India</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/enterpret/jobs/7847134003</t>
+          <t>https://bit.ly/LinkedinHiringIntern</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1919,33 +1967,29 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-25T14:24:07.705529+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>SDE Intern</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Hiver</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Data / AI</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://bit.ly/45LFHxK</t>
+          <t>https://hiverhq.pinpointhq.com/postings/5380a35c-4644-4a46-bf6b-7ecb42e285dd</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1957,33 +2001,29 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-25T14:24:05.267553+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Data Science Intern</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Data / AI</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Bengaluru/Hyderabad/Delhi/Pune/Chennai</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.amazon.jobs/en/jobs/10506481/sde-i-intern-amazon-university-talent-acquisition</t>
+          <t>https://careers.geaerospace.com/global/en/job/GAOGAYGLOBALR5039463EXTERNALENGLOBAL/Data-Science-Intern</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -1995,55 +2035,55 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-25T14:23:37.191168+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MCP Expert</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>2 Locations</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://bit.ly/4wJiMOk</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/job/Bangalore-India/Intern_R1567860</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>R1567860</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-25T14:23:33.82492+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>China Clinical Intern</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2052,32 +2092,36 @@
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Chengdu, Sichuan, China</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://careers.hpe.com/us/en/job/1211844/Intern</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/job/Chengdu-Sichuan-China/China-Clinical-Intern_R1535126</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>R1535126</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-25T14:23:25.612917+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DevOps Engineering Intern</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fampay</t>
+          <t>GE Healthcare</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2086,36 +2130,32 @@
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/fampay/293a18f9-446a-437c-ba5d-d1300094b833</t>
+          <t>https://careers.gehealthcare.com/global/en/job/GEVGHLGLOBALR4043323EXTERNALENGLOBAL/Intern</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">About Fam (previously FamPay) Fam is India’s first payments app for everyone above 11. FamApp helps make online and offline payments through UPI and FamCard. We are on a mission to raise a new, financially aware generation, and drive 250 million+ young users in India to kickstart their financial journey super early in their life. We’re reimagining how the next generation experiences fintech—going beyond payments to build a lifestyle brand that blends money, identity, and everyday experiences into one seamless, intuitive journey. Founded in 2019 by IIT Roorkee alumni, Fam is backed by some of the most respected investors around the world like Elevation Capital, Y-Combinator, Peak XV (Sequoia Capital) India, Venture Highway, Global Founder’s Capital and the likes of Kunal Shah, Amrish Rao as angel investors. About this Role Always ready for with a Plan C because Plan A and B didn't work? We are looking for you! We’re looking for builders who enjoy creating things from scratch, breaking them, figuring out why they broke, and making them better. As a DevOps Engineer at FamApp, you’ll work at the intersection of infrastructure, reliability, and DevEx. You’ll help build the systems that </t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-25T14:22:34.800573+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DevOps Intern</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cloudsek</t>
+          <t>Iqvia</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2124,52 +2164,44 @@
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Bengaluru, Karnataka, India</t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/cloudsek/jobs/6149788004</t>
+          <t>https://jobs.iqvia.com/en/jobs/R1567860-1</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>DevOps Intern</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-25T14:22:23.10638+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://bit.ly/45nkUAn</t>
+          <t>https://jobs.ea.com/en_US/careers/JobDetail/Software-Engineer-Intern/216034?source=KrishanKumarLinkedin</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2181,33 +2213,29 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-25T14:22:21.002594+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Frontend Engineer</t>
+          <t>SDE Intern</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>NewSpace Tech</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://bit.ly/4qkLIuH</t>
+          <t>https://newspace.keka.com/careers/jobdetails/111933</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2219,12 +2247,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-25T14:22:16.887203+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Generalist</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2234,18 +2262,18 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote (Work From Home)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://bit.ly/4wZ8B9r</t>
+          <t>https://bit.ly/4A1zUSE</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2257,12 +2285,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-25T14:22:13.458112+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fullstack Developer</t>
+          <t>Video Annotation Specialist</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2272,18 +2300,18 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote (Work From Home)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://bit.ly/3Sy7PRO</t>
+          <t>https://bit.ly/4ienwrP</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2295,12 +2323,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-25T14:22:10.397388+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Generalist</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2316,12 +2344,12 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote (Work From Home)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://bit.ly/4gebHAv</t>
+          <t>https://bit.ly/4A1zUSE</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2333,33 +2361,33 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-22T12:33:35.076089+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Backend Intern</t>
+          <t>Video Annotation Specialist</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Smallcase</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote (Work From Home)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://app.pyjamahr.com/careers?company=smallcase&amp;job_id=256252&amp;company_uuid=2615584222</t>
+          <t>https://bit.ly/4ienwrP</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2371,29 +2399,33 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-22T12:33:32.004558+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Meritshot</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4454242112/</t>
+          <t>https://bit.ly/4gLwZpt</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2405,12 +2437,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-22T12:33:28.837146+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Frontend Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2420,18 +2452,18 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Remote (Work From Home)</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://bit.ly/4qkLIuH</t>
+          <t>https://bit.ly/4r2sHxt</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2443,12 +2475,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-22T12:33:26.419583+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Github Contributor</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2464,12 +2496,12 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Remote (Work From Home)</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://bit.ly/45nkUAn</t>
+          <t>https://bit.ly/3SwmNYL</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2481,12 +2513,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-22T12:33:20.104134+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AI Facial Data Collection Contributor</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2507,7 +2539,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://bit.ly/4gbo4vO</t>
+          <t>https://bit.ly/4gNZBP2</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2519,29 +2551,33 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-22T12:33:05.251094+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (Summer)</t>
+          <t>Creative &amp; Design Specialist</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.salesforce.com/company/careers/jobs/JR337715/summer-2027-intern-software-engineer/</t>
+          <t>https://bit.ly/4yvGfnM</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2553,33 +2589,29 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-22T12:33:03.503245+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Backend Java Developer</t>
+          <t>Information Technology Intern</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>MSD</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Remote (Work From Home)</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://bit.ly/4wRJpkA</t>
+          <t>https://jobs.msd.com/gb/en/job/MSD1GBR414761ENGB/Information-Technology-Intern</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2591,29 +2623,29 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-22T12:33:01.650538+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Data Analyst Intern</t>
+          <t>Energy Tech Hackathon</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SWIFT</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Data / AI</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://goswift.keka.com/careers/jobdetails/153432</t>
+          <t>https://bit.ly/EnergyTechHackathon</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2625,29 +2657,33 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-22T12:32:59.807222+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NXP Semiconductor Women in Tech</t>
+          <t>Technology Program Intern (Summer Internship 2027)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NXP Semiconductors</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Bengaluru/Hyderabad, India</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.nxp.com/company/about-nxp/events/women-in-tech:WOMEN-IN-TECH</t>
+          <t>https://bit.ly/WellsFargoIntern</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2659,17 +2695,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-22T12:32:56.748107+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>2027 - Summer Software Engineer Intern, Gurugram</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FRND</t>
+          <t>Mdbgeneralreferrals</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2678,32 +2714,36 @@
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4455599485/</t>
+          <t>https://job-boards.greenhouse.io/mdbgeneralreferrals/jobs/8127588</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>2027 - Summer Software Engineer Intern, Gurugram</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-22T12:32:54.751872+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>2027 - Summer Software Engineer Intern, Gurugram</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Harman</t>
+          <t>Mdbgeneralreferrals</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2712,146 +2752,150 @@
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://jobsearch.harman.com/en_US/careers/searchjobs/R-54623-2026</t>
+          <t>https://job-boards.greenhouse.io/mdbgeneralreferrals/jobs/7989869</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>2027 - Summer Software Engineer Intern, Gurugram</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-22T12:32:52.811769+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AI Facial Data Collection Contributor</t>
+          <t>2027 - Summer Software Engineer Intern, Gurugram</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Mdbgeneralreferrals</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Data / AI</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Remote (Work From Home)</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://bit.ly/4hl4Ar1</t>
+          <t>https://job-boards.greenhouse.io/mdbgeneralreferrals/jobs/8127585</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>2027 - Summer Software Engineer Intern, Gurugram</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-22T12:32:50.619505+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>2027 - Winter Software Engineer Intern, Gurugram</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Mdbgeneralreferrals</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Remote (Work From Home)</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://bit.ly/4hH3q9A</t>
+          <t>https://job-boards.greenhouse.io/mdbgeneralreferrals/jobs/8128091</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>2027 - Winter Software Engineer Intern, Gurugram</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-22T12:32:48.755864+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Software Engineer - AMTS</t>
+          <t>2027 - Winter Software Engineer Intern, Gurugram</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Mdbgeneralreferrals</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Hyderabad/Bangalore, India</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://bit.ly/4xGBIOS</t>
+          <t>https://job-boards.greenhouse.io/mdbgeneralreferrals/jobs/8127582</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>2027 - Winter Software Engineer Intern, Gurugram</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-22T12:32:46.368924+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>2027 - Winter Software Engineer Intern, Gurugram</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Joveo</t>
+          <t>Mdbgeneralreferrals</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2860,146 +2904,150 @@
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4453427249/</t>
+          <t>https://job-boards.greenhouse.io/mdbgeneralreferrals/jobs/7989832</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>2027 - Winter Software Engineer Intern, Gurugram</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-22T12:32:43.264285+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Fullstack Developer</t>
+          <t>VP, Technology Risk Management</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Remote (Work From Home)</t>
+          <t>O'Fallon, Missouri</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://bit.ly/3Sy7PRO</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/OFallon-Missouri/Vice-President--Technology-Risk-Management_R-290882</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>R-290882</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-22T12:32:40.571545+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Director, Product Management</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Remote (Work From Home)</t>
+          <t>3 Locations</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://bit.ly/4wZ8B9r</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Miami-Florida/Director--Product-Management_R-281337</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>R-281337</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-21T18:33:37.259219+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Intern - AI/ML</t>
+          <t>Manager – Global Small Business Product Pricing &amp; Interchange Solutions</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Towerresearchcapital</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Data / AI</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>gurgaon</t>
+          <t>Purchase, New York</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=8143756</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Purchase-New-York/Manager---Global-Small-Business-Product-Pricing---Interchange-Solutions_R-281793</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Intern - AI/ML</t>
+          <t>R-281793</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-21T18:33:33.878834+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Quantitative Developer Intern</t>
+          <t>Copy Intern</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Towerresearchcapital</t>
+          <t>Fampay</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3010,72 +3058,68 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=8138524</t>
+          <t>https://jobs.lever.co/fampay/23dd18f9-a331-4115-98e9-e98c404c47c6</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Quantitative Developer Intern</t>
+          <t>About Fam (previously FamPay) Fam is India’s first payments app for everyone above 11. FamApp helps make online and offline payments through UPI and FamCard. We are on a mission to raise a new, financially aware generation, and drive 250 million+ young users in India to kickstart their financial journey super early in their life. We’re reimagining how the next generation experiences fintech—going beyond payments to build a lifestyle brand that blends money, identity, and everyday experiences into one seamless, intuitive journey. Founded in 2019 by IIT Roorkee alumni, Fam is backed by some of the most respected investors around the world like Elevation Capital, Y-Combinator, Peak XV (Sequoia Capital) India, Venture Highway, Global Founder’s Capital and the likes of Kunal Shah, Amrish Rao as angel investors. About this Role You don't come across a company every day that puts content and communication on top of its priorities. We believe communication is the most powerful tool and can be a total game changer. With a product aimed at next generation, it's essential for us to reach our users in the form they actually want to consume, not the form we think sounds "professional." We're lo</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-21T18:33:29.313779+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sales &amp; Customer Success Intern - EU</t>
+          <t>Tata Challenge 2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Truecaller</t>
+          <t>Tata</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
+      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/truecaller/jobs/8138837</t>
+          <t>https://bit.ly/TataChallenge2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Sales &amp; Customer Success Intern - EU</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-14T03:46:04.307219+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Quantitative Research Internship - 6 Months, Central Execution Research</t>
+          <t>Software Engineering Intern (Summer)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Towerresearchcapital</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3086,144 +3130,148 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>India - Bangalore</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=8113986</t>
+          <t>https://salesforce.wd12.myworkdayjobs.com/en-US/External_Career_Site/job/India---Bangalore/Summer-2027-Intern---Software-Engineer_JR337715</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Quantitative Research Internship - 6 Months, Central Execution Research</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-10T17:40:51.724814+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>AI Engineer, Internship - Summer 2026 - Applications Open Now</t>
+          <t>Assistant Manager - Internal Audit</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Postman</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Data / AI</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Berkeley, California, United States; San Francisco, California, United States</t>
+          <t>Bengaluru-VTP, India</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/postman/jobs/7823417003</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4970739101</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>AI Engineer, Internship - Summer 2026 - Applications Open Now</t>
+          <t>Assistant Manager - Internal Audit</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-10T17:40:47.009978+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>[Backend] Software Engineering Intern</t>
+          <t>Coding Solver/ DSA Problem Solver/ Competitive Coder</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Enterpret</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bengaluru, Onsite</t>
+          <t>Remote (Work From Home)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/enterpret/jobs/7847134003</t>
+          <t>https://bit.ly/4xm5V56</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>[Backend] Software Engineering Intern</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-08-08T04:12:52.37725+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Brand Marketing Intern</t>
+          <t>Application Engineering Intern</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Earnin</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka, India</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/earnin/jobs/8113206</t>
+          <t>https://bit.ly/46Hc9St</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Brand Marketing Intern</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-08-08T04:12:50.084908+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Customer Success Intern</t>
+          <t>SDE Intern</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Knowbe4</t>
+          <t>Baxter</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3232,100 +3280,112 @@
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/knowbe4/jobs/8660687002</t>
+          <t>https://baxter.wd1.myworkdayjobs.com/en-US/baxter/job/Bangalore-Karnataka/Intern_JR-208532</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Customer Success Intern</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-08T04:12:46.851447+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Product Marketing Intern - Tetriz</t>
+          <t>Application Engineering Intern</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Epifi</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka, India</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/c6d070ce-d859-4d96-b82e-bca1fea37ddd</t>
+          <t>https://bit.ly/GoogleInternSummer27</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Product Marketing Intern - Tetriz</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-08-08T04:12:45.117452+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Junior Execution Trader Intern</t>
+          <t>Internal Events Marketing Manager</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Towerresearchcapital</t>
+          <t>Addepar1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=8091833</t>
+          <t>https://job-boards.greenhouse.io/addepar1/jobs/8799895002</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Junior Execution Trader Intern</t>
+          <t>Internal Events Marketing Manager</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:43.226773+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Copy Writer - Intern</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>Zeta</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3334,32 +3394,36 @@
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Bangalore - EC</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774341101</t>
+          <t>https://jobs.lever.co/zeta/72ee1884-8e8b-447b-ab96-aa76605b5f4a</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Copy Writer - Intern</t>
+          <t>Intern</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:36.983937+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Application Engineering Intern (Summer Internship 2027)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3368,712 +3432,796 @@
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka, India</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4771440101</t>
+          <t>https://bit.ly/GoogleInternSummer27</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:35.138664+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Internship - Content </t>
+          <t>2027 - Summer Internal Software Engineer Intern, Gurugram</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>Mdbgeneralreferrals</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4819749101</t>
+          <t>https://job-boards.greenhouse.io/mdbgeneralreferrals/jobs/8127570</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Internship - Content</t>
+          <t>2027 - Summer Internal Software Engineer Intern, Gurugram</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:33.590227+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Graphic Designer - Intern</t>
+          <t>Consulting Intern</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Mexico City, Mexico</t>
+        </is>
+      </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774342101</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/job/Mexico-City-Mexico/Intern_R1556962</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Graphic Designer - Intern</t>
+          <t>R1556962</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:31.543915+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Business Development Specialist (Outbound- International)</t>
+          <t>Director, Platform Engineering</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tide</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>O'Fallon, Missouri</t>
+        </is>
+      </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/tide/jobs/7081017003</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/OFallon-Missouri/Director--Platform-Engineering_R-273321</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Business Development Specialist (Outbound- International)</t>
+          <t>R-273321</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:28.879852+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Business Development Specialist (International Sales)</t>
+          <t>Senior Technical Program Manager</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tide</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Arlington, Virginia</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/tide/jobs/7598880003</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Arlington-Virginia/Senior-Technical-Program-Manager_R-282015</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Business Development Specialist (International Sales)</t>
+          <t>R-282015</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:17.721593+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Risk Intern - 6 Month Internship Opportunity</t>
+          <t>Lead, Product Experience Design</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Towerresearchcapital</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>O'Fallon, Missouri</t>
+        </is>
+      </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=7789933</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/OFallon-Missouri/Lead--Product-Experience-Design_R-280168</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Risk Intern - 6 Month Internship Opportunity</t>
+          <t>R-280168</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:10.248679+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Quantitative Trader Intern - Summer 2027</t>
+          <t>Director, Product Experience Design</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Towerresearchcapital</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>O'Fallon, Missouri</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=8024128</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/OFallon-Missouri/Director--Product-Experience-Design_R-280164</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Quantitative Trader Intern - Summer 2027</t>
+          <t>R-280164</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:07.980596+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Quantitative Trader Intern, PhD</t>
+          <t>Director, North American B2B Secular Shift Program Operations</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Towerresearchcapital</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Purchase, New York</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=8024138</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Purchase-New-York/Director--North-American-B2B-Secular-Shift-Program-Operations_R-281572</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Quantitative Trader Intern, PhD</t>
+          <t>R-281572</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:05.838281+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Quantitative Developer Intern - Summer 2027</t>
+          <t>Director, Project Management (AI)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Towerresearchcapital</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Data / AI</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2 Locations</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=8044334</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/OFallon-Missouri/Director--Project-Management_R-282004</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Quantitative Developer Intern - Summer 2027</t>
+          <t>R-282004</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:03.426202+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Business Analytics Intern - 6 Month Internship Opportunity</t>
+          <t>Senior Solutions Consultant, Personalization</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Towerresearchcapital</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Data / AI</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>3 Locations</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=8041512</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Sao-Paulo-Brazil/Senior-Solutions-Consultant--Personalization_R-275745</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Business Analytics Intern - 6 Month Internship Opportunity</t>
+          <t>R-275745</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:01.432263+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Sales Development Representative Intern (Hybrid)</t>
+          <t>Senior Counsel, Regulatory - Technology</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Knowbe4</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2 Locations</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/knowbe4/jobs/8566454002</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Purchase-New-York/Senior-Counsel--Regulatory---Technology_R-290617-2</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Sales Development Representative Intern (Hybrid)</t>
+          <t>R-290617</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-07-27T16:29:59.490728+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Sales Development Representative Intern (Hybrid)</t>
+          <t>Director, Finance Business Partner</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Knowbe4</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>3 Locations</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/knowbe4/jobs/8566457002</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Miami-Florida/Director--Finance-Business-Partner_R-281187</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Sales Development Representative Intern (Hybrid)</t>
+          <t>R-281187</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-07-27T16:29:55.183092+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Intern - Industrial Trainee</t>
+          <t>Manager, Authentication Product Management-2</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Inmobi</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Data / AI</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Warsaw, Poland</t>
+        </is>
+      </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/inmobi/jobs/8029868</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Warsaw-Poland/Manager--Authentication-Product-Management-2_R-290606</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Intern - Industrial Trainee</t>
+          <t>R-290606</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-07-27T16:29:52.581754+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Intern - Industrial Trainee</t>
+          <t>Consultant, Program Management, Advisors &amp; Consulting Service</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Inmobi</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Data / AI</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Sao Paulo, Brazil</t>
+        </is>
+      </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/inmobi/jobs/7793050</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Sao-Paulo-Brazil/Consultant--Program-Management--Advisors---Consulting-Service_R-276150</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Intern - Industrial Trainee</t>
+          <t>R-276150</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-07-27T16:29:48.780995+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Security Consultant Intern</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Cloudsek</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Data / AI</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>O'Fallon, Missouri</t>
+        </is>
+      </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/cloudsek/jobs/6115382004</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/OFallon-Missouri/Senior-Data-Engineer_R-288332-1</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Security Consultant Intern</t>
+          <t>R-288332</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-07-27T16:29:47.193044+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">SDE Intern - Frontend   </t>
+          <t>Senior Intelligence Analyst</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cloudsek</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Dubai, United Arab Emirates</t>
+        </is>
+      </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/cloudsek/jobs/5831215004</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Dubai-United-Arab-Emirates/Senior-Intelligence-Analyst_R-289820-1</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>SDE Intern - Frontend</t>
+          <t>R-289820</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-07-27T16:29:44.845632+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SDE - Backend - Intern</t>
+          <t>Manager, Specialist Sales, SME Solutions Northern Europe</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Cloudsek</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>6 Locations</t>
+        </is>
+      </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/cloudsek/jobs/5766402004</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Helsinki-Finland/Manager--Specialist-Sales--SME-Solutions-Northern-Europe_R-289760</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>SDE - Backend - Intern</t>
+          <t>R-289760</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-07-27T16:29:42.382537+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Business Development Representative Intern - Canada</t>
+          <t>Manager, Product Management - MDES Localization</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cloudsek</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2 Locations</t>
+        </is>
+      </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/cloudsek/jobs/6005469004</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/OFallon-Missouri/Manager--Product-Management---MDES-Localization_R-290229</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Business Development Representative Intern - Canada</t>
+          <t>R-290229</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-07-27T16:29:25.892883+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>DS/ML Intern</t>
+          <t>Senior Specialist, Product Development</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Epifi</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Data / AI</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Toronto, Canada (Ethoca)</t>
+        </is>
+      </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Toronto-Canada-Ethoca/Manager--Product-Development--Dispute-Product-_R-284467</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>A builder mindset is the core of this role and where you'll spend most of your time. But we're a small team building a whole product, not a research lab. The best person here treats ML systems as their primary craft while staying willing to do whatever the product needs — thinking through the product itself, shipping backend or frontend code, untangling data pipelines. We're looking for someone energized by the breadth, not someone who wants to stay in their lane. What you'll work on Evaluation systems for AI features Help build the eval backbone our AI features ship against — failure taxonomies, LLM-as-judge rubrics, golden datasets, calibration against human judgment. Learn what it takes to keep automated scores honest as models and prompts change. A feature with no eval has no quality floor. Model routing &amp; inference economics Get hands-on with how we route work across models — balancing cost, quality, and latency per task. Help run the experiments that justify those choices and catch regressions. Scoring, measurement &amp; signal quality Work on turning noisy, real-world signals into scores you can actually trust — grounded in real statistical rigor, not vibes. Help move heuristic-</t>
+          <t>R-284467</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-07-27T16:29:22.213288+00:00</t>
+          <t>2026-09-16T11:53:22.888535+00:00</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ai Engg Intern</t>
+          <t>Director Business Analysis</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Epifi</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Data / AI</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>O'Fallon, Missouri</t>
+        </is>
+      </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08c743e8-2b29-4f78-827e-5bd90476ed86</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/OFallon-Missouri/Director-Business-Analysis_R-288845-1</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Ai Engg Intern</t>
+          <t>R-288845</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-07-27T16:29:12.993097+00:00</t>
+          <t>2026-09-06T18:32:19.531425+00:00</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>[Tech Cooperative Internship 2026] Software Engineer in Back End intern (6 months)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Agoda</t>
+          <t>Mercor</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Fully Remote (Work From Home)</t>
+        </is>
+      </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/agoda/jobs/5443559</t>
+          <t>https://bit.ly/4fQS7dt</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>[Tech Cooperative Internship 2026] Software Engineer in Back End intern (6 months)</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-07-27T16:28:57.849831+00:00</t>
+          <t>2026-09-06T18:32:12.802999+00:00</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>International Payroll Partner</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Agoda</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4082,100 +4230,104 @@
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Bengaluru-VTP, India</t>
+        </is>
+      </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/agoda/jobs/8063978</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>International Payroll Partner</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-07-27T16:28:36.025672+00:00</t>
+          <t>2026-09-06T18:32:12.088231+00:00</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GenAI Product Builder Intern</t>
+          <t>Ecologic Hackathon</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Epifi</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Data / AI</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/4f5b7548-ea0a-4be0-816b-11d712853169</t>
+          <t>https://bit.ly/EcoLogicHackathon</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>GenAI Product Builder Intern About us Tetriz is an AI Engineering Intelligence platform that helps engineering organizations become AI-native, faster. We measure how AI coding tools like Cursor, Claude Code, and GitHub Copilot are actually used, improve engineer effectiveness through prompt and workflow coaching, and help engineering leaders demonstrate AI ROI with board-ready, defensible insights. Who should apply This is not a general internship, you should apply only if: - You’ve built or designed things outside of college - You have a portfolio / GitHub of real work - Your work shows initiative, not just completion - You care about problems, not just tools If your experience is mostly coursework, this won’t be a fit. What you’ll get - Work on a real AI product used by engineering teams - Own problems end-to-end, not assist someone else - Exposure to cutting-edge GenAI workflows - A steep learning curve — we’ll push you hard and help you grow fast If you’re hungry and serious, you’ll leave this internship 10x better and ready for the AI-first world. What you’ll do - Build features end-to-end — from idea to production - Work with LLMs, APIs, and internal systems - Create tools th</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-07-27T10:49:04.274532+00:00</t>
+          <t>2026-09-06T18:32:11.785346+00:00</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Copy Writer - Intern</t>
+          <t>Generalist</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774341101</t>
+          <t>https://bit.ly/4A1zUSE</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Copy Writer - Intern</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-07-27T10:49:00.838626+00:00</t>
+          <t>2026-09-06T18:32:09.855425+00:00</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4187,92 +4339,92 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4771440101</t>
+          <t>https://hccz.fa.em3.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_2/job/25450</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-07-27T10:48:58.630946+00:00</t>
+          <t>2026-09-06T18:32:09.765669+00:00</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Internship - Content </t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4819749101</t>
+          <t>https://careers.cargill.com/en/job/-/-/23251/100079360032</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Internship - Content</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-07-27T10:48:56.06648+00:00</t>
+          <t>2026-09-06T18:32:08.510234+00:00</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Graphic Designer - Intern</t>
+          <t>SDE Intern</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>Spyne</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774342101</t>
+          <t>https://spyneai.keka.com/careers/jobdetails/156605</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Graphic Designer - Intern</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-07-27T10:42:53.996409+00:00</t>
+          <t>2026-09-06T18:32:08.206959+00:00</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Copy Writer - Intern</t>
+          <t>YouTube &amp; Content - Internship</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4282,176 +4434,192 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Bengaluru-VTP, India</t>
+        </is>
+      </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774341101</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Copy Writer - Intern</t>
+          <t>YouTube &amp; Content - Internship</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-07-27T10:42:50.938109+00:00</t>
+          <t>2026-09-06T18:30:59.524083+00:00</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Graphic Designer - Intern</t>
+          <t>Frontend Engineer</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774342101</t>
+          <t>https://bit.ly/4i9Esjd</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Graphic Designer - Intern</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-07-27T10:42:47.32783+00:00</t>
+          <t>2026-09-06T18:30:57.840717+00:00</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Internship - Content </t>
+          <t>Visual Designer</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4819749101</t>
+          <t>https://bit.ly/4ye7bbp</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Internship - Content</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-07-27T10:42:43.192382+00:00</t>
+          <t>2026-09-06T18:30:56.243151+00:00</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>UX Designer</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4771440101</t>
+          <t>https://bit.ly/4wWLfQV</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-07-26T19:14:17.297621+00:00</t>
+          <t>2026-09-06T18:30:54.557526+00:00</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ReactJS Internship</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ElevateHQ</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Frontend</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>₹240000 - ₹420000</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr"/>
+          <t>Data / AI</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/4794473734?utm_medium=api&amp;utm_source=e044e1cb</t>
+          <t>https://bit.ly/3Usl5bu</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Position Overview: We are seeking a talented and motivated ReactJS Intern to join our team for a 6-month full-time internship. This is a fantastic opportunity for someone with prior internship experience to deepen their knowledge and skills in ReactJS while working on cutting-edge projects. Responsibilities: Collaborate with the development team to design, develop, and maintain web applications using ReactJS. Write clean, maintainable, and efficient code. Participate in code reviews and contrib…</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-07-26T19:14:13.725695+00:00</t>
+          <t>2026-09-06T18:30:51.717612+00:00</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Developer Internship</t>
+          <t>Quantitative Developer Intern</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>PBL India</t>
+          <t>Towerresearchcapital</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4460,168 +4628,184 @@
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/4801600698?utm_medium=api&amp;utm_source=e044e1cb</t>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=7011493</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Percpktika Brand Lab is a Product Development startup which supports and develops products guiding social innovation. We are looking for smart and talented interns who are capable of working from Delhi or remote and submitting results. At PBL we have an efficient training process which provides resources to grow and nurture your talent. The selected intern(s) will work on following during the internship: 1. Code Reviews and Research. 2. Creating Core features using Node.js and Native Script sup…</t>
+          <t>Quantitative Developer Intern</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-07-26T19:14:07.63634+00:00</t>
+          <t>2026-09-06T18:30:49.789951+00:00</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Design Internship</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>PBL India</t>
+          <t>Proctor &amp; Gamble</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/4801437257?utm_medium=api&amp;utm_source=e044e1cb</t>
+          <t>https://www.pgcareers.com/global/en/job/R000158265/Information-Technology-Intern</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Percpktika Brand Lab is a Product Development startup which supports and develops products guiding social innovation. We are looking for smart and talented interns who are capable of working from Delhi or remote and submitting results. At PBL we have an efficient training process which provides resources to grow and nurture your talent. The selected intern(s) will work on following during the internship: 1. Designing User Interface. 2. Experience planning and flow. 3. Product Branding and Desig…</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-07-26T19:13:19.489348+00:00</t>
+          <t>2026-09-06T18:30:47.137206+00:00</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Customer Care Intern</t>
+          <t>Product Designer</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Criteo</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5790410523?se=rFvE0iWJ8RGGXqQIyNVN5Q&amp;utm_medium=api&amp;utm_source=e044e1cb&amp;v=5E72C4726A0DF728D03FF51102E0532CA986DDEA</t>
+          <t>https://bit.ly/4xuqIEp</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>This job is with Criteo, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. What You'll Do: The multinational Global Customer Care Team is the first point of contact for Criteo Customers; our goal is to provide excellent customer support to all incoming client requests using email or live chat. We excel at collaboration, communication, and teamwork, as they are key to solving our client's re…</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-07-26T19:13:17.765892+00:00</t>
+          <t>2026-09-06T18:30:45.345284+00:00</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Sales &amp; Strategy Intern</t>
+          <t>SDE1</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Criteo</t>
+          <t>Hevo Data</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5806276940?se=rFvE0iWJ8RGGXqQIyNVN5Q&amp;utm_medium=api&amp;utm_source=e044e1cb&amp;v=B2147145725F724ABD3B0362E330EB1DD5EB962B</t>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSdUXEWZMGd9k4A_Thkhl_tya1Zcu5ROnWP9SjMKhHSQzKUGog/viewform</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>This job is with Criteo, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. What You'll Do: As a Sales &amp; Strategy Intern, you will be part of our India team that works with new and existing clients. You will be learning and working with brands, analyzing and optimizing campaigns, along with cultivating a strong and productive relationship with clients. This is a 12-month paid, full-time inte…</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-07-26T18:23:56.921677+00:00</t>
+          <t>2026-09-06T18:30:42.493975+00:00</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>GRAPHIC DESIGNER</t>
+          <t>Quantitative Trader/Researcher Summer Internship 2027 (2028 Graduates)</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>NEW VINE LIMITED</t>
+          <t>Towerresearchcapital</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-graphic-designer-new-vine-limited-1135316</t>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=8037860</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Graphic Designer (part-time) An exciting opportunity has arisen for a Graphic Designer (part-time) to join us, working remotely with great benefits. The role will work primarily on our books, subscription materials, and digital resources, creating eye-catching covers, inside layouts, and ebooks. Prior experience of working on these types of resources in Adobe Creative Suite is essential, as is a solid understanding of design, layout, typography, and brand. Salary: Â£16,500 (Â£27,500 FTE) Applications close: 29 August 2026 Download the job information (.pdf) Download the application form (.docx) We welcome applicants from all backgrounds and communities, in particular those that are currently under-represented within our staff team. This includes, but is not limited to, people from Black, Asian, and other ethnic groups, especially within our leadership roles. Please mention the word **PROLIFIC** and tag RMjAyLjY2LjE2NC42 when applying to show you read the job post completely (#RMjAyLjY2LjE2NC42). This is a beta feature to avoid spam applicants. Companies can search these words to find applicants that read this and see they're human.</t>
+          <t>Quantitative Trader/Researcher Summer Internship 2027 (2028 Graduates)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-07-26T18:23:39.597545+00:00</t>
+          <t>2026-09-06T18:30:39.619912+00:00</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Executive Assistant</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ritual AdsÂ®</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -4630,202 +4814,218 @@
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Remote (Work From Home)</t>
+        </is>
+      </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-executive-assistant-ritual-adsr-1135344</t>
+          <t>https://bit.ly/4guHNbm</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Company Description Ritual AdsÂ® is a cutting-edge AI software company that uses generative AI to create tailored, data-driven advertising content on demand. The platform helps organizations quickly produce high-impact, customized ads that align with their brand and audience. By combining advanced machine learning with real-time data, Ritual AdsÂ® aims to improve campaign performance and efficiency. Team members collaborate in a technology-forward environment focused on innovation, scalability, and measurable results. Role Description The Executive Assistant at Ritual AdsÂ® is a full-time, remote role responsible for providing comprehensive administrative and organizational support to company leadership. Day-to-day tasks include managing calendars, scheduling meetings, coordinating travel, and preparing agendas and meeting materials. The Executive Assistant will handle expense reports, track reimbursements, and maintain accurate documentation. The role also includes managing correspondence, drafting and editing communications, organizing digital files, and supporting special projects and operational tasks to ensure smooth executive workflows. Qualifications Strong Executive Adminis</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-07-26T18:23:35.307873+00:00</t>
+          <t>2026-09-06T18:30:37.644164+00:00</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Product Designer</t>
+          <t>AI Fullstack Engineer Intern</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Flint</t>
+          <t>Gesture</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-product-designer-flint-1135340</t>
+          <t>https://jobs.gusto.com/postings/gesture-us-inc-ai-full-stack-engineer-intern-e6b31003-155a-48dd-a442-a664809ff969</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Compensation: $160kâ190k base + meaningful equity About Flint The best education anyone has ever received is one person paying close attention to one student: moving at their pace, noticing what they missed, asking the next question at the right moment. But the current system is built around a compromise with one teacher managing thirty students. Flint exists to take that compromise off the table. Personalized learning, at the scale of a whole school â every student working with something closer to a tutor, and every teacher able to see what's actually happening across their class instead of guessing. Go look at the product before you read any further: app.flintk12.com The Role Students want something that stays with them, going at their pace and helps them get unstuck without just handing over the answer. Teachers want that happening inside a class they still control, and they'd like their evenings back. Admins want proof that the platform they rolled out is leading to teacher productivity and student progress. Your job is to dive deep into this design problem, holding three sets of needs within one product. Weâll trust you to ship designs that are the best possible solution</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-07-26T18:23:18.030686+00:00</t>
+          <t>2026-09-06T18:30:34.590215+00:00</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Join our UK team</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Workdry Germany</t>
+          <t>Joveo</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-join-our-uk-team-workdry-germany-1135314</t>
+          <t>https://www.linkedin.com/jobs/view/4458863278/</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>BracknellPump Rental SolutionsBracknellPump Rental SolutionsGreat YarmouthPump Rental SolutionsNottinghamPump Rental SolutionsAberdeenPump Rental SolutionsConwyPump Rental SolutionsStokeWorkdry - Group Central ServicesStokeWorkdry - Group Central ServicesWorkingtonPump Rental Solutions Please mention the word **GREATNESS** and tag RMjAyLjY2LjE2NC42 when applying to show you read the job post completely (#RMjAyLjY2LjE2NC42). This is a beta feature to avoid spam applicants. Companies can search these words to find applicants that read this and see they're human.</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-07-26T18:23:11.834056+00:00</t>
+          <t>2026-09-06T18:30:32.212932+00:00</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Safety Data Analyst</t>
+          <t>Quantitative Researcher Intern, Bachelor or Master</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SkyWest Airlines</t>
+          <t>Towerresearchcapital</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Data / AI</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Singapore, Hong Kong, Shanghai, Sydney</t>
+        </is>
+      </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-safety-data-analyst-skywest-airlines-1135445</t>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=8168750</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>About SkyWest With over 16,000 aviation professionals operating thousands of daily flights, SkyWest Airlines connects millions of passengers each month to hundreds of destinations across North America. SkyWest operates in partnership with Delta Air Lines, United Airlines, American Airlines, and Alaska Airlines and has a fleet of nearly 450 aircraft. Headquartered in St. George, Utah, SkyWest's industry-leading workforce and excellent leadership team have consistently generated solid operational and economic performance, setting the standard for excellence in the regional industry. SkyWest employees enjoy a distinctive and unmatched culture of teamwork, respect, quality, and professionalism, along with world-class benefits such as a 401(k) match, Performance Rewards, health care, retirement, and discounted travel worldwide. Primary Job Duties Analyze, compile, and report safety data to support all SkyWest safety programs. Collect, analyze, and report safety assurance data from multiple safety data sources. Identify, monitor, and communicate safety performance trends and emerging risks. Track, maintain, and report key performance indicators (KPIs) for the Safety Department, including</t>
+          <t>Quantitative Researcher Intern, Bachelor or Master</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-07-26T18:22:46.777033+00:00</t>
+          <t>2026-09-06T18:30:29.806106+00:00</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Engineering Manager - Edge AI</t>
+          <t>Quantitative Researcher Intern, PhD or Postdoc</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SumUp</t>
+          <t>Towerresearchcapital</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Data / AI</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Singapore, Hong Kong, Shanghai, Sydney</t>
+        </is>
+      </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/sumup/engineering-manager-edge-ai-berlin-258996</t>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=8168634</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Our AI Platform &amp;amp; Edge team sits at the heart of how SumUp is scaling intelligent, merchant-facing experiences across millions of interactions. We build and operate the AI systems — from LLM-powered assistants to agentic platforms — that directly shape how merchants get support, resolve issues, and engage with SumUp's products. As Engineering Manager for Edge, you'll take ownership of a growing, cross-functional team of engineers and ML specialists, leading the execution of some of our most technically complex and commercially critical AI initiatives. This is a rare opportunity to lead meaningful AI work at scale — not just shipping features, but shaping how an entire platform evolves. What you'll do Lead the day-to-day execution of the Edge AI team, translating long-term product vision into clear sprint roadmaps and measurable delivery milestones Own the migration of our AI assistant to an autonomous agentic setup, maintaining performance while expanding AI support across all merchant-facing channels Set the technical direction for LLM-powered system design, making clear tradeoffs across quality, latency, and cost Build a data-informed engineering culture by defining performan</t>
+          <t>Quantitative Researcher Intern, PhD or Postdoc</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-07-26T18:22:37.744444+00:00</t>
+          <t>2026-09-06T18:30:26.26421+00:00</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Chief Marketing Officer (m/w/d)</t>
+          <t>Ecologic Hackathon</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>InkuPlay UG (haftungsbeschränkt)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/inkuplay-ug-haftungsbeschrankt/chief-marketing-officer-biesenthal-255944</t>
+          <t>https://bit.ly/EcoLogicHackathon</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>InkuPlay ist ein wachstumsorientiertes Unternehmen aus dem Gaming- und E-Sports-Umfeld. Wir entwickeln Marken, Communities, digitale Formate und Partnerschaften an der Schnittstelle von Gaming, Entertainment, Content, Creator Economy und E-Sports. Unser Ziel ist es, InkuPlay als moderne, international relevante Gaming- und E-Sports-Marke zu etablieren. Dafür suchen wir eine unternehmerisch denkende Führungspersönlichkeit, die unsere Marketingstrategie entwickelt, unsere Markenpositionierung schärft und nachhaltiges Wachstum vorantreibt. Als Chief Marketing Officer (m/w/d) übernimmst du die Gesamtverantwortung für Marketing, Marke, Kommunikation und Wachstum bei InkuPlay. Du entwickelst nicht nur Kampagnen, sondern baust gemeinsam mit der Geschäftsführung eine belastbare Marketingorganisation auf. Dabei verbindest du strategische Markenführung mit datengetriebenem Growth Marketing, aufmerksamkeitsstarkem Content und kommerziell erfolgreichen Partnerschaften. Du berichtest direkt an den Founder &amp;#x26; CEO und arbeitest eng mit den Bereichen Esports, Content &amp;#x26; Media, Partnerships, Sales, Community, Recruiting und Business Development zusammen. Aufgaben Marketing- und Unternehmens</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-07-26T18:22:34.380054+00:00</t>
+          <t>2026-09-06T18:30:23.45402+00:00</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Head of People &amp; Culture / HR (m/w/d)</t>
+          <t>Tata Imagination Challenge</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>InkuPlay UG (haftungsbeschränkt)</t>
+          <t>Tata</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -4837,150 +5037,3652 @@
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/inkuplay-ug-haftungsbeschrankt/head-of-people-culture-hr-biesenthal-163623</t>
+          <t>https://bit.ly/TataChallenge2026</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">InkuPlay ist ein wachsendes Unternehmen aus den Bereichen Gaming, Esports, digitale Plattformen, Content, Community und Partnerschaften. Wir befinden uns in einer Phase des strukturellen Aufbaus und der Professionalisierung. Dafür suchen wir eine erfahrene Persönlichkeit, die unsere Personalorganisation nicht nur verwaltet, sondern aktiv gestaltet. Als Head of People &amp;#x26; Culture / HR übernimmst du die Verantwortung für den Aufbau moderner, rechtssicherer und skalierbarer Personalstrukturen. Du arbeitest eng mit dem Founder &amp;#x26; CEO, dem operativen Management, den Führungskräften sowie externen arbeitsrechtlichen und steuerlichen Beratern zusammen. Die Position verbindet strategische Personalarbeit mit operativer Umsetzung. Gesucht wird daher keine rein beratende HR-Funktion, sondern eine Person, die Verantwortung übernimmt, Entscheidungen vorbereitet, Prozesse etabliert und Themen zuverlässig bis zum Abschluss begleitet. Deine Rolle Als Head of People &amp;#x26; Culture / HR verantwortest du sämtliche personalbezogenen Themen bei InkuPlay. Du entwickelst eine professionelle HR-Struktur, die zu einem dynamischen Startup im Gaming- und Esports-Umfeld passt. Dabei stellst du sicher, </t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-07-26T18:22:32.624515+00:00</t>
+          <t>2026-09-06T18:30:10.428183+00:00</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Praktikum Amazon PPC &amp; Performance Marketing im E-Commerce Start-up (m/w/d)</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Sayano Deutschland GmbH</t>
+          <t>Weekday works</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/sayano-deutschland-gmbh/praktikum-amazon-ppc-performance-marketing-im-e-commerce-start-up-stuttgart-189082</t>
+          <t>https://jobs.lever.co/weekdayworks/a86efff4-1c2e-43fc-8ecb-dc8f873db2f1</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Du willst mitgestalten statt nur zuschauen? Dann bist Du bei uns richtig. Wir sind Sayano – ein modernes, international tätiges E-Commerce-Unternehmen hinter Marken wie MIAMIO, Tortillada und Calmado. Unsere Produkte erreichen Kundinnen und Kunden in mehr als 80 Ländern. Die Financial Times hat uns vier Jahre in Folge als eines der am schnellsten wachsenden Unternehmen Europas ausgezeichnet. Wir arbeiten schnell, datengetrieben und konsequent mit modernen KI-Technologien. KI ist für uns kein Zukunftsthema, sondern fester Bestandteil unseres Arbeitsalltags – von Analysen und Recherchen über Automatisierungen bis zur Optimierung unserer Werbekampagnen. Aufgaben Du unterstützt bei der Analyse und Optimierung unserer Amazon-PPC-Kampagnen Du arbeitest mit Sponsored Products, Sponsored Brands und Sponsored Display Du führst Keyword-, Suchbegriff- und Wettbewerbsanalysen durch Du identifizierst profitable Suchbegriffe und entwickelst diese gemeinsam mit uns weiter Du hilfst dabei, unnötige Werbeausgaben zu erkennen und zu reduzieren Du unterstützt bei der Optimierung von Geboten, Budgets, Platzierungen und negativen Keywords Du analysierst Kennzahlen wie ACOS, TACOS, ROAS, CPC, CTR und Co</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-07-26T18:22:28.361273+00:00</t>
+          <t>2026-09-06T18:30:07.464823+00:00</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Brand &amp; Content Lead</t>
+          <t>Ecologic Hackathon</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Klar</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/klar/brand-content-lead-munich-463374</t>
+          <t>https://bit.ly/EcoLogicHackathon</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>In Short: We are looking for someone that loves content and eCommerce to own our entire brand surface — content, community, product marketing, and website — and turn Klar into the go-to resource for actionable eCom knowledge in Europe. About Klar 🚀 The Mission Klar is the Data Operating System for growing eCommerce companies, meaning no more spreadsheets . We integrate with all of a brand's data sources to provide a holistic understanding of their business, offering detailed insights on how to accelerate growth and increase profitability. 🛍️ The Reach We are already the "single source of truth" for over 1,000 leading eCom brands. Market leaders like Sunday Natural, Loop Earplugs, Holy, Maniko, and Armed Angels use Klar to make better decisions every single day. 🤝 The Backstory We deeply empathize with our customers because we were our customers. The founders (who met in South Africa working for Zando) spent the last 10 years in e-commerce. We know the pain of running these businesses, and we built Klar specifically to solve it. ✨ The Principle Our guiding principle is Do Work You Are Proud Of . We emphasize long-term quality over short-term results. We evaluate our tools and dec</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-07-26T18:22:23.542927+00:00</t>
+          <t>2026-09-06T18:29:59.581469+00:00</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Kreativer Allrounder Marketing (m/w/d) | Gestalte unseren Markenauftritt aktiv</t>
+          <t>Fullstack Developer Intern</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Autohaus Wernsing GmbH</t>
+          <t>Amber</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.arbeitnow.com/jobs/companies/autohaus-wernsing-gmbh/kreativer-allrounder-marketing-gestalte-unseren-markenauftritt-aktiv-bersenbruck-288838</t>
+          <t>https://amberstudent.keka.com/careers/jobdetails/140686</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Werde kreativ. Mach unsere Marken sichtbar. Du hast Freude an Social Media, Content Creation und kreativem Marketing? Du möchtest nicht einfach nur bestehende Aufgaben abarbeiten, sondern einen Marketingbereich aktiv mitgestalten und weiterentwickeln? Dann bist du bei uns genau richtig! Für unsere Unternehmen Autohaus Wernsing und 2Rad Wernsing suchen wir eine kreative und engagierte Persönlichkeit, die unseren Außenauftritt eigenverantwortlich weiterentwickelt und gemeinsam mit der Geschäftsführung den Marketingbereich aufbaut. Du arbeitest auf Basis unseres bestehenden Markenbooks mit klar definiertem Corporate Design und hast gleichzeitig viel Freiraum für eigene Ideen und kreative Konzepte. Der Schwerpunkt deiner Tätigkeit liegt eindeutig im Marketing. Ein kleiner Teil deiner Arbeitszeit unterstützt unser Team bei Veranstaltungen oder vertriebsnahen Projekten. Ob in Teilzeit oder auf geringfügiger Basis – wir sind flexibel. Ein Teil deiner Arbeit kann nach Absprache auch im Homeoffice erledigt werden. Aufgaben Marketing &amp;#x26; Content Creation Eigenverantwortlicher Aufbau und Weiterentwicklung unseres Marketingbereichs in enger Abstimmung mit der Geschäftsführung Planung, Erste</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
+          <t>2026-09-06T18:29:55.077161+00:00</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Video Annotation Specialist</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>micro1</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://bit.ly/4ienwrP</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-09-06T18:29:52.586654+00:00</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Video Annotation Specialist</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>micro1</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://bit.ly/4ienwrP</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09-06T18:29:50.197001+00:00</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Generalist</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>micro1</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://bit.ly/4A1zUSE</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-06T18:29:46.570284+00:00</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Anakin</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSePeI5SrB8J3suBCknPymGNWFzvp-0xVoLR4eW4umoYj2y-CA/viewform</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-08-29T13:47:20.141291+00:00</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Engineering Intern</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>CoinDCX</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://bit.ly/4gaN1ry</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-08-29T13:47:17.751204+00:00</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://bit.ly/3SdzZBE</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-08-29T13:47:14.843938+00:00</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Tata Challenge 2026</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Tata</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://bit.ly/TataChallenge2026</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-08-29T13:47:11.897733+00:00</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Tata Imagination Challenge</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Tata</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://bit.ly/TataChallenge2026</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-08-29T13:47:10.137948+00:00</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern (Summer Internship)</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://bit.ly/3SdzZBE</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-08-29T13:47:07.044183+00:00</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Product Marketing Manager, International Markets &amp; Family Offices</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Addepar1</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Remote, USA</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/addepar1/jobs/8744007002</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Product Marketing Manager, International Markets &amp; Family Offices</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-08-29T13:47:01.689263+00:00</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>AI Engineering Intern</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Unisys</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Data / AI</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Bangalore, KA, India</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://unisys.wd5.myworkdayjobs.com/External/job/Bangalore-KA-India/AI-Engineering-Intern_REQ574280?source=KrishanKumarLinkedin</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-08-25T14:24:51.17624+00:00</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Product Operations Intern</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Fampay</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/fampay/e21b862f-cde6-4fb7-a08b-02c72f26ae99</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>About Fam (previously FamPay) Fam is India’s first payments app for everyone above 11. FamApp helps make online and offline payments through UPI and FamCard. We are on a mission to raise a new, financially aware generation, and drive 250 million+ young users in India to kickstart their financial journey super early in their life. We’re reimagining how the next generation experiences fintech—going beyond payments to build a lifestyle brand that blends money, identity, and everyday experiences into one seamless, intuitive journey. Founded in 2019 by IIT Roorkee alumni, Fam is backed by some of the most respected investors around the world like Elevation Capital, Y-Combinator, Peak XV (Sequoia Capital) India, Venture Highway, Global Founder’s Capital and the likes of Kunal Shah, Amrish Rao as angel investors. About this role This role is operations heavy role with analytics as an added responsibility. You need to be comfortable executing campaigns relentlessly and working with data. You’ll be majorly working on Category Growth projects and Product Operations along with delivering high-quality outcomes in a fast-paced, dynamic environment. Understand that outcomes &gt; outputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-08-25T14:24:11.044632+00:00</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Enterpret</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/enterpret/jobs/7847134003</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-08-25T14:24:07.705529+00:00</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>micro1</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Data / AI</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://bit.ly/45LFHxK</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-08-25T14:24:05.267553+00:00</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Bengaluru/Hyderabad/Delhi/Pune/Chennai</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.amazon.jobs/en/jobs/10506481/sde-i-intern-amazon-university-talent-acquisition</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-08-25T14:23:37.191168+00:00</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>MCP Expert</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>micro1</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://bit.ly/4wJiMOk</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-08-25T14:23:33.82492+00:00</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>HPE</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://careers.hpe.com/us/en/job/1211844/Intern</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-08-25T14:23:25.612917+00:00</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>DevOps Engineering Intern</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Fampay</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/fampay/293a18f9-446a-437c-ba5d-d1300094b833</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">About Fam (previously FamPay) Fam is India’s first payments app for everyone above 11. FamApp helps make online and offline payments through UPI and FamCard. We are on a mission to raise a new, financially aware generation, and drive 250 million+ young users in India to kickstart their financial journey super early in their life. We’re reimagining how the next generation experiences fintech—going beyond payments to build a lifestyle brand that blends money, identity, and everyday experiences into one seamless, intuitive journey. Founded in 2019 by IIT Roorkee alumni, Fam is backed by some of the most respected investors around the world like Elevation Capital, Y-Combinator, Peak XV (Sequoia Capital) India, Venture Highway, Global Founder’s Capital and the likes of Kunal Shah, Amrish Rao as angel investors. About this Role Always ready for with a Plan C because Plan A and B didn't work? We are looking for you! We’re looking for builders who enjoy creating things from scratch, breaking them, figuring out why they broke, and making them better. As a DevOps Engineer at FamApp, you’ll work at the intersection of infrastructure, reliability, and DevEx. You’ll help build the systems that </t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-08-25T14:22:34.800573+00:00</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>DevOps Intern</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Cloudsek</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka, India</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/cloudsek/jobs/6149788004</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>DevOps Intern</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-08-25T14:22:23.10638+00:00</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>micro1</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://bit.ly/45nkUAn</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-08-25T14:22:21.002594+00:00</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Frontend Engineer</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>micro1</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://bit.ly/4qkLIuH</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-08-25T14:22:16.887203+00:00</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Backend Engineer</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>micro1</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://bit.ly/4wZ8B9r</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-08-25T14:22:13.458112+00:00</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Fullstack Developer</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>micro1</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Full Stack</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://bit.ly/3Sy7PRO</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-08-25T14:22:10.397388+00:00</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>micro1</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://bit.ly/4gebHAv</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-08-22T12:33:35.076089+00:00</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Backend Intern</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Smallcase</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://app.pyjamahr.com/careers?company=smallcase&amp;job_id=256252&amp;company_uuid=2615584222</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-08-22T12:33:32.004558+00:00</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Meritshot</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4454242112/</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-08-22T12:33:28.837146+00:00</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Frontend Engineer</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>micro1</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Remote (Work From Home)</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://bit.ly/4qkLIuH</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-08-22T12:33:26.419583+00:00</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>micro1</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Remote (Work From Home)</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://bit.ly/45nkUAn</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-08-22T12:33:20.104134+00:00</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>AI Facial Data Collection Contributor</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>micro1</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Data / AI</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://bit.ly/4gbo4vO</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-08-22T12:33:05.251094+00:00</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern (Summer)</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.salesforce.com/company/careers/jobs/JR337715/summer-2027-intern-software-engineer/</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-08-22T12:33:03.503245+00:00</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Backend Java Developer</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>micro1</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Remote (Work From Home)</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://bit.ly/4wRJpkA</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-08-22T12:33:01.650538+00:00</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Data Analyst Intern</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>SWIFT</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Data / AI</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://goswift.keka.com/careers/jobdetails/153432</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-08-22T12:32:59.807222+00:00</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>NXP Semiconductor Women in Tech</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>NXP Semiconductors</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.nxp.com/company/about-nxp/events/women-in-tech:WOMEN-IN-TECH</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-08-22T12:32:56.748107+00:00</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>FRND</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4455599485/</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-08-22T12:32:54.751872+00:00</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Harman</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://jobsearch.harman.com/en_US/careers/searchjobs/R-54623-2026</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-08-22T12:32:52.811769+00:00</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>AI Facial Data Collection Contributor</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>micro1</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Data / AI</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Remote (Work From Home)</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://bit.ly/4hl4Ar1</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-08-22T12:32:50.619505+00:00</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>micro1</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Remote (Work From Home)</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://bit.ly/4hH3q9A</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-08-22T12:32:48.755864+00:00</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Software Engineer - AMTS</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Hyderabad/Bangalore, India</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://bit.ly/4xGBIOS</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-08-22T12:32:46.368924+00:00</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Software Engineering Intern</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Joveo</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4453427249/</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-08-22T12:32:43.264285+00:00</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Fullstack Developer</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>micro1</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Full Stack</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Remote (Work From Home)</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://bit.ly/3Sy7PRO</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-08-22T12:32:40.571545+00:00</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Backend Engineer</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>micro1</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Remote (Work From Home)</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://bit.ly/4wZ8B9r</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-08-21T18:33:37.259219+00:00</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Intern - AI/ML</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Towerresearchcapital</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Data / AI</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>gurgaon</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=8143756</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Intern - AI/ML</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-08-21T18:33:33.878834+00:00</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Quantitative Developer Intern</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Towerresearchcapital</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=8138524</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Quantitative Developer Intern</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-08-21T18:33:29.313779+00:00</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Sales &amp; Customer Success Intern - EU</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Truecaller</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/truecaller/jobs/8138837</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Sales &amp; Customer Success Intern - EU</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-08-14T03:46:04.307219+00:00</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Quantitative Research Internship - 6 Months, Central Execution Research</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Towerresearchcapital</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=8113986</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Quantitative Research Internship - 6 Months, Central Execution Research</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-08-10T17:40:51.724814+00:00</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>AI Engineer, Internship - Summer 2026 - Applications Open Now</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Data / AI</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Berkeley, California, United States; San Francisco, California, United States</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/postman/jobs/7823417003</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>AI Engineer, Internship - Summer 2026 - Applications Open Now</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-08-10T17:40:47.009978+00:00</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>[Backend] Software Engineering Intern</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Enterpret</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Bengaluru, Onsite</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/enterpret/jobs/7847134003</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>[Backend] Software Engineering Intern</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:12:52.37725+00:00</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Brand Marketing Intern</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Earnin</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/earnin/jobs/8113206</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Brand Marketing Intern</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:12:50.084908+00:00</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Customer Success Intern</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Knowbe4</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/knowbe4/jobs/8660687002</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Customer Success Intern</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:12:46.851447+00:00</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Product Marketing Intern - Tetriz</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Epifi</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/epifi/c6d070ce-d859-4d96-b82e-bca1fea37ddd</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Product Marketing Intern - Tetriz</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:12:45.117452+00:00</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Junior Execution Trader Intern</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Towerresearchcapital</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=8091833</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Junior Execution Trader Intern</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:30:43.226773+00:00</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Copy Writer - Intern</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Groww</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774341101</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Copy Writer - Intern</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:30:36.983937+00:00</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Video Editor Intern</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Groww</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4771440101</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Video Editor Intern</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:30:35.138664+00:00</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Internship - Content </t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Groww</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4819749101</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Internship - Content</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:30:33.590227+00:00</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Graphic Designer - Intern</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Groww</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774342101</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Graphic Designer - Intern</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:30:31.543915+00:00</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Business Development Specialist (Outbound- International)</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Tide</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/tide/jobs/7081017003</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Business Development Specialist (Outbound- International)</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:30:28.879852+00:00</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Business Development Specialist (International Sales)</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Tide</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/tide/jobs/7598880003</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Business Development Specialist (International Sales)</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:30:17.721593+00:00</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Risk Intern - 6 Month Internship Opportunity</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Towerresearchcapital</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=7789933</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Risk Intern - 6 Month Internship Opportunity</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:30:10.248679+00:00</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Quantitative Trader Intern - Summer 2027</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Towerresearchcapital</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=8024128</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Quantitative Trader Intern - Summer 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:30:07.980596+00:00</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Quantitative Trader Intern, PhD</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Towerresearchcapital</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=8024138</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Quantitative Trader Intern, PhD</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:30:05.838281+00:00</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Quantitative Developer Intern - Summer 2027</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Towerresearchcapital</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=8044334</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Quantitative Developer Intern - Summer 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:30:03.426202+00:00</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Business Analytics Intern - 6 Month Internship Opportunity</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Towerresearchcapital</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Data / AI</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=8041512</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Business Analytics Intern - 6 Month Internship Opportunity</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:30:01.432263+00:00</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Sales Development Representative Intern (Hybrid)</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Knowbe4</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/knowbe4/jobs/8566454002</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Sales Development Representative Intern (Hybrid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:29:59.490728+00:00</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Sales Development Representative Intern (Hybrid)</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Knowbe4</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/knowbe4/jobs/8566457002</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Sales Development Representative Intern (Hybrid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:29:55.183092+00:00</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Intern - Industrial Trainee</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Inmobi</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Data / AI</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/inmobi/jobs/8029868</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Intern - Industrial Trainee</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:29:52.581754+00:00</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Intern - Industrial Trainee</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Inmobi</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Data / AI</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/inmobi/jobs/7793050</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Intern - Industrial Trainee</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:29:48.780995+00:00</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Security Consultant Intern</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Cloudsek</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/cloudsek/jobs/6115382004</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Security Consultant Intern</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:29:47.193044+00:00</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SDE Intern - Frontend   </t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Cloudsek</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/cloudsek/jobs/5831215004</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>SDE Intern - Frontend</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:29:44.845632+00:00</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>SDE - Backend - Intern</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Cloudsek</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/cloudsek/jobs/5766402004</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>SDE - Backend - Intern</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:29:42.382537+00:00</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Business Development Representative Intern - Canada</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Cloudsek</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/cloudsek/jobs/6005469004</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Business Development Representative Intern - Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:29:25.892883+00:00</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>DS/ML Intern</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Epifi</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Data / AI</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>A builder mindset is the core of this role and where you'll spend most of your time. But we're a small team building a whole product, not a research lab. The best person here treats ML systems as their primary craft while staying willing to do whatever the product needs — thinking through the product itself, shipping backend or frontend code, untangling data pipelines. We're looking for someone energized by the breadth, not someone who wants to stay in their lane. What you'll work on Evaluation systems for AI features Help build the eval backbone our AI features ship against — failure taxonomies, LLM-as-judge rubrics, golden datasets, calibration against human judgment. Learn what it takes to keep automated scores honest as models and prompts change. A feature with no eval has no quality floor. Model routing &amp; inference economics Get hands-on with how we route work across models — balancing cost, quality, and latency per task. Help run the experiments that justify those choices and catch regressions. Scoring, measurement &amp; signal quality Work on turning noisy, real-world signals into scores you can actually trust — grounded in real statistical rigor, not vibes. Help move heuristic-</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:29:22.213288+00:00</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Ai Engg Intern</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Epifi</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Data / AI</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/epifi/08c743e8-2b29-4f78-827e-5bd90476ed86</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Ai Engg Intern</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:29:12.993097+00:00</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>[Tech Cooperative Internship 2026] Software Engineer in Back End intern (6 months)</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Agoda</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/agoda/jobs/5443559</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>[Tech Cooperative Internship 2026] Software Engineer in Back End intern (6 months)</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:28:57.849831+00:00</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>International Payroll Partner</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Agoda</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/agoda/jobs/8063978</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>International Payroll Partner</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:28:36.025672+00:00</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>GenAI Product Builder Intern</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Epifi</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Data / AI</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/epifi/4f5b7548-ea0a-4be0-816b-11d712853169</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>GenAI Product Builder Intern About us Tetriz is an AI Engineering Intelligence platform that helps engineering organizations become AI-native, faster. We measure how AI coding tools like Cursor, Claude Code, and GitHub Copilot are actually used, improve engineer effectiveness through prompt and workflow coaching, and help engineering leaders demonstrate AI ROI with board-ready, defensible insights. Who should apply This is not a general internship, you should apply only if: - You’ve built or designed things outside of college - You have a portfolio / GitHub of real work - Your work shows initiative, not just completion - You care about problems, not just tools If your experience is mostly coursework, this won’t be a fit. What you’ll get - Work on a real AI product used by engineering teams - Own problems end-to-end, not assist someone else - Exposure to cutting-edge GenAI workflows - A steep learning curve — we’ll push you hard and help you grow fast If you’re hungry and serious, you’ll leave this internship 10x better and ready for the AI-first world. What you’ll do - Build features end-to-end — from idea to production - Work with LLMs, APIs, and internal systems - Create tools th</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-07-27T10:49:04.274532+00:00</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Copy Writer - Intern</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Groww</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774341101</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Copy Writer - Intern</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-07-27T10:49:00.838626+00:00</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Video Editor Intern</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Groww</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4771440101</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Video Editor Intern</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-07-27T10:48:58.630946+00:00</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Internship - Content </t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Groww</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4819749101</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Internship - Content</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-07-27T10:48:56.06648+00:00</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Graphic Designer - Intern</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Groww</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774342101</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Graphic Designer - Intern</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-07-27T10:42:53.996409+00:00</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Copy Writer - Intern</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Groww</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774341101</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Copy Writer - Intern</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-07-27T10:42:50.938109+00:00</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Graphic Designer - Intern</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Groww</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774342101</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Graphic Designer - Intern</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-07-27T10:42:47.32783+00:00</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Internship - Content </t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Groww</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4819749101</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Internship - Content</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-07-27T10:42:43.192382+00:00</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Video Editor Intern</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Groww</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4771440101</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Video Editor Intern</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-07-26T19:14:17.297621+00:00</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>ReactJS Internship</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>ElevateHQ</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>₹240000 - ₹420000</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/4794473734?utm_medium=api&amp;utm_source=e044e1cb</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Position Overview: We are seeking a talented and motivated ReactJS Intern to join our team for a 6-month full-time internship. This is a fantastic opportunity for someone with prior internship experience to deepen their knowledge and skills in ReactJS while working on cutting-edge projects. Responsibilities: Collaborate with the development team to design, develop, and maintain web applications using ReactJS. Write clean, maintainable, and efficient code. Participate in code reviews and contrib…</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-07-26T19:14:13.725695+00:00</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Developer Internship</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>PBL India</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/4801600698?utm_medium=api&amp;utm_source=e044e1cb</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Percpktika Brand Lab is a Product Development startup which supports and develops products guiding social innovation. We are looking for smart and talented interns who are capable of working from Delhi or remote and submitting results. At PBL we have an efficient training process which provides resources to grow and nurture your talent. The selected intern(s) will work on following during the internship: 1. Code Reviews and Research. 2. Creating Core features using Node.js and Native Script sup…</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-07-26T19:14:07.63634+00:00</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Design Internship</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>PBL India</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/details/4801437257?utm_medium=api&amp;utm_source=e044e1cb</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Percpktika Brand Lab is a Product Development startup which supports and develops products guiding social innovation. We are looking for smart and talented interns who are capable of working from Delhi or remote and submitting results. At PBL we have an efficient training process which provides resources to grow and nurture your talent. The selected intern(s) will work on following during the internship: 1. Designing User Interface. 2. Experience planning and flow. 3. Product Branding and Desig…</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-07-26T19:13:19.489348+00:00</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Customer Care Intern</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5790410523?se=rFvE0iWJ8RGGXqQIyNVN5Q&amp;utm_medium=api&amp;utm_source=e044e1cb&amp;v=5E72C4726A0DF728D03FF51102E0532CA986DDEA</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>This job is with Criteo, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. What You'll Do: The multinational Global Customer Care Team is the first point of contact for Criteo Customers; our goal is to provide excellent customer support to all incoming client requests using email or live chat. We excel at collaboration, communication, and teamwork, as they are key to solving our client's re…</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-07-26T19:13:17.765892+00:00</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Sales &amp; Strategy Intern</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Criteo</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>https://www.adzuna.in/land/ad/5806276940?se=rFvE0iWJ8RGGXqQIyNVN5Q&amp;utm_medium=api&amp;utm_source=e044e1cb&amp;v=B2147145725F724ABD3B0362E330EB1DD5EB962B</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>This job is with Criteo, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. What You'll Do: As a Sales &amp; Strategy Intern, you will be part of our India team that works with new and existing clients. You will be learning and working with brands, analyzing and optimizing campaigns, along with cultivating a strong and productive relationship with clients. This is a 12-month paid, full-time inte…</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:23:56.921677+00:00</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>GRAPHIC DESIGNER</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>NEW VINE LIMITED</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-graphic-designer-new-vine-limited-1135316</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Graphic Designer (part-time) An exciting opportunity has arisen for a Graphic Designer (part-time) to join us, working remotely with great benefits. The role will work primarily on our books, subscription materials, and digital resources, creating eye-catching covers, inside layouts, and ebooks. Prior experience of working on these types of resources in Adobe Creative Suite is essential, as is a solid understanding of design, layout, typography, and brand. Salary: Â£16,500 (Â£27,500 FTE) Applications close: 29 August 2026 Download the job information (.pdf) Download the application form (.docx) We welcome applicants from all backgrounds and communities, in particular those that are currently under-represented within our staff team. This includes, but is not limited to, people from Black, Asian, and other ethnic groups, especially within our leadership roles. Please mention the word **PROLIFIC** and tag RMjAyLjY2LjE2NC42 when applying to show you read the job post completely (#RMjAyLjY2LjE2NC42). This is a beta feature to avoid spam applicants. Companies can search these words to find applicants that read this and see they're human.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:23:39.597545+00:00</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Executive Assistant</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Ritual AdsÂ®</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-executive-assistant-ritual-adsr-1135344</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Company Description Ritual AdsÂ® is a cutting-edge AI software company that uses generative AI to create tailored, data-driven advertising content on demand. The platform helps organizations quickly produce high-impact, customized ads that align with their brand and audience. By combining advanced machine learning with real-time data, Ritual AdsÂ® aims to improve campaign performance and efficiency. Team members collaborate in a technology-forward environment focused on innovation, scalability, and measurable results. Role Description The Executive Assistant at Ritual AdsÂ® is a full-time, remote role responsible for providing comprehensive administrative and organizational support to company leadership. Day-to-day tasks include managing calendars, scheduling meetings, coordinating travel, and preparing agendas and meeting materials. The Executive Assistant will handle expense reports, track reimbursements, and maintain accurate documentation. The role also includes managing correspondence, drafting and editing communications, organizing digital files, and supporting special projects and operational tasks to ensure smooth executive workflows. Qualifications Strong Executive Adminis</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:23:35.307873+00:00</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Product Designer</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Flint</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-product-designer-flint-1135340</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Compensation: $160kâ190k base + meaningful equity About Flint The best education anyone has ever received is one person paying close attention to one student: moving at their pace, noticing what they missed, asking the next question at the right moment. But the current system is built around a compromise with one teacher managing thirty students. Flint exists to take that compromise off the table. Personalized learning, at the scale of a whole school â every student working with something closer to a tutor, and every teacher able to see what's actually happening across their class instead of guessing. Go look at the product before you read any further: app.flintk12.com The Role Students want something that stays with them, going at their pace and helps them get unstuck without just handing over the answer. Teachers want that happening inside a class they still control, and they'd like their evenings back. Admins want proof that the platform they rolled out is leading to teacher productivity and student progress. Your job is to dive deep into this design problem, holding three sets of needs within one product. Weâll trust you to ship designs that are the best possible solution</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:23:18.030686+00:00</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Join our UK team</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Workdry Germany</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-join-our-uk-team-workdry-germany-1135314</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>BracknellPump Rental SolutionsBracknellPump Rental SolutionsGreat YarmouthPump Rental SolutionsNottinghamPump Rental SolutionsAberdeenPump Rental SolutionsConwyPump Rental SolutionsStokeWorkdry - Group Central ServicesStokeWorkdry - Group Central ServicesWorkingtonPump Rental Solutions Please mention the word **GREATNESS** and tag RMjAyLjY2LjE2NC42 when applying to show you read the job post completely (#RMjAyLjY2LjE2NC42). This is a beta feature to avoid spam applicants. Companies can search these words to find applicants that read this and see they're human.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:23:11.834056+00:00</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Safety Data Analyst</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>SkyWest Airlines</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Data / AI</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>https://remoteOK.com/remote-jobs/remote-safety-data-analyst-skywest-airlines-1135445</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>About SkyWest With over 16,000 aviation professionals operating thousands of daily flights, SkyWest Airlines connects millions of passengers each month to hundreds of destinations across North America. SkyWest operates in partnership with Delta Air Lines, United Airlines, American Airlines, and Alaska Airlines and has a fleet of nearly 450 aircraft. Headquartered in St. George, Utah, SkyWest's industry-leading workforce and excellent leadership team have consistently generated solid operational and economic performance, setting the standard for excellence in the regional industry. SkyWest employees enjoy a distinctive and unmatched culture of teamwork, respect, quality, and professionalism, along with world-class benefits such as a 401(k) match, Performance Rewards, health care, retirement, and discounted travel worldwide. Primary Job Duties Analyze, compile, and report safety data to support all SkyWest safety programs. Collect, analyze, and report safety assurance data from multiple safety data sources. Identify, monitor, and communicate safety performance trends and emerging risks. Track, maintain, and report key performance indicators (KPIs) for the Safety Department, including</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:22:46.777033+00:00</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Engineering Manager - Edge AI</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>SumUp</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Data / AI</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/sumup/engineering-manager-edge-ai-berlin-258996</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Our AI Platform &amp;amp; Edge team sits at the heart of how SumUp is scaling intelligent, merchant-facing experiences across millions of interactions. We build and operate the AI systems — from LLM-powered assistants to agentic platforms — that directly shape how merchants get support, resolve issues, and engage with SumUp's products. As Engineering Manager for Edge, you'll take ownership of a growing, cross-functional team of engineers and ML specialists, leading the execution of some of our most technically complex and commercially critical AI initiatives. This is a rare opportunity to lead meaningful AI work at scale — not just shipping features, but shaping how an entire platform evolves. What you'll do Lead the day-to-day execution of the Edge AI team, translating long-term product vision into clear sprint roadmaps and measurable delivery milestones Own the migration of our AI assistant to an autonomous agentic setup, maintaining performance while expanding AI support across all merchant-facing channels Set the technical direction for LLM-powered system design, making clear tradeoffs across quality, latency, and cost Build a data-informed engineering culture by defining performan</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:22:37.744444+00:00</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Chief Marketing Officer (m/w/d)</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>InkuPlay UG (haftungsbeschränkt)</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/inkuplay-ug-haftungsbeschrankt/chief-marketing-officer-biesenthal-255944</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>InkuPlay ist ein wachstumsorientiertes Unternehmen aus dem Gaming- und E-Sports-Umfeld. Wir entwickeln Marken, Communities, digitale Formate und Partnerschaften an der Schnittstelle von Gaming, Entertainment, Content, Creator Economy und E-Sports. Unser Ziel ist es, InkuPlay als moderne, international relevante Gaming- und E-Sports-Marke zu etablieren. Dafür suchen wir eine unternehmerisch denkende Führungspersönlichkeit, die unsere Marketingstrategie entwickelt, unsere Markenpositionierung schärft und nachhaltiges Wachstum vorantreibt. Als Chief Marketing Officer (m/w/d) übernimmst du die Gesamtverantwortung für Marketing, Marke, Kommunikation und Wachstum bei InkuPlay. Du entwickelst nicht nur Kampagnen, sondern baust gemeinsam mit der Geschäftsführung eine belastbare Marketingorganisation auf. Dabei verbindest du strategische Markenführung mit datengetriebenem Growth Marketing, aufmerksamkeitsstarkem Content und kommerziell erfolgreichen Partnerschaften. Du berichtest direkt an den Founder &amp;#x26; CEO und arbeitest eng mit den Bereichen Esports, Content &amp;#x26; Media, Partnerships, Sales, Community, Recruiting und Business Development zusammen. Aufgaben Marketing- und Unternehmens</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:22:34.380054+00:00</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Head of People &amp; Culture / HR (m/w/d)</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>InkuPlay UG (haftungsbeschränkt)</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/inkuplay-ug-haftungsbeschrankt/head-of-people-culture-hr-biesenthal-163623</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">InkuPlay ist ein wachsendes Unternehmen aus den Bereichen Gaming, Esports, digitale Plattformen, Content, Community und Partnerschaften. Wir befinden uns in einer Phase des strukturellen Aufbaus und der Professionalisierung. Dafür suchen wir eine erfahrene Persönlichkeit, die unsere Personalorganisation nicht nur verwaltet, sondern aktiv gestaltet. Als Head of People &amp;#x26; Culture / HR übernimmst du die Verantwortung für den Aufbau moderner, rechtssicherer und skalierbarer Personalstrukturen. Du arbeitest eng mit dem Founder &amp;#x26; CEO, dem operativen Management, den Führungskräften sowie externen arbeitsrechtlichen und steuerlichen Beratern zusammen. Die Position verbindet strategische Personalarbeit mit operativer Umsetzung. Gesucht wird daher keine rein beratende HR-Funktion, sondern eine Person, die Verantwortung übernimmt, Entscheidungen vorbereitet, Prozesse etabliert und Themen zuverlässig bis zum Abschluss begleitet. Deine Rolle Als Head of People &amp;#x26; Culture / HR verantwortest du sämtliche personalbezogenen Themen bei InkuPlay. Du entwickelst eine professionelle HR-Struktur, die zu einem dynamischen Startup im Gaming- und Esports-Umfeld passt. Dabei stellst du sicher, </t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:22:32.624515+00:00</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Praktikum Amazon PPC &amp; Performance Marketing im E-Commerce Start-up (m/w/d)</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Sayano Deutschland GmbH</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/sayano-deutschland-gmbh/praktikum-amazon-ppc-performance-marketing-im-e-commerce-start-up-stuttgart-189082</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Du willst mitgestalten statt nur zuschauen? Dann bist Du bei uns richtig. Wir sind Sayano – ein modernes, international tätiges E-Commerce-Unternehmen hinter Marken wie MIAMIO, Tortillada und Calmado. Unsere Produkte erreichen Kundinnen und Kunden in mehr als 80 Ländern. Die Financial Times hat uns vier Jahre in Folge als eines der am schnellsten wachsenden Unternehmen Europas ausgezeichnet. Wir arbeiten schnell, datengetrieben und konsequent mit modernen KI-Technologien. KI ist für uns kein Zukunftsthema, sondern fester Bestandteil unseres Arbeitsalltags – von Analysen und Recherchen über Automatisierungen bis zur Optimierung unserer Werbekampagnen. Aufgaben Du unterstützt bei der Analyse und Optimierung unserer Amazon-PPC-Kampagnen Du arbeitest mit Sponsored Products, Sponsored Brands und Sponsored Display Du führst Keyword-, Suchbegriff- und Wettbewerbsanalysen durch Du identifizierst profitable Suchbegriffe und entwickelst diese gemeinsam mit uns weiter Du hilfst dabei, unnötige Werbeausgaben zu erkennen und zu reduzieren Du unterstützt bei der Optimierung von Geboten, Budgets, Platzierungen und negativen Keywords Du analysierst Kennzahlen wie ACOS, TACOS, ROAS, CPC, CTR und Co</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:22:28.361273+00:00</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Brand &amp; Content Lead</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Klar</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/klar/brand-content-lead-munich-463374</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>In Short: We are looking for someone that loves content and eCommerce to own our entire brand surface — content, community, product marketing, and website — and turn Klar into the go-to resource for actionable eCom knowledge in Europe. About Klar 🚀 The Mission Klar is the Data Operating System for growing eCommerce companies, meaning no more spreadsheets . We integrate with all of a brand's data sources to provide a holistic understanding of their business, offering detailed insights on how to accelerate growth and increase profitability. 🛍️ The Reach We are already the "single source of truth" for over 1,000 leading eCom brands. Market leaders like Sunday Natural, Loop Earplugs, Holy, Maniko, and Armed Angels use Klar to make better decisions every single day. 🤝 The Backstory We deeply empathize with our customers because we were our customers. The founders (who met in South Africa working for Zando) spent the last 10 years in e-commerce. We know the pain of running these businesses, and we built Klar specifically to solve it. ✨ The Principle Our guiding principle is Do Work You Are Proud Of . We emphasize long-term quality over short-term results. We evaluate our tools and dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-07-26T18:22:23.542927+00:00</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Kreativer Allrounder Marketing (m/w/d) | Gestalte unseren Markenauftritt aktiv</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Autohaus Wernsing GmbH</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>https://www.arbeitnow.com/jobs/companies/autohaus-wernsing-gmbh/kreativer-allrounder-marketing-gestalte-unseren-markenauftritt-aktiv-bersenbruck-288838</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Werde kreativ. Mach unsere Marken sichtbar. Du hast Freude an Social Media, Content Creation und kreativem Marketing? Du möchtest nicht einfach nur bestehende Aufgaben abarbeiten, sondern einen Marketingbereich aktiv mitgestalten und weiterentwickeln? Dann bist du bei uns genau richtig! Für unsere Unternehmen Autohaus Wernsing und 2Rad Wernsing suchen wir eine kreative und engagierte Persönlichkeit, die unseren Außenauftritt eigenverantwortlich weiterentwickelt und gemeinsam mit der Geschäftsführung den Marketingbereich aufbaut. Du arbeitest auf Basis unseres bestehenden Markenbooks mit klar definiertem Corporate Design und hast gleichzeitig viel Freiraum für eigene Ideen und kreative Konzepte. Der Schwerpunkt deiner Tätigkeit liegt eindeutig im Marketing. Ein kleiner Teil deiner Arbeitszeit unterstützt unser Team bei Veranstaltungen oder vertriebsnahen Projekten. Ob in Teilzeit oder auf geringfügiger Basis – wir sind flexibel. Ein Teil deiner Arbeit kann nach Absprache auch im Homeoffice erledigt werden. Aufgaben Marketing &amp;#x26; Content Creation Eigenverantwortlicher Aufbau und Weiterentwicklung unseres Marketingbereichs in enger Abstimmung mit der Geschäftsführung Planung, Erste</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
           <t>2026-07-17T10:23:01.374271+00:00</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B227" t="inlineStr">
         <is>
           <t>Test Internship</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="C227" t="inlineStr">
         <is>
           <t>Test Company</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="D227" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="E227" t="inlineStr">
         <is>
           <t>10,000/mo</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr">
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr">
         <is>
           <t>https://example.com</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
+      <c r="H227" t="inlineStr">
         <is>
           <t>This is a test listing</t>
         </is>

--- a/approved_jobs.xlsx
+++ b/approved_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H466"/>
+  <dimension ref="A1:H465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -15911,17 +15911,17 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2026-08-22T12:32:56.748107+00:00</t>
+          <t>2026-08-22T12:32:54.751872+00:00</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>FRND</t>
+          <t>Harman</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -15933,7 +15933,7 @@
       <c r="F412" t="inlineStr"/>
       <c r="G412" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4455599485/</t>
+          <t>https://jobsearch.harman.com/en_US/careers/searchjobs/R-54623-2026</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -15945,29 +15945,33 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2026-08-22T12:32:54.751872+00:00</t>
+          <t>2026-08-22T12:32:52.811769+00:00</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>AI Facial Data Collection Contributor</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Harman</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Data / AI</t>
         </is>
       </c>
       <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Remote (Work From Home)</t>
+        </is>
+      </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>https://jobsearch.harman.com/en_US/careers/searchjobs/R-54623-2026</t>
+          <t>https://bit.ly/4hl4Ar1</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -15979,12 +15983,12 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>2026-08-22T12:32:52.811769+00:00</t>
+          <t>2026-08-22T12:32:50.619505+00:00</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>AI Facial Data Collection Contributor</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -15994,7 +15998,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Data / AI</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E414" t="inlineStr"/>
@@ -16005,7 +16009,7 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>https://bit.ly/4hl4Ar1</t>
+          <t>https://bit.ly/4hH3q9A</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -16017,17 +16021,17 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2026-08-22T12:32:50.619505+00:00</t>
+          <t>2026-08-22T12:32:48.755864+00:00</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer - AMTS</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -16038,12 +16042,12 @@
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="inlineStr">
         <is>
-          <t>Remote (Work From Home)</t>
+          <t>Hyderabad/Bangalore, India</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>https://bit.ly/4hH3q9A</t>
+          <t>https://bit.ly/4xGBIOS</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -16055,33 +16059,33 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>2026-08-22T12:32:48.755864+00:00</t>
+          <t>2026-08-22T12:32:43.264285+00:00</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Software Engineer - AMTS</t>
+          <t>Fullstack Developer</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="inlineStr">
         <is>
-          <t>Hyderabad/Bangalore, India</t>
+          <t>Remote (Work From Home)</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>https://bit.ly/4xGBIOS</t>
+          <t>https://bit.ly/3Sy7PRO</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -16093,12 +16097,12 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2026-08-22T12:32:43.264285+00:00</t>
+          <t>2026-08-22T12:32:40.571545+00:00</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Fullstack Developer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -16108,7 +16112,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="E417" t="inlineStr"/>
@@ -16119,7 +16123,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>https://bit.ly/3Sy7PRO</t>
+          <t>https://bit.ly/4wZ8B9r</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -16131,50 +16135,50 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2026-08-22T12:32:40.571545+00:00</t>
+          <t>2026-08-21T18:33:37.259219+00:00</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Intern - AI/ML</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Towerresearchcapital</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Data / AI</t>
         </is>
       </c>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="inlineStr">
         <is>
-          <t>Remote (Work From Home)</t>
+          <t>gurgaon</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>https://bit.ly/4wZ8B9r</t>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=8143756</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>Intern - AI/ML</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>2026-08-21T18:33:37.259219+00:00</t>
+          <t>2026-08-21T18:33:33.878834+00:00</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Intern - AI/ML</t>
+          <t>Quantitative Developer Intern</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -16184,226 +16188,222 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Data / AI</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E419" t="inlineStr"/>
       <c r="F419" t="inlineStr">
         <is>
-          <t>gurgaon</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=8143756</t>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=8138524</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>Intern - AI/ML</t>
+          <t>Quantitative Developer Intern</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>2026-08-21T18:33:33.878834+00:00</t>
+          <t>2026-08-21T18:33:29.313779+00:00</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Quantitative Developer Intern</t>
+          <t>Sales &amp; Customer Success Intern - EU</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Towerresearchcapital</t>
+          <t>Truecaller</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E420" t="inlineStr"/>
       <c r="F420" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=8138524</t>
+          <t>https://job-boards.greenhouse.io/truecaller/jobs/8138837</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>Quantitative Developer Intern</t>
+          <t>Sales &amp; Customer Success Intern - EU</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>2026-08-21T18:33:29.313779+00:00</t>
+          <t>2026-08-14T03:46:04.307219+00:00</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Sales &amp; Customer Success Intern - EU</t>
+          <t>Quantitative Research Internship - 6 Months, Central Execution Research</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Truecaller</t>
+          <t>Towerresearchcapital</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E421" t="inlineStr"/>
       <c r="F421" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>London</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/truecaller/jobs/8138837</t>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=8113986</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>Sales &amp; Customer Success Intern - EU</t>
+          <t>Quantitative Research Internship - 6 Months, Central Execution Research</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>2026-08-14T03:46:04.307219+00:00</t>
+          <t>2026-08-10T17:40:47.009978+00:00</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Quantitative Research Internship - 6 Months, Central Execution Research</t>
+          <t>[Backend] Software Engineering Intern</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Towerresearchcapital</t>
+          <t>Enterpret</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="E422" t="inlineStr"/>
       <c r="F422" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Bengaluru, Onsite</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=8113986</t>
+          <t>https://job-boards.greenhouse.io/enterpret/jobs/7847134003</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>Quantitative Research Internship - 6 Months, Central Execution Research</t>
+          <t>[Backend] Software Engineering Intern</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>2026-08-10T17:40:47.009978+00:00</t>
+          <t>2026-08-08T04:12:52.37725+00:00</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>[Backend] Software Engineering Intern</t>
+          <t>Brand Marketing Intern</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Enterpret</t>
+          <t>Earnin</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E423" t="inlineStr"/>
-      <c r="F423" t="inlineStr">
-        <is>
-          <t>Bengaluru, Onsite</t>
-        </is>
-      </c>
+      <c r="F423" t="inlineStr"/>
       <c r="G423" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/enterpret/jobs/7847134003</t>
+          <t>https://job-boards.greenhouse.io/earnin/jobs/8113206</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>[Backend] Software Engineering Intern</t>
+          <t>Brand Marketing Intern</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>2026-08-08T04:12:52.37725+00:00</t>
+          <t>2026-08-08T04:12:50.084908+00:00</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Brand Marketing Intern</t>
+          <t>Customer Success Intern</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Earnin</t>
+          <t>Knowbe4</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E424" t="inlineStr"/>
       <c r="F424" t="inlineStr"/>
       <c r="G424" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/earnin/jobs/8113206</t>
+          <t>https://job-boards.greenhouse.io/knowbe4/jobs/8660687002</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>Brand Marketing Intern</t>
+          <t>Customer Success Intern</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>2026-08-08T04:12:50.084908+00:00</t>
+          <t>2026-08-08T04:12:45.117452+00:00</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Customer Success Intern</t>
+          <t>Junior Execution Trader Intern</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Knowbe4</t>
+          <t>Towerresearchcapital</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -16415,29 +16415,29 @@
       <c r="F425" t="inlineStr"/>
       <c r="G425" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/knowbe4/jobs/8660687002</t>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=8091833</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>Customer Success Intern</t>
+          <t>Junior Execution Trader Intern</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>2026-08-08T04:12:45.117452+00:00</t>
+          <t>2026-07-27T16:30:43.226773+00:00</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Junior Execution Trader Intern</t>
+          <t>Copy Writer - Intern</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Towerresearchcapital</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -16449,24 +16449,24 @@
       <c r="F426" t="inlineStr"/>
       <c r="G426" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=8091833</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774341101</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>Junior Execution Trader Intern</t>
+          <t>Copy Writer - Intern</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:43.226773+00:00</t>
+          <t>2026-07-27T16:30:36.983937+00:00</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Copy Writer - Intern</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -16483,24 +16483,24 @@
       <c r="F427" t="inlineStr"/>
       <c r="G427" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774341101</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4771440101</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>Copy Writer - Intern</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:36.983937+00:00</t>
+          <t>2026-07-27T16:30:35.138664+00:00</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t xml:space="preserve">Internship - Content </t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -16510,31 +16510,31 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E428" t="inlineStr"/>
       <c r="F428" t="inlineStr"/>
       <c r="G428" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4771440101</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4819749101</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Internship - Content</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:35.138664+00:00</t>
+          <t>2026-07-27T16:30:33.590227+00:00</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t xml:space="preserve">Internship - Content </t>
+          <t>Graphic Designer - Intern</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -16544,65 +16544,65 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E429" t="inlineStr"/>
       <c r="F429" t="inlineStr"/>
       <c r="G429" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4819749101</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774342101</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>Internship - Content</t>
+          <t>Graphic Designer - Intern</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:33.590227+00:00</t>
+          <t>2026-07-27T16:30:31.543915+00:00</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Graphic Designer - Intern</t>
+          <t>Business Development Specialist (Outbound- International)</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>Tide</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E430" t="inlineStr"/>
       <c r="F430" t="inlineStr"/>
       <c r="G430" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774342101</t>
+          <t>https://job-boards.greenhouse.io/tide/jobs/7081017003</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>Graphic Designer - Intern</t>
+          <t>Business Development Specialist (Outbound- International)</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:31.543915+00:00</t>
+          <t>2026-07-27T16:30:28.879852+00:00</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Business Development Specialist (Outbound- International)</t>
+          <t>Business Development Specialist (International Sales)</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -16612,65 +16612,65 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E431" t="inlineStr"/>
       <c r="F431" t="inlineStr"/>
       <c r="G431" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/tide/jobs/7081017003</t>
+          <t>https://job-boards.greenhouse.io/tide/jobs/7598880003</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>Business Development Specialist (Outbound- International)</t>
+          <t>Business Development Specialist (International Sales)</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:28.879852+00:00</t>
+          <t>2026-07-27T16:30:17.721593+00:00</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Business Development Specialist (International Sales)</t>
+          <t>Risk Intern - 6 Month Internship Opportunity</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Tide</t>
+          <t>Towerresearchcapital</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E432" t="inlineStr"/>
       <c r="F432" t="inlineStr"/>
       <c r="G432" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/tide/jobs/7598880003</t>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=7789933</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>Business Development Specialist (International Sales)</t>
+          <t>Risk Intern - 6 Month Internship Opportunity</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:17.721593+00:00</t>
+          <t>2026-07-27T16:30:10.248679+00:00</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Risk Intern - 6 Month Internship Opportunity</t>
+          <t>Quantitative Trader Intern - Summer 2027</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -16687,24 +16687,24 @@
       <c r="F433" t="inlineStr"/>
       <c r="G433" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=7789933</t>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=8024128</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>Risk Intern - 6 Month Internship Opportunity</t>
+          <t>Quantitative Trader Intern - Summer 2027</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:10.248679+00:00</t>
+          <t>2026-07-27T16:30:07.980596+00:00</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Quantitative Trader Intern - Summer 2027</t>
+          <t>Quantitative Trader Intern, PhD</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -16721,24 +16721,24 @@
       <c r="F434" t="inlineStr"/>
       <c r="G434" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=8024128</t>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=8024138</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>Quantitative Trader Intern - Summer 2027</t>
+          <t>Quantitative Trader Intern, PhD</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:07.980596+00:00</t>
+          <t>2026-07-27T16:30:05.838281+00:00</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Quantitative Trader Intern, PhD</t>
+          <t>Quantitative Developer Intern - Summer 2027</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -16755,24 +16755,24 @@
       <c r="F435" t="inlineStr"/>
       <c r="G435" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=8024138</t>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=8044334</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>Quantitative Trader Intern, PhD</t>
+          <t>Quantitative Developer Intern - Summer 2027</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:05.838281+00:00</t>
+          <t>2026-07-27T16:30:03.426202+00:00</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Quantitative Developer Intern - Summer 2027</t>
+          <t>Business Analytics Intern - 6 Month Internship Opportunity</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -16782,60 +16782,60 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Data / AI</t>
         </is>
       </c>
       <c r="E436" t="inlineStr"/>
       <c r="F436" t="inlineStr"/>
       <c r="G436" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=8044334</t>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=8041512</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>Quantitative Developer Intern - Summer 2027</t>
+          <t>Business Analytics Intern - 6 Month Internship Opportunity</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:03.426202+00:00</t>
+          <t>2026-07-27T16:30:01.432263+00:00</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Business Analytics Intern - 6 Month Internship Opportunity</t>
+          <t>Sales Development Representative Intern (Hybrid)</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Towerresearchcapital</t>
+          <t>Knowbe4</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Data / AI</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E437" t="inlineStr"/>
       <c r="F437" t="inlineStr"/>
       <c r="G437" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=8041512</t>
+          <t>https://job-boards.greenhouse.io/knowbe4/jobs/8566454002</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>Business Analytics Intern - 6 Month Internship Opportunity</t>
+          <t>Sales Development Representative Intern (Hybrid)</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:01.432263+00:00</t>
+          <t>2026-07-27T16:29:59.490728+00:00</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -16857,7 +16857,7 @@
       <c r="F438" t="inlineStr"/>
       <c r="G438" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/knowbe4/jobs/8566454002</t>
+          <t>https://job-boards.greenhouse.io/knowbe4/jobs/8566457002</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -16869,41 +16869,41 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>2026-07-27T16:29:59.490728+00:00</t>
+          <t>2026-07-27T16:29:55.183092+00:00</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Sales Development Representative Intern (Hybrid)</t>
+          <t>Intern - Industrial Trainee</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Knowbe4</t>
+          <t>Inmobi</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Data / AI</t>
         </is>
       </c>
       <c r="E439" t="inlineStr"/>
       <c r="F439" t="inlineStr"/>
       <c r="G439" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/knowbe4/jobs/8566457002</t>
+          <t>https://job-boards.greenhouse.io/inmobi/jobs/8029868</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>Sales Development Representative Intern (Hybrid)</t>
+          <t>Intern - Industrial Trainee</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>2026-07-27T16:29:55.183092+00:00</t>
+          <t>2026-07-27T16:29:52.581754+00:00</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -16925,7 +16925,7 @@
       <c r="F440" t="inlineStr"/>
       <c r="G440" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/inmobi/jobs/8029868</t>
+          <t>https://job-boards.greenhouse.io/inmobi/jobs/7793050</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -16937,46 +16937,46 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>2026-07-27T16:29:52.581754+00:00</t>
+          <t>2026-07-27T16:29:48.780995+00:00</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Intern - Industrial Trainee</t>
+          <t>Security Consultant Intern</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Inmobi</t>
+          <t>Cloudsek</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Data / AI</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E441" t="inlineStr"/>
       <c r="F441" t="inlineStr"/>
       <c r="G441" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/inmobi/jobs/7793050</t>
+          <t>https://job-boards.greenhouse.io/cloudsek/jobs/6115382004</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>Intern - Industrial Trainee</t>
+          <t>Security Consultant Intern</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>2026-07-27T16:29:48.780995+00:00</t>
+          <t>2026-07-27T16:29:47.193044+00:00</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Security Consultant Intern</t>
+          <t xml:space="preserve">SDE Intern - Frontend   </t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -16986,31 +16986,31 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="E442" t="inlineStr"/>
       <c r="F442" t="inlineStr"/>
       <c r="G442" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/cloudsek/jobs/6115382004</t>
+          <t>https://job-boards.greenhouse.io/cloudsek/jobs/5831215004</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>Security Consultant Intern</t>
+          <t>SDE Intern - Frontend</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>2026-07-27T16:29:47.193044+00:00</t>
+          <t>2026-07-27T16:29:44.845632+00:00</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t xml:space="preserve">SDE Intern - Frontend   </t>
+          <t>SDE - Backend - Intern</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -17020,31 +17020,31 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="E443" t="inlineStr"/>
       <c r="F443" t="inlineStr"/>
       <c r="G443" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/cloudsek/jobs/5831215004</t>
+          <t>https://job-boards.greenhouse.io/cloudsek/jobs/5766402004</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>SDE Intern - Frontend</t>
+          <t>SDE - Backend - Intern</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>2026-07-27T16:29:44.845632+00:00</t>
+          <t>2026-07-27T16:29:42.382537+00:00</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>SDE - Backend - Intern</t>
+          <t>Business Development Representative Intern - Canada</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -17054,36 +17054,36 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E444" t="inlineStr"/>
       <c r="F444" t="inlineStr"/>
       <c r="G444" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/cloudsek/jobs/5766402004</t>
+          <t>https://job-boards.greenhouse.io/cloudsek/jobs/6005469004</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>SDE - Backend - Intern</t>
+          <t>Business Development Representative Intern - Canada</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>2026-07-27T16:29:42.382537+00:00</t>
+          <t>2026-07-27T16:29:12.993097+00:00</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Business Development Representative Intern - Canada</t>
+          <t>[Tech Cooperative Internship 2026] Software Engineer in Back End intern (6 months)</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Cloudsek</t>
+          <t>Agoda</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -17095,24 +17095,24 @@
       <c r="F445" t="inlineStr"/>
       <c r="G445" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/cloudsek/jobs/6005469004</t>
+          <t>https://job-boards.greenhouse.io/agoda/jobs/5443559</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>Business Development Representative Intern - Canada</t>
+          <t>[Tech Cooperative Internship 2026] Software Engineer in Back End intern (6 months)</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>2026-07-27T16:29:12.993097+00:00</t>
+          <t>2026-07-27T16:28:57.849831+00:00</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>[Tech Cooperative Internship 2026] Software Engineer in Back End intern (6 months)</t>
+          <t>International Payroll Partner</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -17129,29 +17129,29 @@
       <c r="F446" t="inlineStr"/>
       <c r="G446" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/agoda/jobs/5443559</t>
+          <t>https://job-boards.greenhouse.io/agoda/jobs/8063978</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>[Tech Cooperative Internship 2026] Software Engineer in Back End intern (6 months)</t>
+          <t>International Payroll Partner</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>2026-07-27T16:28:57.849831+00:00</t>
+          <t>2026-07-27T10:49:04.274532+00:00</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>International Payroll Partner</t>
+          <t>Copy Writer - Intern</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Agoda</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -17163,24 +17163,24 @@
       <c r="F447" t="inlineStr"/>
       <c r="G447" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/agoda/jobs/8063978</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774341101</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>International Payroll Partner</t>
+          <t>Copy Writer - Intern</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>2026-07-27T10:49:04.274532+00:00</t>
+          <t>2026-07-27T10:49:00.838626+00:00</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Copy Writer - Intern</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -17197,24 +17197,24 @@
       <c r="F448" t="inlineStr"/>
       <c r="G448" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774341101</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4771440101</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>Copy Writer - Intern</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>2026-07-27T10:49:00.838626+00:00</t>
+          <t>2026-07-27T10:48:58.630946+00:00</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t xml:space="preserve">Internship - Content </t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -17224,31 +17224,31 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E449" t="inlineStr"/>
       <c r="F449" t="inlineStr"/>
       <c r="G449" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4771440101</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4819749101</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Internship - Content</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>2026-07-27T10:48:58.630946+00:00</t>
+          <t>2026-07-27T10:48:56.06648+00:00</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t xml:space="preserve">Internship - Content </t>
+          <t>Graphic Designer - Intern</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -17258,31 +17258,31 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E450" t="inlineStr"/>
       <c r="F450" t="inlineStr"/>
       <c r="G450" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4819749101</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774342101</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>Internship - Content</t>
+          <t>Graphic Designer - Intern</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>2026-07-27T10:48:56.06648+00:00</t>
+          <t>2026-07-27T10:42:53.996409+00:00</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Graphic Designer - Intern</t>
+          <t>Copy Writer - Intern</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -17292,31 +17292,31 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E451" t="inlineStr"/>
       <c r="F451" t="inlineStr"/>
       <c r="G451" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774342101</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774341101</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>Graphic Designer - Intern</t>
+          <t>Copy Writer - Intern</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>2026-07-27T10:42:53.996409+00:00</t>
+          <t>2026-07-27T10:42:50.938109+00:00</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Copy Writer - Intern</t>
+          <t>Graphic Designer - Intern</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -17326,31 +17326,31 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E452" t="inlineStr"/>
       <c r="F452" t="inlineStr"/>
       <c r="G452" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774341101</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774342101</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>Copy Writer - Intern</t>
+          <t>Graphic Designer - Intern</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>2026-07-27T10:42:50.938109+00:00</t>
+          <t>2026-07-27T10:42:47.32783+00:00</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Graphic Designer - Intern</t>
+          <t xml:space="preserve">Internship - Content </t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -17360,31 +17360,31 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E453" t="inlineStr"/>
       <c r="F453" t="inlineStr"/>
       <c r="G453" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774342101</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4819749101</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>Graphic Designer - Intern</t>
+          <t>Internship - Content</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>2026-07-27T10:42:47.32783+00:00</t>
+          <t>2026-07-27T10:42:43.192382+00:00</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t xml:space="preserve">Internship - Content </t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -17394,103 +17394,103 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E454" t="inlineStr"/>
       <c r="F454" t="inlineStr"/>
       <c r="G454" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4819749101</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4771440101</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>Internship - Content</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>2026-07-27T10:42:43.192382+00:00</t>
+          <t>2026-07-26T19:14:17.297621+00:00</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>ReactJS Internship</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>ElevateHQ</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>Internship</t>
-        </is>
-      </c>
-      <c r="E455" t="inlineStr"/>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>₹240000 - ₹420000</t>
+        </is>
+      </c>
       <c r="F455" t="inlineStr"/>
       <c r="G455" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4771440101</t>
+          <t>https://www.adzuna.in/details/4794473734?utm_medium=api&amp;utm_source=e044e1cb</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Position Overview: We are seeking a talented and motivated ReactJS Intern to join our team for a 6-month full-time internship. This is a fantastic opportunity for someone with prior internship experience to deepen their knowledge and skills in ReactJS while working on cutting-edge projects. Responsibilities: Collaborate with the development team to design, develop, and maintain web applications using ReactJS. Write clean, maintainable, and efficient code. Participate in code reviews and contrib…</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>2026-07-26T19:14:17.297621+00:00</t>
+          <t>2026-07-26T19:14:13.725695+00:00</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>ReactJS Internship</t>
+          <t>Developer Internship</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>ElevateHQ</t>
+          <t>PBL India</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>Frontend</t>
-        </is>
-      </c>
-      <c r="E456" t="inlineStr">
-        <is>
-          <t>₹240000 - ₹420000</t>
-        </is>
-      </c>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr"/>
       <c r="F456" t="inlineStr"/>
       <c r="G456" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/4794473734?utm_medium=api&amp;utm_source=e044e1cb</t>
+          <t>https://www.adzuna.in/details/4801600698?utm_medium=api&amp;utm_source=e044e1cb</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>Position Overview: We are seeking a talented and motivated ReactJS Intern to join our team for a 6-month full-time internship. This is a fantastic opportunity for someone with prior internship experience to deepen their knowledge and skills in ReactJS while working on cutting-edge projects. Responsibilities: Collaborate with the development team to design, develop, and maintain web applications using ReactJS. Write clean, maintainable, and efficient code. Participate in code reviews and contrib…</t>
+          <t>Percpktika Brand Lab is a Product Development startup which supports and develops products guiding social innovation. We are looking for smart and talented interns who are capable of working from Delhi or remote and submitting results. At PBL we have an efficient training process which provides resources to grow and nurture your talent. The selected intern(s) will work on following during the internship: 1. Code Reviews and Research. 2. Creating Core features using Node.js and Native Script sup…</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>2026-07-26T19:14:13.725695+00:00</t>
+          <t>2026-07-26T19:14:07.63634+00:00</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Developer Internship</t>
+          <t>Design Internship</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -17500,65 +17500,65 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E457" t="inlineStr"/>
       <c r="F457" t="inlineStr"/>
       <c r="G457" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/4801600698?utm_medium=api&amp;utm_source=e044e1cb</t>
+          <t>https://www.adzuna.in/details/4801437257?utm_medium=api&amp;utm_source=e044e1cb</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>Percpktika Brand Lab is a Product Development startup which supports and develops products guiding social innovation. We are looking for smart and talented interns who are capable of working from Delhi or remote and submitting results. At PBL we have an efficient training process which provides resources to grow and nurture your talent. The selected intern(s) will work on following during the internship: 1. Code Reviews and Research. 2. Creating Core features using Node.js and Native Script sup…</t>
+          <t>Percpktika Brand Lab is a Product Development startup which supports and develops products guiding social innovation. We are looking for smart and talented interns who are capable of working from Delhi or remote and submitting results. At PBL we have an efficient training process which provides resources to grow and nurture your talent. The selected intern(s) will work on following during the internship: 1. Designing User Interface. 2. Experience planning and flow. 3. Product Branding and Desig…</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>2026-07-26T19:14:07.63634+00:00</t>
+          <t>2026-07-26T19:13:19.489348+00:00</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Design Internship</t>
+          <t>Customer Care Intern</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>PBL India</t>
+          <t>Criteo</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E458" t="inlineStr"/>
       <c r="F458" t="inlineStr"/>
       <c r="G458" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/4801437257?utm_medium=api&amp;utm_source=e044e1cb</t>
+          <t>https://www.adzuna.in/land/ad/5790410523?se=rFvE0iWJ8RGGXqQIyNVN5Q&amp;utm_medium=api&amp;utm_source=e044e1cb&amp;v=5E72C4726A0DF728D03FF51102E0532CA986DDEA</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>Percpktika Brand Lab is a Product Development startup which supports and develops products guiding social innovation. We are looking for smart and talented interns who are capable of working from Delhi or remote and submitting results. At PBL we have an efficient training process which provides resources to grow and nurture your talent. The selected intern(s) will work on following during the internship: 1. Designing User Interface. 2. Experience planning and flow. 3. Product Branding and Desig…</t>
+          <t>This job is with Criteo, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. What You'll Do: The multinational Global Customer Care Team is the first point of contact for Criteo Customers; our goal is to provide excellent customer support to all incoming client requests using email or live chat. We excel at collaboration, communication, and teamwork, as they are key to solving our client's re…</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>2026-07-26T19:13:19.489348+00:00</t>
+          <t>2026-07-26T19:13:17.765892+00:00</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Customer Care Intern</t>
+          <t>Sales &amp; Strategy Intern</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -17568,259 +17568,225 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E459" t="inlineStr"/>
       <c r="F459" t="inlineStr"/>
       <c r="G459" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5790410523?se=rFvE0iWJ8RGGXqQIyNVN5Q&amp;utm_medium=api&amp;utm_source=e044e1cb&amp;v=5E72C4726A0DF728D03FF51102E0532CA986DDEA</t>
+          <t>https://www.adzuna.in/land/ad/5806276940?se=rFvE0iWJ8RGGXqQIyNVN5Q&amp;utm_medium=api&amp;utm_source=e044e1cb&amp;v=B2147145725F724ABD3B0362E330EB1DD5EB962B</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>This job is with Criteo, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. What You'll Do: The multinational Global Customer Care Team is the first point of contact for Criteo Customers; our goal is to provide excellent customer support to all incoming client requests using email or live chat. We excel at collaboration, communication, and teamwork, as they are key to solving our client's re…</t>
+          <t>This job is with Criteo, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. What You'll Do: As a Sales &amp; Strategy Intern, you will be part of our India team that works with new and existing clients. You will be learning and working with brands, analyzing and optimizing campaigns, along with cultivating a strong and productive relationship with clients. This is a 12-month paid, full-time inte…</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>2026-07-26T19:13:17.765892+00:00</t>
+          <t>2026-07-26T18:23:56.921677+00:00</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Sales &amp; Strategy Intern</t>
+          <t>GRAPHIC DESIGNER</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Criteo</t>
+          <t>NEW VINE LIMITED</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E460" t="inlineStr"/>
       <c r="F460" t="inlineStr"/>
       <c r="G460" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5806276940?se=rFvE0iWJ8RGGXqQIyNVN5Q&amp;utm_medium=api&amp;utm_source=e044e1cb&amp;v=B2147145725F724ABD3B0362E330EB1DD5EB962B</t>
+          <t>https://remoteOK.com/remote-jobs/remote-graphic-designer-new-vine-limited-1135316</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>This job is with Criteo, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. What You'll Do: As a Sales &amp; Strategy Intern, you will be part of our India team that works with new and existing clients. You will be learning and working with brands, analyzing and optimizing campaigns, along with cultivating a strong and productive relationship with clients. This is a 12-month paid, full-time inte…</t>
+          <t>Graphic Designer (part-time) An exciting opportunity has arisen for a Graphic Designer (part-time) to join us, working remotely with great benefits. The role will work primarily on our books, subscription materials, and digital resources, creating eye-catching covers, inside layouts, and ebooks. Prior experience of working on these types of resources in Adobe Creative Suite is essential, as is a solid understanding of design, layout, typography, and brand. Salary: Â£16,500 (Â£27,500 FTE) Applications close: 29 August 2026 Download the job information (.pdf) Download the application form (.docx) We welcome applicants from all backgrounds and communities, in particular those that are currently under-represented within our staff team. This includes, but is not limited to, people from Black, Asian, and other ethnic groups, especially within our leadership roles. Please mention the word **PROLIFIC** and tag RMjAyLjY2LjE2NC42 when applying to show you read the job post completely (#RMjAyLjY2LjE2NC42). This is a beta feature to avoid spam applicants. Companies can search these words to find applicants that read this and see they're human.</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>2026-07-26T18:23:56.921677+00:00</t>
+          <t>2026-07-26T18:23:39.597545+00:00</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>GRAPHIC DESIGNER</t>
+          <t>Executive Assistant</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>NEW VINE LIMITED</t>
+          <t>Ritual AdsÂ®</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E461" t="inlineStr"/>
       <c r="F461" t="inlineStr"/>
       <c r="G461" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-graphic-designer-new-vine-limited-1135316</t>
+          <t>https://remoteOK.com/remote-jobs/remote-executive-assistant-ritual-adsr-1135344</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>Graphic Designer (part-time) An exciting opportunity has arisen for a Graphic Designer (part-time) to join us, working remotely with great benefits. The role will work primarily on our books, subscription materials, and digital resources, creating eye-catching covers, inside layouts, and ebooks. Prior experience of working on these types of resources in Adobe Creative Suite is essential, as is a solid understanding of design, layout, typography, and brand. Salary: Â£16,500 (Â£27,500 FTE) Applications close: 29 August 2026 Download the job information (.pdf) Download the application form (.docx) We welcome applicants from all backgrounds and communities, in particular those that are currently under-represented within our staff team. This includes, but is not limited to, people from Black, Asian, and other ethnic groups, especially within our leadership roles. Please mention the word **PROLIFIC** and tag RMjAyLjY2LjE2NC42 when applying to show you read the job post completely (#RMjAyLjY2LjE2NC42). This is a beta feature to avoid spam applicants. Companies can search these words to find applicants that read this and see they're human.</t>
+          <t>Company Description Ritual AdsÂ® is a cutting-edge AI software company that uses generative AI to create tailored, data-driven advertising content on demand. The platform helps organizations quickly produce high-impact, customized ads that align with their brand and audience. By combining advanced machine learning with real-time data, Ritual AdsÂ® aims to improve campaign performance and efficiency. Team members collaborate in a technology-forward environment focused on innovation, scalability, and measurable results. Role Description The Executive Assistant at Ritual AdsÂ® is a full-time, remote role responsible for providing comprehensive administrative and organizational support to company leadership. Day-to-day tasks include managing calendars, scheduling meetings, coordinating travel, and preparing agendas and meeting materials. The Executive Assistant will handle expense reports, track reimbursements, and maintain accurate documentation. The role also includes managing correspondence, drafting and editing communications, organizing digital files, and supporting special projects and operational tasks to ensure smooth executive workflows. Qualifications Strong Executive Adminis</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>2026-07-26T18:23:39.597545+00:00</t>
+          <t>2026-07-26T18:23:35.307873+00:00</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Executive Assistant</t>
+          <t>Product Designer</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Ritual AdsÂ®</t>
+          <t>Flint</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E462" t="inlineStr"/>
       <c r="F462" t="inlineStr"/>
       <c r="G462" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-executive-assistant-ritual-adsr-1135344</t>
+          <t>https://remoteOK.com/remote-jobs/remote-product-designer-flint-1135340</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>Company Description Ritual AdsÂ® is a cutting-edge AI software company that uses generative AI to create tailored, data-driven advertising content on demand. The platform helps organizations quickly produce high-impact, customized ads that align with their brand and audience. By combining advanced machine learning with real-time data, Ritual AdsÂ® aims to improve campaign performance and efficiency. Team members collaborate in a technology-forward environment focused on innovation, scalability, and measurable results. Role Description The Executive Assistant at Ritual AdsÂ® is a full-time, remote role responsible for providing comprehensive administrative and organizational support to company leadership. Day-to-day tasks include managing calendars, scheduling meetings, coordinating travel, and preparing agendas and meeting materials. The Executive Assistant will handle expense reports, track reimbursements, and maintain accurate documentation. The role also includes managing correspondence, drafting and editing communications, organizing digital files, and supporting special projects and operational tasks to ensure smooth executive workflows. Qualifications Strong Executive Adminis</t>
+          <t>Compensation: $160kâ190k base + meaningful equity About Flint The best education anyone has ever received is one person paying close attention to one student: moving at their pace, noticing what they missed, asking the next question at the right moment. But the current system is built around a compromise with one teacher managing thirty students. Flint exists to take that compromise off the table. Personalized learning, at the scale of a whole school â every student working with something closer to a tutor, and every teacher able to see what's actually happening across their class instead of guessing. Go look at the product before you read any further: app.flintk12.com The Role Students want something that stays with them, going at their pace and helps them get unstuck without just handing over the answer. Teachers want that happening inside a class they still control, and they'd like their evenings back. Admins want proof that the platform they rolled out is leading to teacher productivity and student progress. Your job is to dive deep into this design problem, holding three sets of needs within one product. Weâll trust you to ship designs that are the best possible solution</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>2026-07-26T18:23:35.307873+00:00</t>
+          <t>2026-07-26T18:23:18.030686+00:00</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Product Designer</t>
+          <t>Join our UK team</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Flint</t>
+          <t>Workdry Germany</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E463" t="inlineStr"/>
       <c r="F463" t="inlineStr"/>
       <c r="G463" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-product-designer-flint-1135340</t>
+          <t>https://remoteOK.com/remote-jobs/remote-join-our-uk-team-workdry-germany-1135314</t>
         </is>
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>Compensation: $160kâ190k base + meaningful equity About Flint The best education anyone has ever received is one person paying close attention to one student: moving at their pace, noticing what they missed, asking the next question at the right moment. But the current system is built around a compromise with one teacher managing thirty students. Flint exists to take that compromise off the table. Personalized learning, at the scale of a whole school â every student working with something closer to a tutor, and every teacher able to see what's actually happening across their class instead of guessing. Go look at the product before you read any further: app.flintk12.com The Role Students want something that stays with them, going at their pace and helps them get unstuck without just handing over the answer. Teachers want that happening inside a class they still control, and they'd like their evenings back. Admins want proof that the platform they rolled out is leading to teacher productivity and student progress. Your job is to dive deep into this design problem, holding three sets of needs within one product. Weâll trust you to ship designs that are the best possible solution</t>
+          <t>BracknellPump Rental SolutionsBracknellPump Rental SolutionsGreat YarmouthPump Rental SolutionsNottinghamPump Rental SolutionsAberdeenPump Rental SolutionsConwyPump Rental SolutionsStokeWorkdry - Group Central ServicesStokeWorkdry - Group Central ServicesWorkingtonPump Rental Solutions Please mention the word **GREATNESS** and tag RMjAyLjY2LjE2NC42 when applying to show you read the job post completely (#RMjAyLjY2LjE2NC42). This is a beta feature to avoid spam applicants. Companies can search these words to find applicants that read this and see they're human.</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>2026-07-26T18:23:18.030686+00:00</t>
+          <t>2026-07-26T18:23:11.834056+00:00</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Join our UK team</t>
+          <t>Safety Data Analyst</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Workdry Germany</t>
+          <t>SkyWest Airlines</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Data / AI</t>
         </is>
       </c>
       <c r="E464" t="inlineStr"/>
       <c r="F464" t="inlineStr"/>
       <c r="G464" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-join-our-uk-team-workdry-germany-1135314</t>
+          <t>https://remoteOK.com/remote-jobs/remote-safety-data-analyst-skywest-airlines-1135445</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>BracknellPump Rental SolutionsBracknellPump Rental SolutionsGreat YarmouthPump Rental SolutionsNottinghamPump Rental SolutionsAberdeenPump Rental SolutionsConwyPump Rental SolutionsStokeWorkdry - Group Central ServicesStokeWorkdry - Group Central ServicesWorkingtonPump Rental Solutions Please mention the word **GREATNESS** and tag RMjAyLjY2LjE2NC42 when applying to show you read the job post completely (#RMjAyLjY2LjE2NC42). This is a beta feature to avoid spam applicants. Companies can search these words to find applicants that read this and see they're human.</t>
+          <t>About SkyWest With over 16,000 aviation professionals operating thousands of daily flights, SkyWest Airlines connects millions of passengers each month to hundreds of destinations across North America. SkyWest operates in partnership with Delta Air Lines, United Airlines, American Airlines, and Alaska Airlines and has a fleet of nearly 450 aircraft. Headquartered in St. George, Utah, SkyWest's industry-leading workforce and excellent leadership team have consistently generated solid operational and economic performance, setting the standard for excellence in the regional industry. SkyWest employees enjoy a distinctive and unmatched culture of teamwork, respect, quality, and professionalism, along with world-class benefits such as a 401(k) match, Performance Rewards, health care, retirement, and discounted travel worldwide. Primary Job Duties Analyze, compile, and report safety data to support all SkyWest safety programs. Collect, analyze, and report safety assurance data from multiple safety data sources. Identify, monitor, and communicate safety performance trends and emerging risks. Track, maintain, and report key performance indicators (KPIs) for the Safety Department, including</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>2026-07-26T18:23:11.834056+00:00</t>
+          <t>2026-07-17T10:23:01.374271+00:00</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Safety Data Analyst</t>
+          <t>Test Internship</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>SkyWest Airlines</t>
+          <t>Test Company</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>Data / AI</t>
-        </is>
-      </c>
-      <c r="E465" t="inlineStr"/>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>10,000/mo</t>
+        </is>
+      </c>
       <c r="F465" t="inlineStr"/>
       <c r="G465" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-safety-data-analyst-skywest-airlines-1135445</t>
+          <t>https://example.com</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
-        <is>
-          <t>About SkyWest With over 16,000 aviation professionals operating thousands of daily flights, SkyWest Airlines connects millions of passengers each month to hundreds of destinations across North America. SkyWest operates in partnership with Delta Air Lines, United Airlines, American Airlines, and Alaska Airlines and has a fleet of nearly 450 aircraft. Headquartered in St. George, Utah, SkyWest's industry-leading workforce and excellent leadership team have consistently generated solid operational and economic performance, setting the standard for excellence in the regional industry. SkyWest employees enjoy a distinctive and unmatched culture of teamwork, respect, quality, and professionalism, along with world-class benefits such as a 401(k) match, Performance Rewards, health care, retirement, and discounted travel worldwide. Primary Job Duties Analyze, compile, and report safety data to support all SkyWest safety programs. Collect, analyze, and report safety assurance data from multiple safety data sources. Identify, monitor, and communicate safety performance trends and emerging risks. Track, maintain, and report key performance indicators (KPIs) for the Safety Department, including</t>
-        </is>
-      </c>
-    </row>
-    <row r="466">
-      <c r="A466" t="inlineStr">
-        <is>
-          <t>2026-07-17T10:23:01.374271+00:00</t>
-        </is>
-      </c>
-      <c r="B466" t="inlineStr">
-        <is>
-          <t>Test Internship</t>
-        </is>
-      </c>
-      <c r="C466" t="inlineStr">
-        <is>
-          <t>Test Company</t>
-        </is>
-      </c>
-      <c r="D466" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E466" t="inlineStr">
-        <is>
-          <t>10,000/mo</t>
-        </is>
-      </c>
-      <c r="F466" t="inlineStr"/>
-      <c r="G466" t="inlineStr">
-        <is>
-          <t>https://example.com</t>
-        </is>
-      </c>
-      <c r="H466" t="inlineStr">
         <is>
           <t>This is a test listing</t>
         </is>

--- a/approved_jobs.xlsx
+++ b/approved_jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H788"/>
+  <dimension ref="A1:H787"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -25574,12 +25574,12 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Application Engineering Intern (Summer Internship 2027)</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Zeta</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
@@ -25590,17 +25590,17 @@
       <c r="E665" t="inlineStr"/>
       <c r="F665" t="inlineStr">
         <is>
-          <t>Bangalore - EC</t>
+          <t>Bengaluru, Karnataka, India</t>
         </is>
       </c>
       <c r="G665" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/zeta/72ee1884-8e8b-447b-ab96-aa76605b5f4a</t>
+          <t>https://bit.ly/GoogleInternSummer27</t>
         </is>
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
@@ -25612,12 +25612,12 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Application Engineering Intern (Summer Internship 2027)</t>
+          <t>2027 - Summer Internal Software Engineer Intern, Gurugram</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Mdbgeneralreferrals</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
@@ -25628,17 +25628,17 @@
       <c r="E666" t="inlineStr"/>
       <c r="F666" t="inlineStr">
         <is>
-          <t>Bengaluru, Karnataka, India</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="G666" t="inlineStr">
         <is>
-          <t>https://bit.ly/GoogleInternSummer27</t>
+          <t>https://job-boards.greenhouse.io/mdbgeneralreferrals/jobs/8127570</t>
         </is>
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>2027 - Summer Internal Software Engineer Intern, Gurugram</t>
         </is>
       </c>
     </row>
@@ -25650,12 +25650,12 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>2027 - Summer Internal Software Engineer Intern, Gurugram</t>
+          <t>Consulting Intern</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Mdbgeneralreferrals</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
@@ -25666,17 +25666,17 @@
       <c r="E667" t="inlineStr"/>
       <c r="F667" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Mexico City, Mexico</t>
         </is>
       </c>
       <c r="G667" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/mdbgeneralreferrals/jobs/8127570</t>
+          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/job/Mexico-City-Mexico/Intern_R1556962</t>
         </is>
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>2027 - Summer Internal Software Engineer Intern, Gurugram</t>
+          <t>R1556962</t>
         </is>
       </c>
     </row>
@@ -25688,33 +25688,33 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Consulting Intern</t>
+          <t>Director, Platform Engineering</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E668" t="inlineStr"/>
       <c r="F668" t="inlineStr">
         <is>
-          <t>Mexico City, Mexico</t>
+          <t>O'Fallon, Missouri</t>
         </is>
       </c>
       <c r="G668" t="inlineStr">
         <is>
-          <t>https://iqvia.wd1.myworkdayjobs.com/IQVIA/job/job/Mexico-City-Mexico/Intern_R1556962</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/OFallon-Missouri/Director--Platform-Engineering_R-273321</t>
         </is>
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>R1556962</t>
+          <t>R-273321</t>
         </is>
       </c>
     </row>
@@ -25726,7 +25726,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Director, Platform Engineering</t>
+          <t>Senior Technical Program Manager</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -25742,17 +25742,17 @@
       <c r="E669" t="inlineStr"/>
       <c r="F669" t="inlineStr">
         <is>
-          <t>O'Fallon, Missouri</t>
+          <t>Arlington, Virginia</t>
         </is>
       </c>
       <c r="G669" t="inlineStr">
         <is>
-          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/OFallon-Missouri/Director--Platform-Engineering_R-273321</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Arlington-Virginia/Senior-Technical-Program-Manager_R-282015</t>
         </is>
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>R-273321</t>
+          <t>R-282015</t>
         </is>
       </c>
     </row>
@@ -25764,7 +25764,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Senior Technical Program Manager</t>
+          <t>Lead, Product Experience Design</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -25774,23 +25774,23 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E670" t="inlineStr"/>
       <c r="F670" t="inlineStr">
         <is>
-          <t>Arlington, Virginia</t>
+          <t>O'Fallon, Missouri</t>
         </is>
       </c>
       <c r="G670" t="inlineStr">
         <is>
-          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Arlington-Virginia/Senior-Technical-Program-Manager_R-282015</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/OFallon-Missouri/Lead--Product-Experience-Design_R-280168</t>
         </is>
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>R-282015</t>
+          <t>R-280168</t>
         </is>
       </c>
     </row>
@@ -25802,7 +25802,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Lead, Product Experience Design</t>
+          <t>Director, Product Experience Design</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -25823,12 +25823,12 @@
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/OFallon-Missouri/Lead--Product-Experience-Design_R-280168</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/OFallon-Missouri/Director--Product-Experience-Design_R-280164</t>
         </is>
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>R-280168</t>
+          <t>R-280164</t>
         </is>
       </c>
     </row>
@@ -25840,7 +25840,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Director, Product Experience Design</t>
+          <t>Director, North American B2B Secular Shift Program Operations</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -25850,23 +25850,23 @@
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E672" t="inlineStr"/>
       <c r="F672" t="inlineStr">
         <is>
-          <t>O'Fallon, Missouri</t>
+          <t>Purchase, New York</t>
         </is>
       </c>
       <c r="G672" t="inlineStr">
         <is>
-          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/OFallon-Missouri/Director--Product-Experience-Design_R-280164</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Purchase-New-York/Director--North-American-B2B-Secular-Shift-Program-Operations_R-281572</t>
         </is>
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>R-280164</t>
+          <t>R-281572</t>
         </is>
       </c>
     </row>
@@ -25878,7 +25878,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Director, North American B2B Secular Shift Program Operations</t>
+          <t>Director, Project Management (AI)</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -25888,23 +25888,23 @@
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Data / AI</t>
         </is>
       </c>
       <c r="E673" t="inlineStr"/>
       <c r="F673" t="inlineStr">
         <is>
-          <t>Purchase, New York</t>
+          <t>2 Locations</t>
         </is>
       </c>
       <c r="G673" t="inlineStr">
         <is>
-          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Purchase-New-York/Director--North-American-B2B-Secular-Shift-Program-Operations_R-281572</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/OFallon-Missouri/Director--Project-Management_R-282004</t>
         </is>
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>R-281572</t>
+          <t>R-282004</t>
         </is>
       </c>
     </row>
@@ -25916,7 +25916,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>Director, Project Management (AI)</t>
+          <t>Senior Solutions Consultant, Personalization</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -25926,23 +25926,23 @@
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>Data / AI</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E674" t="inlineStr"/>
       <c r="F674" t="inlineStr">
         <is>
-          <t>2 Locations</t>
+          <t>3 Locations</t>
         </is>
       </c>
       <c r="G674" t="inlineStr">
         <is>
-          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/OFallon-Missouri/Director--Project-Management_R-282004</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Sao-Paulo-Brazil/Senior-Solutions-Consultant--Personalization_R-275745</t>
         </is>
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>R-282004</t>
+          <t>R-275745</t>
         </is>
       </c>
     </row>
@@ -25954,7 +25954,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>Senior Solutions Consultant, Personalization</t>
+          <t>Senior Counsel, Regulatory - Technology</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -25970,17 +25970,17 @@
       <c r="E675" t="inlineStr"/>
       <c r="F675" t="inlineStr">
         <is>
-          <t>3 Locations</t>
+          <t>2 Locations</t>
         </is>
       </c>
       <c r="G675" t="inlineStr">
         <is>
-          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Sao-Paulo-Brazil/Senior-Solutions-Consultant--Personalization_R-275745</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Purchase-New-York/Senior-Counsel--Regulatory---Technology_R-290617-2</t>
         </is>
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>R-275745</t>
+          <t>R-290617</t>
         </is>
       </c>
     </row>
@@ -25992,7 +25992,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>Senior Counsel, Regulatory - Technology</t>
+          <t>Director, Finance Business Partner</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -26008,17 +26008,17 @@
       <c r="E676" t="inlineStr"/>
       <c r="F676" t="inlineStr">
         <is>
-          <t>2 Locations</t>
+          <t>3 Locations</t>
         </is>
       </c>
       <c r="G676" t="inlineStr">
         <is>
-          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Purchase-New-York/Senior-Counsel--Regulatory---Technology_R-290617-2</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Miami-Florida/Director--Finance-Business-Partner_R-281187</t>
         </is>
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>R-290617</t>
+          <t>R-281187</t>
         </is>
       </c>
     </row>
@@ -26030,7 +26030,7 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>Director, Finance Business Partner</t>
+          <t>Manager, Authentication Product Management-2</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -26046,17 +26046,17 @@
       <c r="E677" t="inlineStr"/>
       <c r="F677" t="inlineStr">
         <is>
-          <t>3 Locations</t>
+          <t>Warsaw, Poland</t>
         </is>
       </c>
       <c r="G677" t="inlineStr">
         <is>
-          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Miami-Florida/Director--Finance-Business-Partner_R-281187</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Warsaw-Poland/Manager--Authentication-Product-Management-2_R-290606</t>
         </is>
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>R-281187</t>
+          <t>R-290606</t>
         </is>
       </c>
     </row>
@@ -26068,7 +26068,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Manager, Authentication Product Management-2</t>
+          <t>Consultant, Program Management, Advisors &amp; Consulting Service</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -26084,17 +26084,17 @@
       <c r="E678" t="inlineStr"/>
       <c r="F678" t="inlineStr">
         <is>
-          <t>Warsaw, Poland</t>
+          <t>Sao Paulo, Brazil</t>
         </is>
       </c>
       <c r="G678" t="inlineStr">
         <is>
-          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Warsaw-Poland/Manager--Authentication-Product-Management-2_R-290606</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Sao-Paulo-Brazil/Consultant--Program-Management--Advisors---Consulting-Service_R-276150</t>
         </is>
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>R-290606</t>
+          <t>R-276150</t>
         </is>
       </c>
     </row>
@@ -26106,7 +26106,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Consultant, Program Management, Advisors &amp; Consulting Service</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -26116,23 +26116,23 @@
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Data / AI</t>
         </is>
       </c>
       <c r="E679" t="inlineStr"/>
       <c r="F679" t="inlineStr">
         <is>
-          <t>Sao Paulo, Brazil</t>
+          <t>O'Fallon, Missouri</t>
         </is>
       </c>
       <c r="G679" t="inlineStr">
         <is>
-          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Sao-Paulo-Brazil/Consultant--Program-Management--Advisors---Consulting-Service_R-276150</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/OFallon-Missouri/Senior-Data-Engineer_R-288332-1</t>
         </is>
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>R-276150</t>
+          <t>R-288332</t>
         </is>
       </c>
     </row>
@@ -26144,7 +26144,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Intelligence Analyst</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -26154,23 +26154,23 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>Data / AI</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E680" t="inlineStr"/>
       <c r="F680" t="inlineStr">
         <is>
-          <t>O'Fallon, Missouri</t>
+          <t>Dubai, United Arab Emirates</t>
         </is>
       </c>
       <c r="G680" t="inlineStr">
         <is>
-          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/OFallon-Missouri/Senior-Data-Engineer_R-288332-1</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Dubai-United-Arab-Emirates/Senior-Intelligence-Analyst_R-289820-1</t>
         </is>
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>R-288332</t>
+          <t>R-289820</t>
         </is>
       </c>
     </row>
@@ -26182,7 +26182,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Senior Intelligence Analyst</t>
+          <t>Manager, Specialist Sales, SME Solutions Northern Europe</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -26192,23 +26192,23 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E681" t="inlineStr"/>
       <c r="F681" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>6 Locations</t>
         </is>
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Dubai-United-Arab-Emirates/Senior-Intelligence-Analyst_R-289820-1</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Helsinki-Finland/Manager--Specialist-Sales--SME-Solutions-Northern-Europe_R-289760</t>
         </is>
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>R-289820</t>
+          <t>R-289760</t>
         </is>
       </c>
     </row>
@@ -26220,7 +26220,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Manager, Specialist Sales, SME Solutions Northern Europe</t>
+          <t>Manager, Product Management - MDES Localization</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -26230,23 +26230,23 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E682" t="inlineStr"/>
       <c r="F682" t="inlineStr">
         <is>
-          <t>6 Locations</t>
+          <t>2 Locations</t>
         </is>
       </c>
       <c r="G682" t="inlineStr">
         <is>
-          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Helsinki-Finland/Manager--Specialist-Sales--SME-Solutions-Northern-Europe_R-289760</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/OFallon-Missouri/Manager--Product-Management---MDES-Localization_R-290229</t>
         </is>
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>R-289760</t>
+          <t>R-290229</t>
         </is>
       </c>
     </row>
@@ -26258,7 +26258,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Manager, Product Management - MDES Localization</t>
+          <t>Senior Specialist, Product Development</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -26274,17 +26274,17 @@
       <c r="E683" t="inlineStr"/>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2 Locations</t>
+          <t>Toronto, Canada (Ethoca)</t>
         </is>
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/OFallon-Missouri/Manager--Product-Management---MDES-Localization_R-290229</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Toronto-Canada-Ethoca/Manager--Product-Development--Dispute-Product-_R-284467</t>
         </is>
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>R-290229</t>
+          <t>R-284467</t>
         </is>
       </c>
     </row>
@@ -26296,7 +26296,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Senior Specialist, Product Development</t>
+          <t>Director Business Analysis</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -26312,122 +26312,118 @@
       <c r="E684" t="inlineStr"/>
       <c r="F684" t="inlineStr">
         <is>
-          <t>Toronto, Canada (Ethoca)</t>
+          <t>O'Fallon, Missouri</t>
         </is>
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/Toronto-Canada-Ethoca/Manager--Product-Development--Dispute-Product-_R-284467</t>
+          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/OFallon-Missouri/Director-Business-Analysis_R-288845-1</t>
         </is>
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>R-284467</t>
+          <t>R-288845</t>
         </is>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>2026-09-16T11:53:22.888535+00:00</t>
+          <t>2026-09-06T18:32:12.802999+00:00</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Director Business Analysis</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E685" t="inlineStr"/>
       <c r="F685" t="inlineStr">
         <is>
-          <t>O'Fallon, Missouri</t>
+          <t>Bengaluru-VTP, India</t>
         </is>
       </c>
       <c r="G685" t="inlineStr">
         <is>
-          <t>https://mastercard.wd1.myworkdayjobs.com/CorporateCareers/job/job/OFallon-Missouri/Director-Business-Analysis_R-288845-1</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
         </is>
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>R-288845</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>2026-09-06T18:32:12.802999+00:00</t>
+          <t>2026-09-06T18:32:11.785346+00:00</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Generalist</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E686" t="inlineStr"/>
-      <c r="F686" t="inlineStr">
-        <is>
-          <t>Bengaluru-VTP, India</t>
-        </is>
-      </c>
+      <c r="F686" t="inlineStr"/>
       <c r="G686" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
+          <t>https://bit.ly/4A1zUSE</t>
         </is>
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>2026-09-06T18:32:11.785346+00:00</t>
+          <t>2026-09-06T18:32:09.855425+00:00</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Generalist</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E687" t="inlineStr"/>
       <c r="F687" t="inlineStr"/>
       <c r="G687" t="inlineStr">
         <is>
-          <t>https://bit.ly/4A1zUSE</t>
+          <t>https://hccz.fa.em3.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_2/job/25450</t>
         </is>
       </c>
       <c r="H687" t="inlineStr">
@@ -26439,7 +26435,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>2026-09-06T18:32:09.855425+00:00</t>
+          <t>2026-09-06T18:32:09.765669+00:00</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
@@ -26449,7 +26445,7 @@
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
@@ -26461,7 +26457,7 @@
       <c r="F688" t="inlineStr"/>
       <c r="G688" t="inlineStr">
         <is>
-          <t>https://hccz.fa.em3.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_2/job/25450</t>
+          <t>https://careers.cargill.com/en/job/-/-/23251/100079360032</t>
         </is>
       </c>
       <c r="H688" t="inlineStr">
@@ -26473,17 +26469,17 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>2026-09-06T18:32:09.765669+00:00</t>
+          <t>2026-09-06T18:32:08.510234+00:00</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>SDE Intern</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Spyne</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
@@ -26495,7 +26491,7 @@
       <c r="F689" t="inlineStr"/>
       <c r="G689" t="inlineStr">
         <is>
-          <t>https://careers.cargill.com/en/job/-/-/23251/100079360032</t>
+          <t>https://spyneai.keka.com/careers/jobdetails/156605</t>
         </is>
       </c>
       <c r="H689" t="inlineStr">
@@ -26507,84 +26503,88 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>2026-09-06T18:32:08.510234+00:00</t>
+          <t>2026-09-06T18:32:08.206959+00:00</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>SDE Intern</t>
+          <t>YouTube &amp; Content - Internship</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Spyne</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E690" t="inlineStr"/>
-      <c r="F690" t="inlineStr"/>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>Bengaluru-VTP, India</t>
+        </is>
+      </c>
       <c r="G690" t="inlineStr">
         <is>
-          <t>https://spyneai.keka.com/careers/jobdetails/156605</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
         </is>
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>YouTube &amp; Content - Internship</t>
         </is>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>2026-09-06T18:32:08.206959+00:00</t>
+          <t>2026-09-06T18:30:59.524083+00:00</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>YouTube &amp; Content - Internship</t>
+          <t>Frontend Engineer</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="E691" t="inlineStr"/>
       <c r="F691" t="inlineStr">
         <is>
-          <t>Bengaluru-VTP, India</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="G691" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
+          <t>https://bit.ly/4i9Esjd</t>
         </is>
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t>YouTube &amp; Content - Internship</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:59.524083+00:00</t>
+          <t>2026-09-06T18:30:57.840717+00:00</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Frontend Engineer</t>
+          <t>Visual Designer</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -26594,7 +26594,7 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E692" t="inlineStr"/>
@@ -26605,7 +26605,7 @@
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>https://bit.ly/4i9Esjd</t>
+          <t>https://bit.ly/4ye7bbp</t>
         </is>
       </c>
       <c r="H692" t="inlineStr">
@@ -26617,12 +26617,12 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:57.840717+00:00</t>
+          <t>2026-09-06T18:30:56.243151+00:00</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Visual Designer</t>
+          <t>UX Designer</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -26643,7 +26643,7 @@
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>https://bit.ly/4ye7bbp</t>
+          <t>https://bit.ly/4wWLfQV</t>
         </is>
       </c>
       <c r="H693" t="inlineStr">
@@ -26655,12 +26655,12 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:56.243151+00:00</t>
+          <t>2026-09-06T18:30:54.557526+00:00</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>UX Designer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -26670,7 +26670,7 @@
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Data / AI</t>
         </is>
       </c>
       <c r="E694" t="inlineStr"/>
@@ -26681,7 +26681,7 @@
       </c>
       <c r="G694" t="inlineStr">
         <is>
-          <t>https://bit.ly/4wWLfQV</t>
+          <t>https://bit.ly/3Usl5bu</t>
         </is>
       </c>
       <c r="H694" t="inlineStr">
@@ -26693,109 +26693,109 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:54.557526+00:00</t>
+          <t>2026-09-06T18:30:51.717612+00:00</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Quantitative Developer Intern</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Towerresearchcapital</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>Data / AI</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E695" t="inlineStr"/>
       <c r="F695" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G695" t="inlineStr">
         <is>
-          <t>https://bit.ly/3Usl5bu</t>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=7011493</t>
         </is>
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>Quantitative Developer Intern</t>
         </is>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:51.717612+00:00</t>
+          <t>2026-09-06T18:30:47.137206+00:00</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Quantitative Developer Intern</t>
+          <t>Product Designer</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Towerresearchcapital</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E696" t="inlineStr"/>
       <c r="F696" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="G696" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=7011493</t>
+          <t>https://bit.ly/4xuqIEp</t>
         </is>
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>Quantitative Developer Intern</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:47.137206+00:00</t>
+          <t>2026-09-06T18:30:45.345284+00:00</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Product Designer</t>
+          <t>SDE1</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Hevo Data</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E697" t="inlineStr"/>
       <c r="F697" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t>https://bit.ly/4xuqIEp</t>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSdUXEWZMGd9k4A_Thkhl_tya1Zcu5ROnWP9SjMKhHSQzKUGog/viewform</t>
         </is>
       </c>
       <c r="H697" t="inlineStr">
@@ -26807,109 +26807,109 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:45.345284+00:00</t>
+          <t>2026-09-06T18:30:42.493975+00:00</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>SDE1</t>
+          <t>Quantitative Trader/Researcher Summer Internship 2027 (2028 Graduates)</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>Hevo Data</t>
+          <t>Towerresearchcapital</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E698" t="inlineStr"/>
       <c r="F698" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>London</t>
         </is>
       </c>
       <c r="G698" t="inlineStr">
         <is>
-          <t>https://docs.google.com/forms/d/e/1FAIpQLSdUXEWZMGd9k4A_Thkhl_tya1Zcu5ROnWP9SjMKhHSQzKUGog/viewform</t>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=8037860</t>
         </is>
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>Quantitative Trader/Researcher Summer Internship 2027 (2028 Graduates)</t>
         </is>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:42.493975+00:00</t>
+          <t>2026-09-06T18:30:39.619912+00:00</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Quantitative Trader/Researcher Summer Internship 2027 (2028 Graduates)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Towerresearchcapital</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E699" t="inlineStr"/>
       <c r="F699" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Remote (Work From Home)</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=8037860</t>
+          <t>https://bit.ly/4guHNbm</t>
         </is>
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>Quantitative Trader/Researcher Summer Internship 2027 (2028 Graduates)</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:39.619912+00:00</t>
+          <t>2026-09-06T18:30:37.644164+00:00</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Fullstack Engineer Intern</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Gesture</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="E700" t="inlineStr"/>
       <c r="F700" t="inlineStr">
         <is>
-          <t>Remote (Work From Home)</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="G700" t="inlineStr">
         <is>
-          <t>https://bit.ly/4guHNbm</t>
+          <t>https://jobs.gusto.com/postings/gesture-us-inc-ai-full-stack-engineer-intern-e6b31003-155a-48dd-a442-a664809ff969</t>
         </is>
       </c>
       <c r="H700" t="inlineStr">
@@ -26921,50 +26921,50 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:37.644164+00:00</t>
+          <t>2026-09-06T18:30:32.212932+00:00</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>AI Fullstack Engineer Intern</t>
+          <t>Quantitative Researcher Intern, Bachelor or Master</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>Gesture</t>
+          <t>Towerresearchcapital</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E701" t="inlineStr"/>
       <c r="F701" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Singapore, Hong Kong, Shanghai, Sydney</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
         <is>
-          <t>https://jobs.gusto.com/postings/gesture-us-inc-ai-full-stack-engineer-intern-e6b31003-155a-48dd-a442-a664809ff969</t>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=8168750</t>
         </is>
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>Quantitative Researcher Intern, Bachelor or Master</t>
         </is>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:32.212932+00:00</t>
+          <t>2026-09-06T18:30:29.806106+00:00</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Quantitative Researcher Intern, Bachelor or Master</t>
+          <t>Quantitative Researcher Intern, PhD or Postdoc</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -26985,79 +26985,79 @@
       </c>
       <c r="G702" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=8168750</t>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=8168634</t>
         </is>
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>Quantitative Researcher Intern, Bachelor or Master</t>
+          <t>Quantitative Researcher Intern, PhD or Postdoc</t>
         </is>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:29.806106+00:00</t>
+          <t>2026-09-06T18:30:23.45402+00:00</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Quantitative Researcher Intern, PhD or Postdoc</t>
+          <t>Tata Imagination Challenge</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>Towerresearchcapital</t>
+          <t>Tata</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E703" t="inlineStr"/>
-      <c r="F703" t="inlineStr">
-        <is>
-          <t>Singapore, Hong Kong, Shanghai, Sydney</t>
-        </is>
-      </c>
+      <c r="F703" t="inlineStr"/>
       <c r="G703" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=8168634</t>
+          <t>https://bit.ly/TataChallenge2026</t>
         </is>
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>Quantitative Researcher Intern, PhD or Postdoc</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:23.45402+00:00</t>
+          <t>2026-09-06T18:30:10.428183+00:00</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>Tata Imagination Challenge</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Tata</t>
+          <t>Weekday works</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E704" t="inlineStr"/>
-      <c r="F704" t="inlineStr"/>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="G704" t="inlineStr">
         <is>
-          <t>https://bit.ly/TataChallenge2026</t>
+          <t>https://jobs.lever.co/weekdayworks/a86efff4-1c2e-43fc-8ecb-dc8f873db2f1</t>
         </is>
       </c>
       <c r="H704" t="inlineStr">
@@ -27069,33 +27069,29 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>2026-09-06T18:30:10.428183+00:00</t>
+          <t>2026-09-06T18:29:59.581469+00:00</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Fullstack Developer Intern</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Weekday works</t>
+          <t>Amber</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="E705" t="inlineStr"/>
-      <c r="F705" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="F705" t="inlineStr"/>
       <c r="G705" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/weekdayworks/a86efff4-1c2e-43fc-8ecb-dc8f873db2f1</t>
+          <t>https://amberstudent.keka.com/careers/jobdetails/140686</t>
         </is>
       </c>
       <c r="H705" t="inlineStr">
@@ -27107,29 +27103,33 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>2026-09-06T18:29:59.581469+00:00</t>
+          <t>2026-09-06T18:29:55.077161+00:00</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>Fullstack Developer Intern</t>
+          <t>Video Annotation Specialist</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>Amber</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E706" t="inlineStr"/>
-      <c r="F706" t="inlineStr"/>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="G706" t="inlineStr">
         <is>
-          <t>https://amberstudent.keka.com/careers/jobdetails/140686</t>
+          <t>https://bit.ly/4ienwrP</t>
         </is>
       </c>
       <c r="H706" t="inlineStr">
@@ -27141,7 +27141,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>2026-09-06T18:29:55.077161+00:00</t>
+          <t>2026-09-06T18:29:52.586654+00:00</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
@@ -27179,12 +27179,12 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>2026-09-06T18:29:52.586654+00:00</t>
+          <t>2026-09-06T18:29:50.197001+00:00</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Video Annotation Specialist</t>
+          <t>Generalist</t>
         </is>
       </c>
       <c r="C708" t="inlineStr">
@@ -27205,7 +27205,7 @@
       </c>
       <c r="G708" t="inlineStr">
         <is>
-          <t>https://bit.ly/4ienwrP</t>
+          <t>https://bit.ly/4A1zUSE</t>
         </is>
       </c>
       <c r="H708" t="inlineStr">
@@ -27217,33 +27217,29 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>2026-09-06T18:29:50.197001+00:00</t>
+          <t>2026-09-06T18:29:46.570284+00:00</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>Generalist</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Anakin</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E709" t="inlineStr"/>
-      <c r="F709" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="F709" t="inlineStr"/>
       <c r="G709" t="inlineStr">
         <is>
-          <t>https://bit.ly/4A1zUSE</t>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSePeI5SrB8J3suBCknPymGNWFzvp-0xVoLR4eW4umoYj2y-CA/viewform</t>
         </is>
       </c>
       <c r="H709" t="inlineStr">
@@ -27255,17 +27251,17 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>2026-09-06T18:29:46.570284+00:00</t>
+          <t>2026-08-29T13:47:20.141291+00:00</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Engineering Intern</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Anakin</t>
+          <t>CoinDCX</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
@@ -27277,7 +27273,7 @@
       <c r="F710" t="inlineStr"/>
       <c r="G710" t="inlineStr">
         <is>
-          <t>https://docs.google.com/forms/d/e/1FAIpQLSePeI5SrB8J3suBCknPymGNWFzvp-0xVoLR4eW4umoYj2y-CA/viewform</t>
+          <t>https://bit.ly/4gaN1ry</t>
         </is>
       </c>
       <c r="H710" t="inlineStr">
@@ -27289,17 +27285,17 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>2026-08-29T13:47:20.141291+00:00</t>
+          <t>2026-08-29T13:47:17.751204+00:00</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Engineering Intern</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>CoinDCX</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
@@ -27311,7 +27307,7 @@
       <c r="F711" t="inlineStr"/>
       <c r="G711" t="inlineStr">
         <is>
-          <t>https://bit.ly/4gaN1ry</t>
+          <t>https://bit.ly/3SdzZBE</t>
         </is>
       </c>
       <c r="H711" t="inlineStr">
@@ -27323,29 +27319,29 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>2026-08-29T13:47:17.751204+00:00</t>
+          <t>2026-08-29T13:47:14.843938+00:00</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Tata Challenge 2026</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Tata</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E712" t="inlineStr"/>
       <c r="F712" t="inlineStr"/>
       <c r="G712" t="inlineStr">
         <is>
-          <t>https://bit.ly/3SdzZBE</t>
+          <t>https://bit.ly/TataChallenge2026</t>
         </is>
       </c>
       <c r="H712" t="inlineStr">
@@ -27357,12 +27353,12 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>2026-08-29T13:47:14.843938+00:00</t>
+          <t>2026-08-29T13:47:11.897733+00:00</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>Tata Challenge 2026</t>
+          <t>Tata Imagination Challenge</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -27391,29 +27387,29 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>2026-08-29T13:47:11.897733+00:00</t>
+          <t>2026-08-29T13:47:10.137948+00:00</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>Tata Imagination Challenge</t>
+          <t>Software Engineering Intern (Summer Internship)</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>Tata</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E714" t="inlineStr"/>
       <c r="F714" t="inlineStr"/>
       <c r="G714" t="inlineStr">
         <is>
-          <t>https://bit.ly/TataChallenge2026</t>
+          <t>https://bit.ly/3SdzZBE</t>
         </is>
       </c>
       <c r="H714" t="inlineStr">
@@ -27425,105 +27421,105 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>2026-08-29T13:47:10.137948+00:00</t>
+          <t>2026-08-29T13:47:07.044183+00:00</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (Summer Internship)</t>
+          <t>Product Marketing Manager, International Markets &amp; Family Offices</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Addepar1</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E715" t="inlineStr"/>
-      <c r="F715" t="inlineStr"/>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>Remote, USA</t>
+        </is>
+      </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>https://bit.ly/3SdzZBE</t>
+          <t>https://job-boards.greenhouse.io/addepar1/jobs/8744007002</t>
         </is>
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>Product Marketing Manager, International Markets &amp; Family Offices</t>
         </is>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>2026-08-29T13:47:07.044183+00:00</t>
+          <t>2026-08-29T13:47:01.689263+00:00</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>Product Marketing Manager, International Markets &amp; Family Offices</t>
+          <t>AI Engineering Intern</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>Addepar1</t>
+          <t>Unisys</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Data / AI</t>
         </is>
       </c>
       <c r="E716" t="inlineStr"/>
       <c r="F716" t="inlineStr">
         <is>
-          <t>Remote, USA</t>
+          <t>Bangalore, KA, India</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/addepar1/jobs/8744007002</t>
+          <t>https://unisys.wd5.myworkdayjobs.com/External/job/Bangalore-KA-India/AI-Engineering-Intern_REQ574280?source=KrishanKumarLinkedin</t>
         </is>
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>Product Marketing Manager, International Markets &amp; Family Offices</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>2026-08-29T13:47:01.689263+00:00</t>
+          <t>2026-08-25T14:24:11.044632+00:00</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>AI Engineering Intern</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>Unisys</t>
+          <t>Enterpret</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>Data / AI</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E717" t="inlineStr"/>
-      <c r="F717" t="inlineStr">
-        <is>
-          <t>Bangalore, KA, India</t>
-        </is>
-      </c>
+      <c r="F717" t="inlineStr"/>
       <c r="G717" t="inlineStr">
         <is>
-          <t>https://unisys.wd5.myworkdayjobs.com/External/job/Bangalore-KA-India/AI-Engineering-Intern_REQ574280?source=KrishanKumarLinkedin</t>
+          <t>https://job-boards.greenhouse.io/enterpret/jobs/7847134003</t>
         </is>
       </c>
       <c r="H717" t="inlineStr">
@@ -27535,29 +27531,33 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>2026-08-25T14:24:11.044632+00:00</t>
+          <t>2026-08-25T14:24:07.705529+00:00</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>Enterpret</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Data / AI</t>
         </is>
       </c>
       <c r="E718" t="inlineStr"/>
-      <c r="F718" t="inlineStr"/>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
       <c r="G718" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/enterpret/jobs/7847134003</t>
+          <t>https://bit.ly/45LFHxK</t>
         </is>
       </c>
       <c r="H718" t="inlineStr">
@@ -27569,12 +27569,12 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>2026-08-25T14:24:07.705529+00:00</t>
+          <t>2026-08-25T14:23:37.191168+00:00</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>MCP Expert</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
@@ -27584,7 +27584,7 @@
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>Data / AI</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E719" t="inlineStr"/>
@@ -27595,7 +27595,7 @@
       </c>
       <c r="G719" t="inlineStr">
         <is>
-          <t>https://bit.ly/45LFHxK</t>
+          <t>https://bit.ly/4wJiMOk</t>
         </is>
       </c>
       <c r="H719" t="inlineStr">
@@ -27607,33 +27607,29 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>2026-08-25T14:23:37.191168+00:00</t>
+          <t>2026-08-25T14:23:33.82492+00:00</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>MCP Expert</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E720" t="inlineStr"/>
-      <c r="F720" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="F720" t="inlineStr"/>
       <c r="G720" t="inlineStr">
         <is>
-          <t>https://bit.ly/4wJiMOk</t>
+          <t>https://careers.hpe.com/us/en/job/1211844/Intern</t>
         </is>
       </c>
       <c r="H720" t="inlineStr">
@@ -27645,17 +27641,17 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>2026-08-25T14:23:33.82492+00:00</t>
+          <t>2026-08-25T14:22:34.800573+00:00</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>DevOps Intern</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>Cloudsek</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
@@ -27664,65 +27660,69 @@
         </is>
       </c>
       <c r="E721" t="inlineStr"/>
-      <c r="F721" t="inlineStr"/>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>Bengaluru, Karnataka, India</t>
+        </is>
+      </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>https://careers.hpe.com/us/en/job/1211844/Intern</t>
+          <t>https://job-boards.greenhouse.io/cloudsek/jobs/6149788004</t>
         </is>
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>DevOps Intern</t>
         </is>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>2026-08-25T14:22:34.800573+00:00</t>
+          <t>2026-08-25T14:22:23.10638+00:00</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>DevOps Intern</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>Cloudsek</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E722" t="inlineStr"/>
       <c r="F722" t="inlineStr">
         <is>
-          <t>Bengaluru, Karnataka, India</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/cloudsek/jobs/6149788004</t>
+          <t>https://bit.ly/45nkUAn</t>
         </is>
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>DevOps Intern</t>
+          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
         </is>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>2026-08-25T14:22:23.10638+00:00</t>
+          <t>2026-08-25T14:22:21.002594+00:00</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Frontend Engineer</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -27732,7 +27732,7 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="E723" t="inlineStr"/>
@@ -27743,7 +27743,7 @@
       </c>
       <c r="G723" t="inlineStr">
         <is>
-          <t>https://bit.ly/45nkUAn</t>
+          <t>https://bit.ly/4qkLIuH</t>
         </is>
       </c>
       <c r="H723" t="inlineStr">
@@ -27755,12 +27755,12 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>2026-08-25T14:22:21.002594+00:00</t>
+          <t>2026-08-25T14:22:16.887203+00:00</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>Frontend Engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -27770,7 +27770,7 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="E724" t="inlineStr"/>
@@ -27781,7 +27781,7 @@
       </c>
       <c r="G724" t="inlineStr">
         <is>
-          <t>https://bit.ly/4qkLIuH</t>
+          <t>https://bit.ly/4wZ8B9r</t>
         </is>
       </c>
       <c r="H724" t="inlineStr">
@@ -27793,12 +27793,12 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>2026-08-25T14:22:16.887203+00:00</t>
+          <t>2026-08-25T14:22:13.458112+00:00</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Fullstack Developer</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -27808,7 +27808,7 @@
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="E725" t="inlineStr"/>
@@ -27819,7 +27819,7 @@
       </c>
       <c r="G725" t="inlineStr">
         <is>
-          <t>https://bit.ly/4wZ8B9r</t>
+          <t>https://bit.ly/3Sy7PRO</t>
         </is>
       </c>
       <c r="H725" t="inlineStr">
@@ -27831,12 +27831,12 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>2026-08-25T14:22:13.458112+00:00</t>
+          <t>2026-08-25T14:22:10.397388+00:00</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>Fullstack Developer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -27846,7 +27846,7 @@
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E726" t="inlineStr"/>
@@ -27857,7 +27857,7 @@
       </c>
       <c r="G726" t="inlineStr">
         <is>
-          <t>https://bit.ly/3Sy7PRO</t>
+          <t>https://bit.ly/4gebHAv</t>
         </is>
       </c>
       <c r="H726" t="inlineStr">
@@ -27869,22 +27869,22 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>2026-08-25T14:22:10.397388+00:00</t>
+          <t>2026-08-22T12:33:35.076089+00:00</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Backend Intern</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Smallcase</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="E727" t="inlineStr"/>
@@ -27895,7 +27895,7 @@
       </c>
       <c r="G727" t="inlineStr">
         <is>
-          <t>https://bit.ly/4gebHAv</t>
+          <t>https://app.pyjamahr.com/careers?company=smallcase&amp;job_id=256252&amp;company_uuid=2615584222</t>
         </is>
       </c>
       <c r="H727" t="inlineStr">
@@ -27907,33 +27907,33 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>2026-08-22T12:33:35.076089+00:00</t>
+          <t>2026-08-22T12:33:28.837146+00:00</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Backend Intern</t>
+          <t>Frontend Engineer</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Smallcase</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="E728" t="inlineStr"/>
       <c r="F728" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote (Work From Home)</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
         <is>
-          <t>https://app.pyjamahr.com/careers?company=smallcase&amp;job_id=256252&amp;company_uuid=2615584222</t>
+          <t>https://bit.ly/4qkLIuH</t>
         </is>
       </c>
       <c r="H728" t="inlineStr">
@@ -27945,12 +27945,12 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>2026-08-22T12:33:28.837146+00:00</t>
+          <t>2026-08-22T12:33:26.419583+00:00</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Frontend Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -27960,7 +27960,7 @@
       </c>
       <c r="D729" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E729" t="inlineStr"/>
@@ -27971,7 +27971,7 @@
       </c>
       <c r="G729" t="inlineStr">
         <is>
-          <t>https://bit.ly/4qkLIuH</t>
+          <t>https://bit.ly/45nkUAn</t>
         </is>
       </c>
       <c r="H729" t="inlineStr">
@@ -27983,12 +27983,12 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>2026-08-22T12:33:26.419583+00:00</t>
+          <t>2026-08-22T12:33:20.104134+00:00</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>AI Facial Data Collection Contributor</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -27998,18 +27998,18 @@
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Data / AI</t>
         </is>
       </c>
       <c r="E730" t="inlineStr"/>
       <c r="F730" t="inlineStr">
         <is>
-          <t>Remote (Work From Home)</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
         <is>
-          <t>https://bit.ly/45nkUAn</t>
+          <t>https://bit.ly/4gbo4vO</t>
         </is>
       </c>
       <c r="H730" t="inlineStr">
@@ -28021,33 +28021,29 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>2026-08-22T12:33:20.104134+00:00</t>
+          <t>2026-08-22T12:33:05.251094+00:00</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>AI Facial Data Collection Contributor</t>
+          <t>Software Engineering Intern (Summer)</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>Data / AI</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E731" t="inlineStr"/>
-      <c r="F731" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
+      <c r="F731" t="inlineStr"/>
       <c r="G731" t="inlineStr">
         <is>
-          <t>https://bit.ly/4gbo4vO</t>
+          <t>https://www.salesforce.com/company/careers/jobs/JR337715/summer-2027-intern-software-engineer/</t>
         </is>
       </c>
       <c r="H731" t="inlineStr">
@@ -28059,29 +28055,33 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>2026-08-22T12:33:05.251094+00:00</t>
+          <t>2026-08-22T12:33:03.503245+00:00</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Software Engineering Intern (Summer)</t>
+          <t>Backend Java Developer</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="E732" t="inlineStr"/>
-      <c r="F732" t="inlineStr"/>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>Remote (Work From Home)</t>
+        </is>
+      </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t>https://www.salesforce.com/company/careers/jobs/JR337715/summer-2027-intern-software-engineer/</t>
+          <t>https://bit.ly/4wRJpkA</t>
         </is>
       </c>
       <c r="H732" t="inlineStr">
@@ -28093,33 +28093,29 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>2026-08-22T12:33:03.503245+00:00</t>
+          <t>2026-08-22T12:33:01.650538+00:00</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Backend Java Developer</t>
+          <t>Data Analyst Intern</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>SWIFT</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Data / AI</t>
         </is>
       </c>
       <c r="E733" t="inlineStr"/>
-      <c r="F733" t="inlineStr">
-        <is>
-          <t>Remote (Work From Home)</t>
-        </is>
-      </c>
+      <c r="F733" t="inlineStr"/>
       <c r="G733" t="inlineStr">
         <is>
-          <t>https://bit.ly/4wRJpkA</t>
+          <t>https://goswift.keka.com/careers/jobdetails/153432</t>
         </is>
       </c>
       <c r="H733" t="inlineStr">
@@ -28131,29 +28127,29 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>2026-08-22T12:33:01.650538+00:00</t>
+          <t>2026-08-22T12:32:54.751872+00:00</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Data Analyst Intern</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>SWIFT</t>
+          <t>Harman</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>Data / AI</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E734" t="inlineStr"/>
       <c r="F734" t="inlineStr"/>
       <c r="G734" t="inlineStr">
         <is>
-          <t>https://goswift.keka.com/careers/jobdetails/153432</t>
+          <t>https://jobsearch.harman.com/en_US/careers/searchjobs/R-54623-2026</t>
         </is>
       </c>
       <c r="H734" t="inlineStr">
@@ -28165,29 +28161,33 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>2026-08-22T12:32:54.751872+00:00</t>
+          <t>2026-08-22T12:32:52.811769+00:00</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>AI Facial Data Collection Contributor</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>Harman</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Data / AI</t>
         </is>
       </c>
       <c r="E735" t="inlineStr"/>
-      <c r="F735" t="inlineStr"/>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>Remote (Work From Home)</t>
+        </is>
+      </c>
       <c r="G735" t="inlineStr">
         <is>
-          <t>https://jobsearch.harman.com/en_US/careers/searchjobs/R-54623-2026</t>
+          <t>https://bit.ly/4hl4Ar1</t>
         </is>
       </c>
       <c r="H735" t="inlineStr">
@@ -28199,12 +28199,12 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>2026-08-22T12:32:52.811769+00:00</t>
+          <t>2026-08-22T12:32:50.619505+00:00</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>AI Facial Data Collection Contributor</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
@@ -28214,7 +28214,7 @@
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>Data / AI</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E736" t="inlineStr"/>
@@ -28225,7 +28225,7 @@
       </c>
       <c r="G736" t="inlineStr">
         <is>
-          <t>https://bit.ly/4hl4Ar1</t>
+          <t>https://bit.ly/4hH3q9A</t>
         </is>
       </c>
       <c r="H736" t="inlineStr">
@@ -28237,17 +28237,17 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>2026-08-22T12:32:50.619505+00:00</t>
+          <t>2026-08-22T12:32:48.755864+00:00</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer - AMTS</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
@@ -28258,12 +28258,12 @@
       <c r="E737" t="inlineStr"/>
       <c r="F737" t="inlineStr">
         <is>
-          <t>Remote (Work From Home)</t>
+          <t>Hyderabad/Bangalore, India</t>
         </is>
       </c>
       <c r="G737" t="inlineStr">
         <is>
-          <t>https://bit.ly/4hH3q9A</t>
+          <t>https://bit.ly/4xGBIOS</t>
         </is>
       </c>
       <c r="H737" t="inlineStr">
@@ -28275,33 +28275,33 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>2026-08-22T12:32:48.755864+00:00</t>
+          <t>2026-08-22T12:32:43.264285+00:00</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Software Engineer - AMTS</t>
+          <t>Fullstack Developer</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="E738" t="inlineStr"/>
       <c r="F738" t="inlineStr">
         <is>
-          <t>Hyderabad/Bangalore, India</t>
+          <t>Remote (Work From Home)</t>
         </is>
       </c>
       <c r="G738" t="inlineStr">
         <is>
-          <t>https://bit.ly/4xGBIOS</t>
+          <t>https://bit.ly/3Sy7PRO</t>
         </is>
       </c>
       <c r="H738" t="inlineStr">
@@ -28313,12 +28313,12 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>2026-08-22T12:32:43.264285+00:00</t>
+          <t>2026-08-22T12:32:40.571545+00:00</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Fullstack Developer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -28328,7 +28328,7 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="E739" t="inlineStr"/>
@@ -28339,7 +28339,7 @@
       </c>
       <c r="G739" t="inlineStr">
         <is>
-          <t>https://bit.ly/3Sy7PRO</t>
+          <t>https://bit.ly/4wZ8B9r</t>
         </is>
       </c>
       <c r="H739" t="inlineStr">
@@ -28351,50 +28351,50 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>2026-08-22T12:32:40.571545+00:00</t>
+          <t>2026-08-21T18:33:37.259219+00:00</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Intern - AI/ML</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Towerresearchcapital</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Data / AI</t>
         </is>
       </c>
       <c r="E740" t="inlineStr"/>
       <c r="F740" t="inlineStr">
         <is>
-          <t>Remote (Work From Home)</t>
+          <t>gurgaon</t>
         </is>
       </c>
       <c r="G740" t="inlineStr">
         <is>
-          <t>https://bit.ly/4wZ8B9r</t>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=8143756</t>
         </is>
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>Found via Telegram channel @jobs_and_internships_updates. Verify details before approving.</t>
+          <t>Intern - AI/ML</t>
         </is>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>2026-08-21T18:33:37.259219+00:00</t>
+          <t>2026-08-21T18:33:33.878834+00:00</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Intern - AI/ML</t>
+          <t>Quantitative Developer Intern</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -28404,226 +28404,222 @@
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>Data / AI</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E741" t="inlineStr"/>
       <c r="F741" t="inlineStr">
         <is>
-          <t>gurgaon</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="G741" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=8143756</t>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=8138524</t>
         </is>
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>Intern - AI/ML</t>
+          <t>Quantitative Developer Intern</t>
         </is>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>2026-08-21T18:33:33.878834+00:00</t>
+          <t>2026-08-21T18:33:29.313779+00:00</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>Quantitative Developer Intern</t>
+          <t>Sales &amp; Customer Success Intern - EU</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>Towerresearchcapital</t>
+          <t>Truecaller</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E742" t="inlineStr"/>
       <c r="F742" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="G742" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=8138524</t>
+          <t>https://job-boards.greenhouse.io/truecaller/jobs/8138837</t>
         </is>
       </c>
       <c r="H742" t="inlineStr">
         <is>
-          <t>Quantitative Developer Intern</t>
+          <t>Sales &amp; Customer Success Intern - EU</t>
         </is>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>2026-08-21T18:33:29.313779+00:00</t>
+          <t>2026-08-14T03:46:04.307219+00:00</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Sales &amp; Customer Success Intern - EU</t>
+          <t>Quantitative Research Internship - 6 Months, Central Execution Research</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>Truecaller</t>
+          <t>Towerresearchcapital</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E743" t="inlineStr"/>
       <c r="F743" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>London</t>
         </is>
       </c>
       <c r="G743" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/truecaller/jobs/8138837</t>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=8113986</t>
         </is>
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>Sales &amp; Customer Success Intern - EU</t>
+          <t>Quantitative Research Internship - 6 Months, Central Execution Research</t>
         </is>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>2026-08-14T03:46:04.307219+00:00</t>
+          <t>2026-08-10T17:40:47.009978+00:00</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>Quantitative Research Internship - 6 Months, Central Execution Research</t>
+          <t>[Backend] Software Engineering Intern</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>Towerresearchcapital</t>
+          <t>Enterpret</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="E744" t="inlineStr"/>
       <c r="F744" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Bengaluru, Onsite</t>
         </is>
       </c>
       <c r="G744" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=8113986</t>
+          <t>https://job-boards.greenhouse.io/enterpret/jobs/7847134003</t>
         </is>
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>Quantitative Research Internship - 6 Months, Central Execution Research</t>
+          <t>[Backend] Software Engineering Intern</t>
         </is>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>2026-08-10T17:40:47.009978+00:00</t>
+          <t>2026-08-08T04:12:52.37725+00:00</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>[Backend] Software Engineering Intern</t>
+          <t>Brand Marketing Intern</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>Enterpret</t>
+          <t>Earnin</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E745" t="inlineStr"/>
-      <c r="F745" t="inlineStr">
-        <is>
-          <t>Bengaluru, Onsite</t>
-        </is>
-      </c>
+      <c r="F745" t="inlineStr"/>
       <c r="G745" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/enterpret/jobs/7847134003</t>
+          <t>https://job-boards.greenhouse.io/earnin/jobs/8113206</t>
         </is>
       </c>
       <c r="H745" t="inlineStr">
         <is>
-          <t>[Backend] Software Engineering Intern</t>
+          <t>Brand Marketing Intern</t>
         </is>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>2026-08-08T04:12:52.37725+00:00</t>
+          <t>2026-08-08T04:12:50.084908+00:00</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>Brand Marketing Intern</t>
+          <t>Customer Success Intern</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>Earnin</t>
+          <t>Knowbe4</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E746" t="inlineStr"/>
       <c r="F746" t="inlineStr"/>
       <c r="G746" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/earnin/jobs/8113206</t>
+          <t>https://job-boards.greenhouse.io/knowbe4/jobs/8660687002</t>
         </is>
       </c>
       <c r="H746" t="inlineStr">
         <is>
-          <t>Brand Marketing Intern</t>
+          <t>Customer Success Intern</t>
         </is>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>2026-08-08T04:12:50.084908+00:00</t>
+          <t>2026-08-08T04:12:45.117452+00:00</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>Customer Success Intern</t>
+          <t>Junior Execution Trader Intern</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>Knowbe4</t>
+          <t>Towerresearchcapital</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
@@ -28635,29 +28631,29 @@
       <c r="F747" t="inlineStr"/>
       <c r="G747" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/knowbe4/jobs/8660687002</t>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=8091833</t>
         </is>
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>Customer Success Intern</t>
+          <t>Junior Execution Trader Intern</t>
         </is>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>2026-08-08T04:12:45.117452+00:00</t>
+          <t>2026-07-27T16:30:43.226773+00:00</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>Junior Execution Trader Intern</t>
+          <t>Copy Writer - Intern</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>Towerresearchcapital</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
@@ -28669,24 +28665,24 @@
       <c r="F748" t="inlineStr"/>
       <c r="G748" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=8091833</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774341101</t>
         </is>
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>Junior Execution Trader Intern</t>
+          <t>Copy Writer - Intern</t>
         </is>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:43.226773+00:00</t>
+          <t>2026-07-27T16:30:36.983937+00:00</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>Copy Writer - Intern</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -28703,24 +28699,24 @@
       <c r="F749" t="inlineStr"/>
       <c r="G749" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774341101</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4771440101</t>
         </is>
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>Copy Writer - Intern</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:36.983937+00:00</t>
+          <t>2026-07-27T16:30:35.138664+00:00</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t xml:space="preserve">Internship - Content </t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -28730,31 +28726,31 @@
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E750" t="inlineStr"/>
       <c r="F750" t="inlineStr"/>
       <c r="G750" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4771440101</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4819749101</t>
         </is>
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Internship - Content</t>
         </is>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:35.138664+00:00</t>
+          <t>2026-07-27T16:30:33.590227+00:00</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t xml:space="preserve">Internship - Content </t>
+          <t>Graphic Designer - Intern</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -28764,65 +28760,65 @@
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E751" t="inlineStr"/>
       <c r="F751" t="inlineStr"/>
       <c r="G751" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4819749101</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774342101</t>
         </is>
       </c>
       <c r="H751" t="inlineStr">
         <is>
-          <t>Internship - Content</t>
+          <t>Graphic Designer - Intern</t>
         </is>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:33.590227+00:00</t>
+          <t>2026-07-27T16:30:31.543915+00:00</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>Graphic Designer - Intern</t>
+          <t>Business Development Specialist (Outbound- International)</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>Tide</t>
         </is>
       </c>
       <c r="D752" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E752" t="inlineStr"/>
       <c r="F752" t="inlineStr"/>
       <c r="G752" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774342101</t>
+          <t>https://job-boards.greenhouse.io/tide/jobs/7081017003</t>
         </is>
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>Graphic Designer - Intern</t>
+          <t>Business Development Specialist (Outbound- International)</t>
         </is>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:31.543915+00:00</t>
+          <t>2026-07-27T16:30:28.879852+00:00</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>Business Development Specialist (Outbound- International)</t>
+          <t>Business Development Specialist (International Sales)</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -28832,65 +28828,65 @@
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E753" t="inlineStr"/>
       <c r="F753" t="inlineStr"/>
       <c r="G753" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/tide/jobs/7081017003</t>
+          <t>https://job-boards.greenhouse.io/tide/jobs/7598880003</t>
         </is>
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t>Business Development Specialist (Outbound- International)</t>
+          <t>Business Development Specialist (International Sales)</t>
         </is>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:28.879852+00:00</t>
+          <t>2026-07-27T16:30:17.721593+00:00</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>Business Development Specialist (International Sales)</t>
+          <t>Risk Intern - 6 Month Internship Opportunity</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>Tide</t>
+          <t>Towerresearchcapital</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E754" t="inlineStr"/>
       <c r="F754" t="inlineStr"/>
       <c r="G754" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/tide/jobs/7598880003</t>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=7789933</t>
         </is>
       </c>
       <c r="H754" t="inlineStr">
         <is>
-          <t>Business Development Specialist (International Sales)</t>
+          <t>Risk Intern - 6 Month Internship Opportunity</t>
         </is>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:17.721593+00:00</t>
+          <t>2026-07-27T16:30:10.248679+00:00</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>Risk Intern - 6 Month Internship Opportunity</t>
+          <t>Quantitative Trader Intern - Summer 2027</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -28907,24 +28903,24 @@
       <c r="F755" t="inlineStr"/>
       <c r="G755" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=7789933</t>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=8024128</t>
         </is>
       </c>
       <c r="H755" t="inlineStr">
         <is>
-          <t>Risk Intern - 6 Month Internship Opportunity</t>
+          <t>Quantitative Trader Intern - Summer 2027</t>
         </is>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:10.248679+00:00</t>
+          <t>2026-07-27T16:30:07.980596+00:00</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>Quantitative Trader Intern - Summer 2027</t>
+          <t>Quantitative Trader Intern, PhD</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -28941,24 +28937,24 @@
       <c r="F756" t="inlineStr"/>
       <c r="G756" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=8024128</t>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=8024138</t>
         </is>
       </c>
       <c r="H756" t="inlineStr">
         <is>
-          <t>Quantitative Trader Intern - Summer 2027</t>
+          <t>Quantitative Trader Intern, PhD</t>
         </is>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:07.980596+00:00</t>
+          <t>2026-07-27T16:30:05.838281+00:00</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>Quantitative Trader Intern, PhD</t>
+          <t>Quantitative Developer Intern - Summer 2027</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -28975,24 +28971,24 @@
       <c r="F757" t="inlineStr"/>
       <c r="G757" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=8024138</t>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=8044334</t>
         </is>
       </c>
       <c r="H757" t="inlineStr">
         <is>
-          <t>Quantitative Trader Intern, PhD</t>
+          <t>Quantitative Developer Intern - Summer 2027</t>
         </is>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:05.838281+00:00</t>
+          <t>2026-07-27T16:30:03.426202+00:00</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>Quantitative Developer Intern - Summer 2027</t>
+          <t>Business Analytics Intern - 6 Month Internship Opportunity</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -29002,60 +28998,60 @@
       </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Data / AI</t>
         </is>
       </c>
       <c r="E758" t="inlineStr"/>
       <c r="F758" t="inlineStr"/>
       <c r="G758" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=8044334</t>
+          <t>https://www.tower-research.com/open-positions/?gh_jid=8041512</t>
         </is>
       </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t>Quantitative Developer Intern - Summer 2027</t>
+          <t>Business Analytics Intern - 6 Month Internship Opportunity</t>
         </is>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:03.426202+00:00</t>
+          <t>2026-07-27T16:30:01.432263+00:00</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>Business Analytics Intern - 6 Month Internship Opportunity</t>
+          <t>Sales Development Representative Intern (Hybrid)</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>Towerresearchcapital</t>
+          <t>Knowbe4</t>
         </is>
       </c>
       <c r="D759" t="inlineStr">
         <is>
-          <t>Data / AI</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E759" t="inlineStr"/>
       <c r="F759" t="inlineStr"/>
       <c r="G759" t="inlineStr">
         <is>
-          <t>https://www.tower-research.com/open-positions/?gh_jid=8041512</t>
+          <t>https://job-boards.greenhouse.io/knowbe4/jobs/8566454002</t>
         </is>
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t>Business Analytics Intern - 6 Month Internship Opportunity</t>
+          <t>Sales Development Representative Intern (Hybrid)</t>
         </is>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:01.432263+00:00</t>
+          <t>2026-07-27T16:29:59.490728+00:00</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
@@ -29077,7 +29073,7 @@
       <c r="F760" t="inlineStr"/>
       <c r="G760" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/knowbe4/jobs/8566454002</t>
+          <t>https://job-boards.greenhouse.io/knowbe4/jobs/8566457002</t>
         </is>
       </c>
       <c r="H760" t="inlineStr">
@@ -29089,41 +29085,41 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>2026-07-27T16:29:59.490728+00:00</t>
+          <t>2026-07-27T16:29:55.183092+00:00</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>Sales Development Representative Intern (Hybrid)</t>
+          <t>Intern - Industrial Trainee</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>Knowbe4</t>
+          <t>Inmobi</t>
         </is>
       </c>
       <c r="D761" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Data / AI</t>
         </is>
       </c>
       <c r="E761" t="inlineStr"/>
       <c r="F761" t="inlineStr"/>
       <c r="G761" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/knowbe4/jobs/8566457002</t>
+          <t>https://job-boards.greenhouse.io/inmobi/jobs/8029868</t>
         </is>
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>Sales Development Representative Intern (Hybrid)</t>
+          <t>Intern - Industrial Trainee</t>
         </is>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>2026-07-27T16:29:55.183092+00:00</t>
+          <t>2026-07-27T16:29:52.581754+00:00</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
@@ -29145,7 +29141,7 @@
       <c r="F762" t="inlineStr"/>
       <c r="G762" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/inmobi/jobs/8029868</t>
+          <t>https://job-boards.greenhouse.io/inmobi/jobs/7793050</t>
         </is>
       </c>
       <c r="H762" t="inlineStr">
@@ -29157,46 +29153,46 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>2026-07-27T16:29:52.581754+00:00</t>
+          <t>2026-07-27T16:29:48.780995+00:00</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>Intern - Industrial Trainee</t>
+          <t>Security Consultant Intern</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>Inmobi</t>
+          <t>Cloudsek</t>
         </is>
       </c>
       <c r="D763" t="inlineStr">
         <is>
-          <t>Data / AI</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E763" t="inlineStr"/>
       <c r="F763" t="inlineStr"/>
       <c r="G763" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/inmobi/jobs/7793050</t>
+          <t>https://job-boards.greenhouse.io/cloudsek/jobs/6115382004</t>
         </is>
       </c>
       <c r="H763" t="inlineStr">
         <is>
-          <t>Intern - Industrial Trainee</t>
+          <t>Security Consultant Intern</t>
         </is>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>2026-07-27T16:29:48.780995+00:00</t>
+          <t>2026-07-27T16:29:47.193044+00:00</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>Security Consultant Intern</t>
+          <t xml:space="preserve">SDE Intern - Frontend   </t>
         </is>
       </c>
       <c r="C764" t="inlineStr">
@@ -29206,31 +29202,31 @@
       </c>
       <c r="D764" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="E764" t="inlineStr"/>
       <c r="F764" t="inlineStr"/>
       <c r="G764" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/cloudsek/jobs/6115382004</t>
+          <t>https://job-boards.greenhouse.io/cloudsek/jobs/5831215004</t>
         </is>
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>Security Consultant Intern</t>
+          <t>SDE Intern - Frontend</t>
         </is>
       </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>2026-07-27T16:29:47.193044+00:00</t>
+          <t>2026-07-27T16:29:44.845632+00:00</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t xml:space="preserve">SDE Intern - Frontend   </t>
+          <t>SDE - Backend - Intern</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -29240,31 +29236,31 @@
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="E765" t="inlineStr"/>
       <c r="F765" t="inlineStr"/>
       <c r="G765" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/cloudsek/jobs/5831215004</t>
+          <t>https://job-boards.greenhouse.io/cloudsek/jobs/5766402004</t>
         </is>
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>SDE Intern - Frontend</t>
+          <t>SDE - Backend - Intern</t>
         </is>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>2026-07-27T16:29:44.845632+00:00</t>
+          <t>2026-07-27T16:29:42.382537+00:00</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>SDE - Backend - Intern</t>
+          <t>Business Development Representative Intern - Canada</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
@@ -29274,36 +29270,36 @@
       </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E766" t="inlineStr"/>
       <c r="F766" t="inlineStr"/>
       <c r="G766" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/cloudsek/jobs/5766402004</t>
+          <t>https://job-boards.greenhouse.io/cloudsek/jobs/6005469004</t>
         </is>
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>SDE - Backend - Intern</t>
+          <t>Business Development Representative Intern - Canada</t>
         </is>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>2026-07-27T16:29:42.382537+00:00</t>
+          <t>2026-07-27T16:29:12.993097+00:00</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>Business Development Representative Intern - Canada</t>
+          <t>[Tech Cooperative Internship 2026] Software Engineer in Back End intern (6 months)</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>Cloudsek</t>
+          <t>Agoda</t>
         </is>
       </c>
       <c r="D767" t="inlineStr">
@@ -29315,24 +29311,24 @@
       <c r="F767" t="inlineStr"/>
       <c r="G767" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/cloudsek/jobs/6005469004</t>
+          <t>https://job-boards.greenhouse.io/agoda/jobs/5443559</t>
         </is>
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t>Business Development Representative Intern - Canada</t>
+          <t>[Tech Cooperative Internship 2026] Software Engineer in Back End intern (6 months)</t>
         </is>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>2026-07-27T16:29:12.993097+00:00</t>
+          <t>2026-07-27T16:28:57.849831+00:00</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>[Tech Cooperative Internship 2026] Software Engineer in Back End intern (6 months)</t>
+          <t>International Payroll Partner</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -29349,29 +29345,29 @@
       <c r="F768" t="inlineStr"/>
       <c r="G768" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/agoda/jobs/5443559</t>
+          <t>https://job-boards.greenhouse.io/agoda/jobs/8063978</t>
         </is>
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>[Tech Cooperative Internship 2026] Software Engineer in Back End intern (6 months)</t>
+          <t>International Payroll Partner</t>
         </is>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>2026-07-27T16:28:57.849831+00:00</t>
+          <t>2026-07-27T10:49:04.274532+00:00</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>International Payroll Partner</t>
+          <t>Copy Writer - Intern</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>Agoda</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="D769" t="inlineStr">
@@ -29383,24 +29379,24 @@
       <c r="F769" t="inlineStr"/>
       <c r="G769" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/agoda/jobs/8063978</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774341101</t>
         </is>
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t>International Payroll Partner</t>
+          <t>Copy Writer - Intern</t>
         </is>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>2026-07-27T10:49:04.274532+00:00</t>
+          <t>2026-07-27T10:49:00.838626+00:00</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>Copy Writer - Intern</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -29417,24 +29413,24 @@
       <c r="F770" t="inlineStr"/>
       <c r="G770" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774341101</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4771440101</t>
         </is>
       </c>
       <c r="H770" t="inlineStr">
         <is>
-          <t>Copy Writer - Intern</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>2026-07-27T10:49:00.838626+00:00</t>
+          <t>2026-07-27T10:48:58.630946+00:00</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t xml:space="preserve">Internship - Content </t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -29444,31 +29440,31 @@
       </c>
       <c r="D771" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E771" t="inlineStr"/>
       <c r="F771" t="inlineStr"/>
       <c r="G771" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4771440101</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4819749101</t>
         </is>
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Internship - Content</t>
         </is>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>2026-07-27T10:48:58.630946+00:00</t>
+          <t>2026-07-27T10:48:56.06648+00:00</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t xml:space="preserve">Internship - Content </t>
+          <t>Graphic Designer - Intern</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
@@ -29478,31 +29474,31 @@
       </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E772" t="inlineStr"/>
       <c r="F772" t="inlineStr"/>
       <c r="G772" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4819749101</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774342101</t>
         </is>
       </c>
       <c r="H772" t="inlineStr">
         <is>
-          <t>Internship - Content</t>
+          <t>Graphic Designer - Intern</t>
         </is>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>2026-07-27T10:48:56.06648+00:00</t>
+          <t>2026-07-27T10:42:53.996409+00:00</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>Graphic Designer - Intern</t>
+          <t>Copy Writer - Intern</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -29512,31 +29508,31 @@
       </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E773" t="inlineStr"/>
       <c r="F773" t="inlineStr"/>
       <c r="G773" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774342101</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774341101</t>
         </is>
       </c>
       <c r="H773" t="inlineStr">
         <is>
-          <t>Graphic Designer - Intern</t>
+          <t>Copy Writer - Intern</t>
         </is>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>2026-07-27T10:42:53.996409+00:00</t>
+          <t>2026-07-27T10:42:50.938109+00:00</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>Copy Writer - Intern</t>
+          <t>Graphic Designer - Intern</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -29546,31 +29542,31 @@
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E774" t="inlineStr"/>
       <c r="F774" t="inlineStr"/>
       <c r="G774" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774341101</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774342101</t>
         </is>
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>Copy Writer - Intern</t>
+          <t>Graphic Designer - Intern</t>
         </is>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>2026-07-27T10:42:50.938109+00:00</t>
+          <t>2026-07-27T10:42:47.32783+00:00</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>Graphic Designer - Intern</t>
+          <t xml:space="preserve">Internship - Content </t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -29580,31 +29576,31 @@
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E775" t="inlineStr"/>
       <c r="F775" t="inlineStr"/>
       <c r="G775" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4774342101</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4819749101</t>
         </is>
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>Graphic Designer - Intern</t>
+          <t>Internship - Content</t>
         </is>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>2026-07-27T10:42:47.32783+00:00</t>
+          <t>2026-07-27T10:42:43.192382+00:00</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t xml:space="preserve">Internship - Content </t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -29614,103 +29610,103 @@
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E776" t="inlineStr"/>
       <c r="F776" t="inlineStr"/>
       <c r="G776" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4819749101</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4771440101</t>
         </is>
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>Internship - Content</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>2026-07-27T10:42:43.192382+00:00</t>
+          <t>2026-07-26T19:14:17.297621+00:00</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>ReactJS Internship</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>ElevateHQ</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>Internship</t>
-        </is>
-      </c>
-      <c r="E777" t="inlineStr"/>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>₹240000 - ₹420000</t>
+        </is>
+      </c>
       <c r="F777" t="inlineStr"/>
       <c r="G777" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4771440101</t>
+          <t>https://www.adzuna.in/details/4794473734?utm_medium=api&amp;utm_source=e044e1cb</t>
         </is>
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Position Overview: We are seeking a talented and motivated ReactJS Intern to join our team for a 6-month full-time internship. This is a fantastic opportunity for someone with prior internship experience to deepen their knowledge and skills in ReactJS while working on cutting-edge projects. Responsibilities: Collaborate with the development team to design, develop, and maintain web applications using ReactJS. Write clean, maintainable, and efficient code. Participate in code reviews and contrib…</t>
         </is>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>2026-07-26T19:14:17.297621+00:00</t>
+          <t>2026-07-26T19:14:13.725695+00:00</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>ReactJS Internship</t>
+          <t>Developer Internship</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>ElevateHQ</t>
+          <t>PBL India</t>
         </is>
       </c>
       <c r="D778" t="inlineStr">
         <is>
-          <t>Frontend</t>
-        </is>
-      </c>
-      <c r="E778" t="inlineStr">
-        <is>
-          <t>₹240000 - ₹420000</t>
-        </is>
-      </c>
+          <t>Internship</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr"/>
       <c r="F778" t="inlineStr"/>
       <c r="G778" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/4794473734?utm_medium=api&amp;utm_source=e044e1cb</t>
+          <t>https://www.adzuna.in/details/4801600698?utm_medium=api&amp;utm_source=e044e1cb</t>
         </is>
       </c>
       <c r="H778" t="inlineStr">
         <is>
-          <t>Position Overview: We are seeking a talented and motivated ReactJS Intern to join our team for a 6-month full-time internship. This is a fantastic opportunity for someone with prior internship experience to deepen their knowledge and skills in ReactJS while working on cutting-edge projects. Responsibilities: Collaborate with the development team to design, develop, and maintain web applications using ReactJS. Write clean, maintainable, and efficient code. Participate in code reviews and contrib…</t>
+          <t>Percpktika Brand Lab is a Product Development startup which supports and develops products guiding social innovation. We are looking for smart and talented interns who are capable of working from Delhi or remote and submitting results. At PBL we have an efficient training process which provides resources to grow and nurture your talent. The selected intern(s) will work on following during the internship: 1. Code Reviews and Research. 2. Creating Core features using Node.js and Native Script sup…</t>
         </is>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>2026-07-26T19:14:13.725695+00:00</t>
+          <t>2026-07-26T19:14:07.63634+00:00</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>Developer Internship</t>
+          <t>Design Internship</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -29720,65 +29716,65 @@
       </c>
       <c r="D779" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E779" t="inlineStr"/>
       <c r="F779" t="inlineStr"/>
       <c r="G779" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/4801600698?utm_medium=api&amp;utm_source=e044e1cb</t>
+          <t>https://www.adzuna.in/details/4801437257?utm_medium=api&amp;utm_source=e044e1cb</t>
         </is>
       </c>
       <c r="H779" t="inlineStr">
         <is>
-          <t>Percpktika Brand Lab is a Product Development startup which supports and develops products guiding social innovation. We are looking for smart and talented interns who are capable of working from Delhi or remote and submitting results. At PBL we have an efficient training process which provides resources to grow and nurture your talent. The selected intern(s) will work on following during the internship: 1. Code Reviews and Research. 2. Creating Core features using Node.js and Native Script sup…</t>
+          <t>Percpktika Brand Lab is a Product Development startup which supports and develops products guiding social innovation. We are looking for smart and talented interns who are capable of working from Delhi or remote and submitting results. At PBL we have an efficient training process which provides resources to grow and nurture your talent. The selected intern(s) will work on following during the internship: 1. Designing User Interface. 2. Experience planning and flow. 3. Product Branding and Desig…</t>
         </is>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>2026-07-26T19:14:07.63634+00:00</t>
+          <t>2026-07-26T19:13:19.489348+00:00</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>Design Internship</t>
+          <t>Customer Care Intern</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>PBL India</t>
+          <t>Criteo</t>
         </is>
       </c>
       <c r="D780" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Internship</t>
         </is>
       </c>
       <c r="E780" t="inlineStr"/>
       <c r="F780" t="inlineStr"/>
       <c r="G780" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/details/4801437257?utm_medium=api&amp;utm_source=e044e1cb</t>
+          <t>https://www.adzuna.in/land/ad/5790410523?se=rFvE0iWJ8RGGXqQIyNVN5Q&amp;utm_medium=api&amp;utm_source=e044e1cb&amp;v=5E72C4726A0DF728D03FF51102E0532CA986DDEA</t>
         </is>
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>Percpktika Brand Lab is a Product Development startup which supports and develops products guiding social innovation. We are looking for smart and talented interns who are capable of working from Delhi or remote and submitting results. At PBL we have an efficient training process which provides resources to grow and nurture your talent. The selected intern(s) will work on following during the internship: 1. Designing User Interface. 2. Experience planning and flow. 3. Product Branding and Desig…</t>
+          <t>This job is with Criteo, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. What You'll Do: The multinational Global Customer Care Team is the first point of contact for Criteo Customers; our goal is to provide excellent customer support to all incoming client requests using email or live chat. We excel at collaboration, communication, and teamwork, as they are key to solving our client's re…</t>
         </is>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>2026-07-26T19:13:19.489348+00:00</t>
+          <t>2026-07-26T19:13:17.765892+00:00</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>Customer Care Intern</t>
+          <t>Sales &amp; Strategy Intern</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -29788,259 +29784,225 @@
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>Internship</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="E781" t="inlineStr"/>
       <c r="F781" t="inlineStr"/>
       <c r="G781" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5790410523?se=rFvE0iWJ8RGGXqQIyNVN5Q&amp;utm_medium=api&amp;utm_source=e044e1cb&amp;v=5E72C4726A0DF728D03FF51102E0532CA986DDEA</t>
+          <t>https://www.adzuna.in/land/ad/5806276940?se=rFvE0iWJ8RGGXqQIyNVN5Q&amp;utm_medium=api&amp;utm_source=e044e1cb&amp;v=B2147145725F724ABD3B0362E330EB1DD5EB962B</t>
         </is>
       </c>
       <c r="H781" t="inlineStr">
         <is>
-          <t>This job is with Criteo, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. What You'll Do: The multinational Global Customer Care Team is the first point of contact for Criteo Customers; our goal is to provide excellent customer support to all incoming client requests using email or live chat. We excel at collaboration, communication, and teamwork, as they are key to solving our client's re…</t>
+          <t>This job is with Criteo, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. What You'll Do: As a Sales &amp; Strategy Intern, you will be part of our India team that works with new and existing clients. You will be learning and working with brands, analyzing and optimizing campaigns, along with cultivating a strong and productive relationship with clients. This is a 12-month paid, full-time inte…</t>
         </is>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>2026-07-26T19:13:17.765892+00:00</t>
+          <t>2026-07-26T18:23:56.921677+00:00</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>Sales &amp; Strategy Intern</t>
+          <t>GRAPHIC DESIGNER</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>Criteo</t>
+          <t>NEW VINE LIMITED</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E782" t="inlineStr"/>
       <c r="F782" t="inlineStr"/>
       <c r="G782" t="inlineStr">
         <is>
-          <t>https://www.adzuna.in/land/ad/5806276940?se=rFvE0iWJ8RGGXqQIyNVN5Q&amp;utm_medium=api&amp;utm_source=e044e1cb&amp;v=B2147145725F724ABD3B0362E330EB1DD5EB962B</t>
+          <t>https://remoteOK.com/remote-jobs/remote-graphic-designer-new-vine-limited-1135316</t>
         </is>
       </c>
       <c r="H782" t="inlineStr">
         <is>
-          <t>This job is with Criteo, an inclusive employer and a member of myGwork – the largest global platform for the LGBTQ business community. Please do not contact the recruiter directly. What You'll Do: As a Sales &amp; Strategy Intern, you will be part of our India team that works with new and existing clients. You will be learning and working with brands, analyzing and optimizing campaigns, along with cultivating a strong and productive relationship with clients. This is a 12-month paid, full-time inte…</t>
+          <t>Graphic Designer (part-time) An exciting opportunity has arisen for a Graphic Designer (part-time) to join us, working remotely with great benefits. The role will work primarily on our books, subscription materials, and digital resources, creating eye-catching covers, inside layouts, and ebooks. Prior experience of working on these types of resources in Adobe Creative Suite is essential, as is a solid understanding of design, layout, typography, and brand. Salary: Â£16,500 (Â£27,500 FTE) Applications close: 29 August 2026 Download the job information (.pdf) Download the application form (.docx) We welcome applicants from all backgrounds and communities, in particular those that are currently under-represented within our staff team. This includes, but is not limited to, people from Black, Asian, and other ethnic groups, especially within our leadership roles. Please mention the word **PROLIFIC** and tag RMjAyLjY2LjE2NC42 when applying to show you read the job post completely (#RMjAyLjY2LjE2NC42). This is a beta feature to avoid spam applicants. Companies can search these words to find applicants that read this and see they're human.</t>
         </is>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>2026-07-26T18:23:56.921677+00:00</t>
+          <t>2026-07-26T18:23:39.597545+00:00</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>GRAPHIC DESIGNER</t>
+          <t>Executive Assistant</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>NEW VINE LIMITED</t>
+          <t>Ritual AdsÂ®</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E783" t="inlineStr"/>
       <c r="F783" t="inlineStr"/>
       <c r="G783" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-graphic-designer-new-vine-limited-1135316</t>
+          <t>https://remoteOK.com/remote-jobs/remote-executive-assistant-ritual-adsr-1135344</t>
         </is>
       </c>
       <c r="H783" t="inlineStr">
         <is>
-          <t>Graphic Designer (part-time) An exciting opportunity has arisen for a Graphic Designer (part-time) to join us, working remotely with great benefits. The role will work primarily on our books, subscription materials, and digital resources, creating eye-catching covers, inside layouts, and ebooks. Prior experience of working on these types of resources in Adobe Creative Suite is essential, as is a solid understanding of design, layout, typography, and brand. Salary: Â£16,500 (Â£27,500 FTE) Applications close: 29 August 2026 Download the job information (.pdf) Download the application form (.docx) We welcome applicants from all backgrounds and communities, in particular those that are currently under-represented within our staff team. This includes, but is not limited to, people from Black, Asian, and other ethnic groups, especially within our leadership roles. Please mention the word **PROLIFIC** and tag RMjAyLjY2LjE2NC42 when applying to show you read the job post completely (#RMjAyLjY2LjE2NC42). This is a beta feature to avoid spam applicants. Companies can search these words to find applicants that read this and see they're human.</t>
+          <t>Company Description Ritual AdsÂ® is a cutting-edge AI software company that uses generative AI to create tailored, data-driven advertising content on demand. The platform helps organizations quickly produce high-impact, customized ads that align with their brand and audience. By combining advanced machine learning with real-time data, Ritual AdsÂ® aims to improve campaign performance and efficiency. Team members collaborate in a technology-forward environment focused on innovation, scalability, and measurable results. Role Description The Executive Assistant at Ritual AdsÂ® is a full-time, remote role responsible for providing comprehensive administrative and organizational support to company leadership. Day-to-day tasks include managing calendars, scheduling meetings, coordinating travel, and preparing agendas and meeting materials. The Executive Assistant will handle expense reports, track reimbursements, and maintain accurate documentation. The role also includes managing correspondence, drafting and editing communications, organizing digital files, and supporting special projects and operational tasks to ensure smooth executive workflows. Qualifications Strong Executive Adminis</t>
         </is>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>2026-07-26T18:23:39.597545+00:00</t>
+          <t>2026-07-26T18:23:35.307873+00:00</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>Executive Assistant</t>
+          <t>Product Designer</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>Ritual AdsÂ®</t>
+          <t>Flint</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="E784" t="inlineStr"/>
       <c r="F784" t="inlineStr"/>
       <c r="G784" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-executive-assistant-ritual-adsr-1135344</t>
+          <t>https://remoteOK.com/remote-jobs/remote-product-designer-flint-1135340</t>
         </is>
       </c>
       <c r="H784" t="inlineStr">
         <is>
-          <t>Company Description Ritual AdsÂ® is a cutting-edge AI software company that uses generative AI to create tailored, data-driven advertising content on demand. The platform helps organizations quickly produce high-impact, customized ads that align with their brand and audience. By combining advanced machine learning with real-time data, Ritual AdsÂ® aims to improve campaign performance and efficiency. Team members collaborate in a technology-forward environment focused on innovation, scalability, and measurable results. Role Description The Executive Assistant at Ritual AdsÂ® is a full-time, remote role responsible for providing comprehensive administrative and organizational support to company leadership. Day-to-day tasks include managing calendars, scheduling meetings, coordinating travel, and preparing agendas and meeting materials. The Executive Assistant will handle expense reports, track reimbursements, and maintain accurate documentation. The role also includes managing correspondence, drafting and editing communications, organizing digital files, and supporting special projects and operational tasks to ensure smooth executive workflows. Qualifications Strong Executive Adminis</t>
+          <t>Compensation: $160kâ190k base + meaningful equity About Flint The best education anyone has ever received is one person paying close attention to one student: moving at their pace, noticing what they missed, asking the next question at the right moment. But the current system is built around a compromise with one teacher managing thirty students. Flint exists to take that compromise off the table. Personalized learning, at the scale of a whole school â every student working with something closer to a tutor, and every teacher able to see what's actually happening across their class instead of guessing. Go look at the product before you read any further: app.flintk12.com The Role Students want something that stays with them, going at their pace and helps them get unstuck without just handing over the answer. Teachers want that happening inside a class they still control, and they'd like their evenings back. Admins want proof that the platform they rolled out is leading to teacher productivity and student progress. Your job is to dive deep into this design problem, holding three sets of needs within one product. Weâll trust you to ship designs that are the best possible solution</t>
         </is>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>2026-07-26T18:23:35.307873+00:00</t>
+          <t>2026-07-26T18:23:18.030686+00:00</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>Product Designer</t>
+          <t>Join our UK team</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>Flint</t>
+          <t>Workdry Germany</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E785" t="inlineStr"/>
       <c r="F785" t="inlineStr"/>
       <c r="G785" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-product-designer-flint-1135340</t>
+          <t>https://remoteOK.com/remote-jobs/remote-join-our-uk-team-workdry-germany-1135314</t>
         </is>
       </c>
       <c r="H785" t="inlineStr">
         <is>
-          <t>Compensation: $160kâ190k base + meaningful equity About Flint The best education anyone has ever received is one person paying close attention to one student: moving at their pace, noticing what they missed, asking the next question at the right moment. But the current system is built around a compromise with one teacher managing thirty students. Flint exists to take that compromise off the table. Personalized learning, at the scale of a whole school â every student working with something closer to a tutor, and every teacher able to see what's actually happening across their class instead of guessing. Go look at the product before you read any further: app.flintk12.com The Role Students want something that stays with them, going at their pace and helps them get unstuck without just handing over the answer. Teachers want that happening inside a class they still control, and they'd like their evenings back. Admins want proof that the platform they rolled out is leading to teacher productivity and student progress. Your job is to dive deep into this design problem, holding three sets of needs within one product. Weâll trust you to ship designs that are the best possible solution</t>
+          <t>BracknellPump Rental SolutionsBracknellPump Rental SolutionsGreat YarmouthPump Rental SolutionsNottinghamPump Rental SolutionsAberdeenPump Rental SolutionsConwyPump Rental SolutionsStokeWorkdry - Group Central ServicesStokeWorkdry - Group Central ServicesWorkingtonPump Rental Solutions Please mention the word **GREATNESS** and tag RMjAyLjY2LjE2NC42 when applying to show you read the job post completely (#RMjAyLjY2LjE2NC42). This is a beta feature to avoid spam applicants. Companies can search these words to find applicants that read this and see they're human.</t>
         </is>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>2026-07-26T18:23:18.030686+00:00</t>
+          <t>2026-07-26T18:23:11.834056+00:00</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>Join our UK team</t>
+          <t>Safety Data Analyst</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>Workdry Germany</t>
+          <t>SkyWest Airlines</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Data / AI</t>
         </is>
       </c>
       <c r="E786" t="inlineStr"/>
       <c r="F786" t="inlineStr"/>
       <c r="G786" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-join-our-uk-team-workdry-germany-1135314</t>
+          <t>https://remoteOK.com/remote-jobs/remote-safety-data-analyst-skywest-airlines-1135445</t>
         </is>
       </c>
       <c r="H786" t="inlineStr">
         <is>
-          <t>BracknellPump Rental SolutionsBracknellPump Rental SolutionsGreat YarmouthPump Rental SolutionsNottinghamPump Rental SolutionsAberdeenPump Rental SolutionsConwyPump Rental SolutionsStokeWorkdry - Group Central ServicesStokeWorkdry - Group Central ServicesWorkingtonPump Rental Solutions Please mention the word **GREATNESS** and tag RMjAyLjY2LjE2NC42 when applying to show you read the job post completely (#RMjAyLjY2LjE2NC42). This is a beta feature to avoid spam applicants. Companies can search these words to find applicants that read this and see they're human.</t>
+          <t>About SkyWest With over 16,000 aviation professionals operating thousands of daily flights, SkyWest Airlines connects millions of passengers each month to hundreds of destinations across North America. SkyWest operates in partnership with Delta Air Lines, United Airlines, American Airlines, and Alaska Airlines and has a fleet of nearly 450 aircraft. Headquartered in St. George, Utah, SkyWest's industry-leading workforce and excellent leadership team have consistently generated solid operational and economic performance, setting the standard for excellence in the regional industry. SkyWest employees enjoy a distinctive and unmatched culture of teamwork, respect, quality, and professionalism, along with world-class benefits such as a 401(k) match, Performance Rewards, health care, retirement, and discounted travel worldwide. Primary Job Duties Analyze, compile, and report safety data to support all SkyWest safety programs. Collect, analyze, and report safety assurance data from multiple safety data sources. Identify, monitor, and communicate safety performance trends and emerging risks. Track, maintain, and report key performance indicators (KPIs) for the Safety Department, including</t>
         </is>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>2026-07-26T18:23:11.834056+00:00</t>
+          <t>2026-07-17T10:23:01.374271+00:00</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>Safety Data Analyst</t>
+          <t>Test Internship</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>SkyWest Airlines</t>
+          <t>Test Company</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>Data / AI</t>
-        </is>
-      </c>
-      <c r="E787" t="inlineStr"/>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>10,000/mo</t>
+        </is>
+      </c>
       <c r="F787" t="inlineStr"/>
       <c r="G787" t="inlineStr">
         <is>
-          <t>https://remoteOK.com/remote-jobs/remote-safety-data-analyst-skywest-airlines-1135445</t>
+          <t>https://example.com</t>
         </is>
       </c>
       <c r="H787" t="inlineStr">
-        <is>
-          <t>About SkyWest With over 16,000 aviation professionals operating thousands of daily flights, SkyWest Airlines connects millions of passengers each month to hundreds of destinations across North America. SkyWest operates in partnership with Delta Air Lines, United Airlines, American Airlines, and Alaska Airlines and has a fleet of nearly 450 aircraft. Headquartered in St. George, Utah, SkyWest's industry-leading workforce and excellent leadership team have consistently generated solid operational and economic performance, setting the standard for excellence in the regional industry. SkyWest employees enjoy a distinctive and unmatched culture of teamwork, respect, quality, and professionalism, along with world-class benefits such as a 401(k) match, Performance Rewards, health care, retirement, and discounted travel worldwide. Primary Job Duties Analyze, compile, and report safety data to support all SkyWest safety programs. Collect, analyze, and report safety assurance data from multiple safety data sources. Identify, monitor, and communicate safety performance trends and emerging risks. Track, maintain, and report key performance indicators (KPIs) for the Safety Department, including</t>
-        </is>
-      </c>
-    </row>
-    <row r="788">
-      <c r="A788" t="inlineStr">
-        <is>
-          <t>2026-07-17T10:23:01.374271+00:00</t>
-        </is>
-      </c>
-      <c r="B788" t="inlineStr">
-        <is>
-          <t>Test Internship</t>
-        </is>
-      </c>
-      <c r="C788" t="inlineStr">
-        <is>
-          <t>Test Company</t>
-        </is>
-      </c>
-      <c r="D788" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E788" t="inlineStr">
-        <is>
-          <t>10,000/mo</t>
-        </is>
-      </c>
-      <c r="F788" t="inlineStr"/>
-      <c r="G788" t="inlineStr">
-        <is>
-          <t>https://example.com</t>
-        </is>
-      </c>
-      <c r="H788" t="inlineStr">
         <is>
           <t>This is a test listing</t>
         </is>
